--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>273239</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>33.6199989318848</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>33.9199981689453</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>161036</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>34.6399993896484</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>33.6399993896484</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>34.0999984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>34.6399993896484</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>152079</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>34.9000015258789</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>34.2400016784668</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>34.560001373291</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>34.6599998474121</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>177656</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>35.0400009155273</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>34.5200004577637</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>34.7000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>34.8800010681152</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>94801</v>
+        <v>87957</v>
       </c>
       <c r="C2715" t="n">
-        <v>37.2599983215332</v>
+        <v>36.939998626709</v>
       </c>
       <c r="D2715" t="n">
-        <v>36.4799995422363</v>
+        <v>36.0800018310547</v>
       </c>
       <c r="E2715" t="n">
-        <v>36.560001373291</v>
+        <v>36.4000015258789</v>
       </c>
       <c r="F2715" t="n">
-        <v>37.060001373291</v>
+        <v>36.8199996948242</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>186521</v>
+        <v>94801</v>
       </c>
       <c r="C2716" t="n">
-        <v>36.939998626709</v>
+        <v>37.2599983215332</v>
       </c>
       <c r="D2716" t="n">
-        <v>35.939998626709</v>
+        <v>36.4799995422363</v>
       </c>
       <c r="E2716" t="n">
-        <v>36.8199996948242</v>
+        <v>36.560001373291</v>
       </c>
       <c r="F2716" t="n">
-        <v>36.7200012207031</v>
+        <v>37.060001373291</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>239118</v>
+        <v>186521</v>
       </c>
       <c r="C2717" t="n">
+        <v>36.939998626709</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>35.939998626709</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>36.8199996948242</v>
+      </c>
+      <c r="F2717" t="n">
         <v>36.7200012207031</v>
-      </c>
-      <c r="D2717" t="n">
-        <v>35.060001373291</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>35.2999992370605</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>151965</v>
+        <v>239118</v>
       </c>
       <c r="C2718" t="n">
-        <v>35.439998626709</v>
+        <v>36.7200012207031</v>
       </c>
       <c r="D2718" t="n">
-        <v>34.8199996948242</v>
+        <v>35.060001373291</v>
       </c>
       <c r="E2718" t="n">
-        <v>35.2599983215332</v>
+        <v>36.5</v>
       </c>
       <c r="F2718" t="n">
-        <v>35.1599998474121</v>
+        <v>35.2999992370605</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>273239</v>
+        <v>151965</v>
       </c>
       <c r="C2719" t="n">
-        <v>35.5</v>
+        <v>35.439998626709</v>
       </c>
       <c r="D2719" t="n">
-        <v>33.6199989318848</v>
+        <v>34.8199996948242</v>
       </c>
       <c r="E2719" t="n">
-        <v>35.5</v>
+        <v>35.2599983215332</v>
       </c>
       <c r="F2719" t="n">
-        <v>33.9199981689453</v>
+        <v>35.1599998474121</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>161036</v>
+        <v>273239</v>
       </c>
       <c r="C2720" t="n">
-        <v>34.6399993896484</v>
+        <v>35.5</v>
       </c>
       <c r="D2720" t="n">
-        <v>33.6399993896484</v>
+        <v>33.6199989318848</v>
       </c>
       <c r="E2720" t="n">
-        <v>34.0999984741211</v>
+        <v>35.5</v>
       </c>
       <c r="F2720" t="n">
-        <v>34.6399993896484</v>
+        <v>33.9199981689453</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>152079</v>
+        <v>161036</v>
       </c>
       <c r="C2721" t="n">
-        <v>34.9000015258789</v>
+        <v>34.6399993896484</v>
       </c>
       <c r="D2721" t="n">
-        <v>34.2400016784668</v>
+        <v>33.6399993896484</v>
       </c>
       <c r="E2721" t="n">
-        <v>34.560001373291</v>
+        <v>34.0999984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>34.6599998474121</v>
+        <v>34.6399993896484</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>177656</v>
+        <v>152079</v>
       </c>
       <c r="C2722" t="n">
-        <v>35.0400009155273</v>
+        <v>34.9000015258789</v>
       </c>
       <c r="D2722" t="n">
-        <v>34.5200004577637</v>
+        <v>34.2400016784668</v>
       </c>
       <c r="E2722" t="n">
+        <v>34.560001373291</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>34.6599998474121</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>844240</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>35.3400001525879</v>
+      </c>
+      <c r="D2723" t="n">
         <v>34.7000007629395</v>
       </c>
-      <c r="F2722" t="n">
-        <v>34.8800010681152</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="E2723" t="n">
+        <v>34.8600006103516</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>35.2599983215332</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>35.5999984741211</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>35.6199989318848</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>341165</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>37.9000015258789</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>35.9599990844727</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>35.9799995422363</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>35.9799995422363</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>37.1199989318848</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>143678</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>37.0200004577637</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>36.7000007629395</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>36.7000007629395</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>36.0400009155273</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>114316</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>35.0999984741211</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>35.8600006103516</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>35.8600006103516</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>35.1800003051758</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>150128</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>36.8800010681152</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>35.6599998474121</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>35.6599998474121</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>83624</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>36.7400016784668</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>35.6199989318848</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>36.4000015258789</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IP.MI.xlsx
+++ b/data/IP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G2" t="n">
-        <v>12.8346071243286</v>
+        <v>12.8346042633057</v>
       </c>
       <c r="H2" t="n">
         <v>180451</v>
@@ -485,7 +485,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G4" t="n">
-        <v>12.7068090438843</v>
+        <v>12.70680809021</v>
       </c>
       <c r="H4" t="n">
         <v>289856</v>
@@ -514,7 +514,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G5" t="n">
-        <v>12.0769424438477</v>
+        <v>12.0769443511963</v>
       </c>
       <c r="H5" t="n">
         <v>388767</v>
@@ -543,7 +543,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G6" t="n">
-        <v>11.8030920028687</v>
+        <v>11.80309009552</v>
       </c>
       <c r="H6" t="n">
         <v>293614</v>
@@ -572,7 +572,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G7" t="n">
-        <v>10.9724035263062</v>
+        <v>10.9724016189575</v>
       </c>
       <c r="H7" t="n">
         <v>615533</v>
@@ -601,7 +601,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G8" t="n">
-        <v>11.1458425521851</v>
+        <v>11.1458415985107</v>
       </c>
       <c r="H8" t="n">
         <v>600916</v>
@@ -659,7 +659,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G10" t="n">
-        <v>10.79896068573</v>
+        <v>10.7989616394043</v>
       </c>
       <c r="H10" t="n">
         <v>618401</v>
@@ -688,7 +688,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>10.406436920166</v>
+        <v>10.4064388275146</v>
       </c>
       <c r="H11" t="n">
         <v>591777</v>
@@ -717,7 +717,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G12" t="n">
-        <v>10.4246940612793</v>
+        <v>10.4246950149536</v>
       </c>
       <c r="H12" t="n">
         <v>596902</v>
@@ -746,7 +746,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G13" t="n">
-        <v>10.4703359603882</v>
+        <v>10.4703378677368</v>
       </c>
       <c r="H13" t="n">
         <v>323065</v>
@@ -775,7 +775,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G14" t="n">
-        <v>10.1964826583862</v>
+        <v>10.1964836120605</v>
       </c>
       <c r="H14" t="n">
         <v>324322</v>
@@ -833,7 +833,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G16" t="n">
-        <v>10.4885950088501</v>
+        <v>10.4885931015015</v>
       </c>
       <c r="H16" t="n">
         <v>536021</v>
@@ -891,7 +891,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G18" t="n">
-        <v>10.5342359542847</v>
+        <v>10.534234046936</v>
       </c>
       <c r="H18" t="n">
         <v>448558</v>
@@ -1007,7 +1007,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G22" t="n">
-        <v>10.7533178329468</v>
+        <v>10.7533187866211</v>
       </c>
       <c r="H22" t="n">
         <v>502246</v>
@@ -1036,7 +1036,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G23" t="n">
-        <v>10.4520797729492</v>
+        <v>10.4520807266235</v>
       </c>
       <c r="H23" t="n">
         <v>213892</v>
@@ -1065,7 +1065,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G24" t="n">
-        <v>10.3607940673828</v>
+        <v>10.3607950210571</v>
       </c>
       <c r="H24" t="n">
         <v>405686</v>
@@ -1094,7 +1094,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G25" t="n">
-        <v>10.278639793396</v>
+        <v>10.2786407470703</v>
       </c>
       <c r="H25" t="n">
         <v>700665</v>
@@ -1123,7 +1123,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G26" t="n">
-        <v>10.1873540878296</v>
+        <v>10.1873531341553</v>
       </c>
       <c r="H26" t="n">
         <v>428569</v>
@@ -1152,7 +1152,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G27" t="n">
-        <v>9.61226177215576</v>
+        <v>9.61226081848145</v>
       </c>
       <c r="H27" t="n">
         <v>421546</v>
@@ -1181,7 +1181,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G28" t="n">
-        <v>9.65790462493896</v>
+        <v>9.65790367126465</v>
       </c>
       <c r="H28" t="n">
         <v>329612</v>
@@ -1210,7 +1210,7 @@
         <v>10.75</v>
       </c>
       <c r="G29" t="n">
-        <v>9.81308555603027</v>
+        <v>9.81308937072754</v>
       </c>
       <c r="H29" t="n">
         <v>224208</v>
@@ -1239,7 +1239,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.53923606872559</v>
+        <v>9.53923416137695</v>
       </c>
       <c r="H30" t="n">
         <v>233991</v>
@@ -1268,7 +1268,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G31" t="n">
-        <v>10.1599702835083</v>
+        <v>10.1599683761597</v>
       </c>
       <c r="H31" t="n">
         <v>398219</v>
@@ -1326,7 +1326,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G33" t="n">
-        <v>10.7441902160645</v>
+        <v>10.7441892623901</v>
       </c>
       <c r="H33" t="n">
         <v>498477</v>
@@ -1355,7 +1355,7 @@
         <v>12.75</v>
       </c>
       <c r="G34" t="n">
-        <v>11.6387796401978</v>
+        <v>11.6387786865234</v>
       </c>
       <c r="H34" t="n">
         <v>904448</v>
@@ -1384,7 +1384,7 @@
         <v>12.75</v>
       </c>
       <c r="G35" t="n">
-        <v>11.6387796401978</v>
+        <v>11.6387786865234</v>
       </c>
       <c r="H35" t="n">
         <v>456330</v>
@@ -1413,7 +1413,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>11.5018529891968</v>
+        <v>11.5018510818481</v>
       </c>
       <c r="H36" t="n">
         <v>361165</v>
@@ -1471,7 +1471,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G38" t="n">
-        <v>11.7848329544067</v>
+        <v>11.7848339080811</v>
       </c>
       <c r="H38" t="n">
         <v>583400</v>
@@ -1500,7 +1500,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>11.6113929748535</v>
+        <v>11.6113939285278</v>
       </c>
       <c r="H39" t="n">
         <v>401441</v>
@@ -1529,7 +1529,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G40" t="n">
-        <v>11.5931348800659</v>
+        <v>11.5931367874146</v>
       </c>
       <c r="H40" t="n">
         <v>308414</v>
@@ -1558,7 +1558,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G41" t="n">
-        <v>11.7391920089722</v>
+        <v>11.7391910552979</v>
       </c>
       <c r="H41" t="n">
         <v>357918</v>
@@ -1587,7 +1587,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G42" t="n">
-        <v>11.693549156189</v>
+        <v>11.6935482025146</v>
       </c>
       <c r="H42" t="n">
         <v>335537</v>
@@ -1616,7 +1616,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G43" t="n">
-        <v>12.0221748352051</v>
+        <v>12.0221757888794</v>
       </c>
       <c r="H43" t="n">
         <v>526993</v>
@@ -1645,7 +1645,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G44" t="n">
-        <v>12.0586891174316</v>
+        <v>12.058687210083</v>
       </c>
       <c r="H44" t="n">
         <v>400260</v>
@@ -1674,7 +1674,7 @@
         <v>13.25</v>
       </c>
       <c r="G45" t="n">
-        <v>12.0952033996582</v>
+        <v>12.0952014923096</v>
       </c>
       <c r="H45" t="n">
         <v>186042</v>
@@ -1703,7 +1703,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G46" t="n">
-        <v>12.1225872039795</v>
+        <v>12.1225852966309</v>
       </c>
       <c r="H46" t="n">
         <v>258141</v>
@@ -1732,7 +1732,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G47" t="n">
-        <v>12.067816734314</v>
+        <v>12.0678157806396</v>
       </c>
       <c r="H47" t="n">
         <v>186390</v>
@@ -1761,7 +1761,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G48" t="n">
-        <v>11.7848329544067</v>
+        <v>11.7848339080811</v>
       </c>
       <c r="H48" t="n">
         <v>164283</v>
@@ -1819,7 +1819,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G50" t="n">
-        <v>11.666163444519</v>
+        <v>11.6661624908447</v>
       </c>
       <c r="H50" t="n">
         <v>214005</v>
@@ -1935,7 +1935,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.9126319885254</v>
+        <v>11.9126329421997</v>
       </c>
       <c r="H54" t="n">
         <v>101621</v>
@@ -1993,7 +1993,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G56" t="n">
-        <v>11.9674015045166</v>
+        <v>11.9674034118652</v>
       </c>
       <c r="H56" t="n">
         <v>535788</v>
@@ -2051,7 +2051,7 @@
         <v>13</v>
       </c>
       <c r="G58" t="n">
-        <v>11.8669900894165</v>
+        <v>11.8669881820679</v>
       </c>
       <c r="H58" t="n">
         <v>429665</v>
@@ -2080,7 +2080,7 @@
         <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>11.8669900894165</v>
+        <v>11.8669881820679</v>
       </c>
       <c r="H59" t="n">
         <v>177405</v>
@@ -2109,7 +2109,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>11.8122186660767</v>
+        <v>11.8122205734253</v>
       </c>
       <c r="H60" t="n">
         <v>164695</v>
@@ -2138,7 +2138,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G61" t="n">
-        <v>11.6296501159668</v>
+        <v>11.6296491622925</v>
       </c>
       <c r="H61" t="n">
         <v>263315</v>
@@ -2167,7 +2167,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G62" t="n">
-        <v>11.9765310287476</v>
+        <v>11.9765329360962</v>
       </c>
       <c r="H62" t="n">
         <v>293041</v>
@@ -2196,7 +2196,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G63" t="n">
-        <v>11.7300643920898</v>
+        <v>11.7300624847412</v>
       </c>
       <c r="H63" t="n">
         <v>194755</v>
@@ -2225,7 +2225,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G64" t="n">
-        <v>11.8030920028687</v>
+        <v>11.80309009552</v>
       </c>
       <c r="H64" t="n">
         <v>219418</v>
@@ -2254,7 +2254,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G65" t="n">
-        <v>11.8396034240723</v>
+        <v>11.8396043777466</v>
       </c>
       <c r="H65" t="n">
         <v>200394</v>
@@ -2283,7 +2283,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G66" t="n">
-        <v>11.2553834915161</v>
+        <v>11.2553844451904</v>
       </c>
       <c r="H66" t="n">
         <v>380459</v>
@@ -2312,7 +2312,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5748796463013</v>
+        <v>11.5748805999756</v>
       </c>
       <c r="H67" t="n">
         <v>141133</v>
@@ -2341,7 +2341,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G68" t="n">
-        <v>11.3466691970825</v>
+        <v>11.3466682434082</v>
       </c>
       <c r="H68" t="n">
         <v>249644</v>
@@ -2370,7 +2370,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G69" t="n">
-        <v>11.5657520294189</v>
+        <v>11.5657510757446</v>
       </c>
       <c r="H69" t="n">
         <v>187170</v>
@@ -2399,7 +2399,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G70" t="n">
-        <v>11.6752920150757</v>
+        <v>11.67529296875</v>
       </c>
       <c r="H70" t="n">
         <v>201666</v>
@@ -2428,7 +2428,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5840082168579</v>
+        <v>11.5840072631836</v>
       </c>
       <c r="H71" t="n">
         <v>177503</v>
@@ -2457,7 +2457,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>11.7300643920898</v>
+        <v>11.7300624847412</v>
       </c>
       <c r="H72" t="n">
         <v>177567</v>
@@ -2515,7 +2515,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>11.4744672775269</v>
+        <v>11.4744653701782</v>
       </c>
       <c r="H74" t="n">
         <v>178617</v>
@@ -2544,7 +2544,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>11.5931348800659</v>
+        <v>11.5931367874146</v>
       </c>
       <c r="H75" t="n">
         <v>265483</v>
@@ -2602,7 +2602,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G77" t="n">
-        <v>11.7483196258545</v>
+        <v>11.7483205795288</v>
       </c>
       <c r="H77" t="n">
         <v>121742</v>
@@ -2631,7 +2631,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G78" t="n">
-        <v>11.5840082168579</v>
+        <v>11.5840072631836</v>
       </c>
       <c r="H78" t="n">
         <v>129150</v>
@@ -2689,7 +2689,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G80" t="n">
-        <v>11.6296501159668</v>
+        <v>11.6296491622925</v>
       </c>
       <c r="H80" t="n">
         <v>107649</v>
@@ -2718,7 +2718,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G81" t="n">
-        <v>11.5109815597534</v>
+        <v>11.5109806060791</v>
       </c>
       <c r="H81" t="n">
         <v>262188</v>
@@ -2747,7 +2747,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G82" t="n">
-        <v>11.5566215515137</v>
+        <v>11.5566234588623</v>
       </c>
       <c r="H82" t="n">
         <v>136282</v>
@@ -2776,7 +2776,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>11.5474939346313</v>
+        <v>11.547492980957</v>
       </c>
       <c r="H83" t="n">
         <v>94718</v>
@@ -2805,7 +2805,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G84" t="n">
-        <v>11.4744672775269</v>
+        <v>11.4744653701782</v>
       </c>
       <c r="H84" t="n">
         <v>49182</v>
@@ -2834,7 +2834,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G85" t="n">
-        <v>11.3010263442993</v>
+        <v>11.3010272979736</v>
       </c>
       <c r="H85" t="n">
         <v>102382</v>
@@ -2863,7 +2863,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0454292297363</v>
+        <v>11.0454301834106</v>
       </c>
       <c r="H86" t="n">
         <v>170860</v>
@@ -2921,7 +2921,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G88" t="n">
-        <v>11.282769203186</v>
+        <v>11.2827682495117</v>
       </c>
       <c r="H88" t="n">
         <v>99317</v>
@@ -2950,7 +2950,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G89" t="n">
-        <v>11.0728149414062</v>
+        <v>11.0728158950806</v>
       </c>
       <c r="H89" t="n">
         <v>151720</v>
@@ -2979,7 +2979,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G90" t="n">
-        <v>11.0363025665283</v>
+        <v>11.0362997055054</v>
       </c>
       <c r="H90" t="n">
         <v>116625</v>
@@ -3008,7 +3008,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G91" t="n">
-        <v>10.9632740020752</v>
+        <v>10.9632730484009</v>
       </c>
       <c r="H91" t="n">
         <v>166945</v>
@@ -3037,7 +3037,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G92" t="n">
-        <v>11.063684463501</v>
+        <v>11.0636854171753</v>
       </c>
       <c r="H92" t="n">
         <v>202236</v>
@@ -3066,7 +3066,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G93" t="n">
-        <v>10.9997882843018</v>
+        <v>10.9997892379761</v>
       </c>
       <c r="H93" t="n">
         <v>366237</v>
@@ -3124,7 +3124,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G95" t="n">
-        <v>11.8578624725342</v>
+        <v>11.8578605651855</v>
       </c>
       <c r="H95" t="n">
         <v>531881</v>
@@ -3182,7 +3182,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G97" t="n">
-        <v>12.2047433853149</v>
+        <v>12.2047424316406</v>
       </c>
       <c r="H97" t="n">
         <v>500870</v>
@@ -3240,7 +3240,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>12.6429090499878</v>
+        <v>12.6429100036621</v>
       </c>
       <c r="H99" t="n">
         <v>465558</v>
@@ -3269,7 +3269,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G100" t="n">
-        <v>12.7632293701172</v>
+        <v>12.7632303237915</v>
       </c>
       <c r="H100" t="n">
         <v>316375</v>
@@ -3298,7 +3298,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G101" t="n">
-        <v>12.9298276901245</v>
+        <v>12.9298267364502</v>
       </c>
       <c r="H101" t="n">
         <v>342008</v>
@@ -3327,7 +3327,7 @@
         <v>14.25</v>
       </c>
       <c r="G102" t="n">
-        <v>13.1889781951904</v>
+        <v>13.1889791488647</v>
       </c>
       <c r="H102" t="n">
         <v>519467</v>
@@ -3356,7 +3356,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G103" t="n">
-        <v>13.1149368286133</v>
+        <v>13.1149349212646</v>
       </c>
       <c r="H103" t="n">
         <v>303573</v>
@@ -3385,7 +3385,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G104" t="n">
-        <v>13.2630233764648</v>
+        <v>13.2630214691162</v>
       </c>
       <c r="H104" t="n">
         <v>387642</v>
@@ -3414,7 +3414,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>13.2815341949463</v>
+        <v>13.281533241272</v>
       </c>
       <c r="H105" t="n">
         <v>298592</v>
@@ -3443,7 +3443,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G106" t="n">
-        <v>13.2537670135498</v>
+        <v>13.2537660598755</v>
       </c>
       <c r="H106" t="n">
         <v>209937</v>
@@ -3530,7 +3530,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G109" t="n">
-        <v>13.2074909210205</v>
+        <v>13.2074899673462</v>
       </c>
       <c r="H109" t="n">
         <v>274408</v>
@@ -3559,7 +3559,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G110" t="n">
-        <v>13.0964241027832</v>
+        <v>13.0964231491089</v>
       </c>
       <c r="H110" t="n">
         <v>201773</v>
@@ -3588,7 +3588,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G111" t="n">
-        <v>13.3648319244385</v>
+        <v>13.3648309707642</v>
       </c>
       <c r="H111" t="n">
         <v>412951</v>
@@ -3617,7 +3617,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G112" t="n">
-        <v>13.7350492477417</v>
+        <v>13.735050201416</v>
       </c>
       <c r="H112" t="n">
         <v>497596</v>
@@ -3675,7 +3675,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>13.3278102874756</v>
+        <v>13.3278112411499</v>
       </c>
       <c r="H114" t="n">
         <v>391995</v>
@@ -3704,7 +3704,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G115" t="n">
-        <v>12.9946146011353</v>
+        <v>12.9946155548096</v>
       </c>
       <c r="H115" t="n">
         <v>351176</v>
@@ -3733,7 +3733,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G116" t="n">
-        <v>12.8650388717651</v>
+        <v>12.8650398254395</v>
       </c>
       <c r="H116" t="n">
         <v>412031</v>
@@ -3820,7 +3820,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G119" t="n">
-        <v>13.2722778320312</v>
+        <v>13.2722768783569</v>
       </c>
       <c r="H119" t="n">
         <v>463830</v>
@@ -3849,7 +3849,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G120" t="n">
-        <v>13.3648319244385</v>
+        <v>13.3648309707642</v>
       </c>
       <c r="H120" t="n">
         <v>535733</v>
@@ -3878,7 +3878,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G121" t="n">
-        <v>13.3833427429199</v>
+        <v>13.3833436965942</v>
       </c>
       <c r="H121" t="n">
         <v>236774</v>
@@ -3907,7 +3907,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>13.3740863800049</v>
+        <v>13.3740873336792</v>
       </c>
       <c r="H122" t="n">
         <v>323224</v>
@@ -3936,7 +3936,7 @@
         <v>14.75</v>
       </c>
       <c r="G123" t="n">
-        <v>13.6517496109009</v>
+        <v>13.6517505645752</v>
       </c>
       <c r="H123" t="n">
         <v>298922</v>
@@ -3965,7 +3965,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G124" t="n">
-        <v>13.0594034194946</v>
+        <v>13.0594024658203</v>
       </c>
       <c r="H124" t="n">
         <v>366553</v>
@@ -3994,7 +3994,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G125" t="n">
-        <v>11.9580087661743</v>
+        <v>11.9580068588257</v>
       </c>
       <c r="H125" t="n">
         <v>847251</v>
@@ -4023,7 +4023,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>12.2541809082031</v>
+        <v>12.2541818618774</v>
       </c>
       <c r="H126" t="n">
         <v>412342</v>
@@ -4081,7 +4081,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G128" t="n">
-        <v>13.013126373291</v>
+        <v>13.0131254196167</v>
       </c>
       <c r="H128" t="n">
         <v>241618</v>
@@ -4110,7 +4110,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G129" t="n">
-        <v>12.9946146011353</v>
+        <v>12.9946155548096</v>
       </c>
       <c r="H129" t="n">
         <v>189841</v>
@@ -4168,7 +4168,7 @@
         <v>13.5</v>
       </c>
       <c r="G131" t="n">
-        <v>12.4948215484619</v>
+        <v>12.4948225021362</v>
       </c>
       <c r="H131" t="n">
         <v>145285</v>
@@ -4197,7 +4197,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G132" t="n">
-        <v>12.3189697265625</v>
+        <v>12.3189706802368</v>
       </c>
       <c r="H132" t="n">
         <v>271999</v>
@@ -4226,7 +4226,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G133" t="n">
-        <v>12.4577989578247</v>
+        <v>12.457799911499</v>
       </c>
       <c r="H133" t="n">
         <v>244689</v>
@@ -4342,7 +4342,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>13.0501489639282</v>
+        <v>13.0501480102539</v>
       </c>
       <c r="H137" t="n">
         <v>364476</v>
@@ -4371,7 +4371,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G138" t="n">
-        <v>13.3000431060791</v>
+        <v>13.3000440597534</v>
       </c>
       <c r="H138" t="n">
         <v>129515</v>
@@ -4400,7 +4400,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G139" t="n">
-        <v>13.0501489639282</v>
+        <v>13.0501480102539</v>
       </c>
       <c r="H139" t="n">
         <v>475215</v>
@@ -4429,7 +4429,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G140" t="n">
-        <v>13.1056804656982</v>
+        <v>13.1056795120239</v>
       </c>
       <c r="H140" t="n">
         <v>206171</v>
@@ -4487,7 +4487,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G142" t="n">
-        <v>13.2537670135498</v>
+        <v>13.2537660598755</v>
       </c>
       <c r="H142" t="n">
         <v>80342</v>
@@ -4545,7 +4545,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G144" t="n">
-        <v>13.2167463302612</v>
+        <v>13.2167453765869</v>
       </c>
       <c r="H144" t="n">
         <v>65982</v>
@@ -4574,7 +4574,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>13.0964241027832</v>
+        <v>13.0964231491089</v>
       </c>
       <c r="H145" t="n">
         <v>135773</v>
@@ -4661,7 +4661,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G148" t="n">
-        <v>13.4018545150757</v>
+        <v>13.4018526077271</v>
       </c>
       <c r="H148" t="n">
         <v>258982</v>
@@ -4690,7 +4690,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G149" t="n">
-        <v>13.4018545150757</v>
+        <v>13.4018526077271</v>
       </c>
       <c r="H149" t="n">
         <v>155777</v>
@@ -4719,7 +4719,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G150" t="n">
-        <v>13.4944067001343</v>
+        <v>13.4944076538086</v>
       </c>
       <c r="H150" t="n">
         <v>542580</v>
@@ -4777,7 +4777,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G152" t="n">
-        <v>13.1149368286133</v>
+        <v>13.1149349212646</v>
       </c>
       <c r="H152" t="n">
         <v>153654</v>
@@ -4806,7 +4806,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G153" t="n">
-        <v>13.2074909210205</v>
+        <v>13.2074899673462</v>
       </c>
       <c r="H153" t="n">
         <v>145274</v>
@@ -4893,7 +4893,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G156" t="n">
-        <v>13.7998361587524</v>
+        <v>13.7998371124268</v>
       </c>
       <c r="H156" t="n">
         <v>200300</v>
@@ -4922,7 +4922,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G157" t="n">
-        <v>13.9386692047119</v>
+        <v>13.9386682510376</v>
       </c>
       <c r="H157" t="n">
         <v>349471</v>
@@ -5009,7 +5009,7 @@
         <v>15</v>
       </c>
       <c r="G160" t="n">
-        <v>13.8831348419189</v>
+        <v>13.8831367492676</v>
       </c>
       <c r="H160" t="n">
         <v>188118</v>
@@ -5038,7 +5038,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G161" t="n">
-        <v>13.7998361587524</v>
+        <v>13.7998371124268</v>
       </c>
       <c r="H161" t="n">
         <v>170685</v>
@@ -5067,7 +5067,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G162" t="n">
-        <v>14.1052665710449</v>
+        <v>14.1052656173706</v>
       </c>
       <c r="H162" t="n">
         <v>276372</v>
@@ -5096,7 +5096,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G163" t="n">
-        <v>14.3551626205444</v>
+        <v>14.3551616668701</v>
       </c>
       <c r="H163" t="n">
         <v>587089</v>
@@ -5125,7 +5125,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G164" t="n">
-        <v>14.4754848480225</v>
+        <v>14.4754829406738</v>
       </c>
       <c r="H164" t="n">
         <v>391413</v>
@@ -5154,7 +5154,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G165" t="n">
-        <v>14.4939937591553</v>
+        <v>14.4939918518066</v>
       </c>
       <c r="H165" t="n">
         <v>535227</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>14.623571395874</v>
+        <v>14.6235685348511</v>
       </c>
       <c r="H166" t="n">
         <v>501267</v>
@@ -5328,7 +5328,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6698484420776</v>
+        <v>14.669846534729</v>
       </c>
       <c r="H171" t="n">
         <v>245734</v>
@@ -5357,7 +5357,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G172" t="n">
-        <v>14.4754848480225</v>
+        <v>14.4754829406738</v>
       </c>
       <c r="H172" t="n">
         <v>183802</v>
@@ -5502,7 +5502,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G177" t="n">
-        <v>14.2533512115479</v>
+        <v>14.2533521652222</v>
       </c>
       <c r="H177" t="n">
         <v>312051</v>
@@ -5531,7 +5531,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G178" t="n">
-        <v>14.1422872543335</v>
+        <v>14.1422863006592</v>
       </c>
       <c r="H178" t="n">
         <v>139080</v>
@@ -5589,7 +5589,7 @@
         <v>15</v>
       </c>
       <c r="G180" t="n">
-        <v>13.8831348419189</v>
+        <v>13.8831367492676</v>
       </c>
       <c r="H180" t="n">
         <v>152895</v>
@@ -5618,7 +5618,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G181" t="n">
-        <v>13.9201583862305</v>
+        <v>13.9201555252075</v>
       </c>
       <c r="H181" t="n">
         <v>96895</v>
@@ -5647,7 +5647,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G182" t="n">
-        <v>14.0404767990112</v>
+        <v>14.0404796600342</v>
       </c>
       <c r="H182" t="n">
         <v>181764</v>
@@ -5676,7 +5676,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G183" t="n">
-        <v>13.8461141586304</v>
+        <v>13.8461132049561</v>
       </c>
       <c r="H183" t="n">
         <v>191170</v>
@@ -5705,7 +5705,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G184" t="n">
-        <v>13.8738803863525</v>
+        <v>13.8738813400269</v>
       </c>
       <c r="H184" t="n">
         <v>190113</v>
@@ -5734,7 +5734,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G185" t="n">
-        <v>13.8923892974854</v>
+        <v>13.892391204834</v>
       </c>
       <c r="H185" t="n">
         <v>260510</v>
@@ -5763,7 +5763,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G186" t="n">
-        <v>13.9571800231934</v>
+        <v>13.9571781158447</v>
       </c>
       <c r="H186" t="n">
         <v>112338</v>
@@ -5792,7 +5792,7 @@
         <v>15.5</v>
       </c>
       <c r="G187" t="n">
-        <v>14.3459053039551</v>
+        <v>14.3459072113037</v>
       </c>
       <c r="H187" t="n">
         <v>347953</v>
@@ -5821,7 +5821,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G188" t="n">
-        <v>14.0960102081299</v>
+        <v>14.0960092544556</v>
       </c>
       <c r="H188" t="n">
         <v>147425</v>
@@ -5850,7 +5850,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G189" t="n">
-        <v>13.9571800231934</v>
+        <v>13.9571781158447</v>
       </c>
       <c r="H189" t="n">
         <v>104787</v>
@@ -5879,7 +5879,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G190" t="n">
-        <v>13.8276023864746</v>
+        <v>13.8276042938232</v>
       </c>
       <c r="H190" t="n">
         <v>226301</v>
@@ -5908,7 +5908,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G191" t="n">
-        <v>14.1515426635742</v>
+        <v>14.1515436172485</v>
       </c>
       <c r="H191" t="n">
         <v>153043</v>
@@ -5937,7 +5937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G192" t="n">
-        <v>14.1607990264893</v>
+        <v>14.1607999801636</v>
       </c>
       <c r="H192" t="n">
         <v>390055</v>
@@ -5966,7 +5966,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G193" t="n">
-        <v>14.0404767990112</v>
+        <v>14.0404796600342</v>
       </c>
       <c r="H193" t="n">
         <v>254654</v>
@@ -5995,7 +5995,7 @@
         <v>15.5</v>
       </c>
       <c r="G194" t="n">
-        <v>14.3459053039551</v>
+        <v>14.3459072113037</v>
       </c>
       <c r="H194" t="n">
         <v>311816</v>
@@ -6024,7 +6024,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G195" t="n">
-        <v>14.4754848480225</v>
+        <v>14.4754829406738</v>
       </c>
       <c r="H195" t="n">
         <v>186282</v>
@@ -6053,7 +6053,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G196" t="n">
-        <v>14.3921842575073</v>
+        <v>14.3921852111816</v>
       </c>
       <c r="H196" t="n">
         <v>333848</v>
@@ -6082,7 +6082,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G197" t="n">
-        <v>14.2440958023071</v>
+        <v>14.2440967559814</v>
       </c>
       <c r="H197" t="n">
         <v>218249</v>
@@ -6111,7 +6111,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>14.1885633468628</v>
+        <v>14.1885652542114</v>
       </c>
       <c r="H198" t="n">
         <v>129437</v>
@@ -6140,7 +6140,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G199" t="n">
-        <v>14.2626085281372</v>
+        <v>14.2626066207886</v>
       </c>
       <c r="H199" t="n">
         <v>71306</v>
@@ -6198,7 +6198,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G201" t="n">
-        <v>14.0774993896484</v>
+        <v>14.0775003433228</v>
       </c>
       <c r="H201" t="n">
         <v>189443</v>
@@ -6256,7 +6256,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G203" t="n">
-        <v>14.1885633468628</v>
+        <v>14.1885652542114</v>
       </c>
       <c r="H203" t="n">
         <v>102035</v>
@@ -6285,7 +6285,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G204" t="n">
-        <v>14.3181419372559</v>
+        <v>14.3181409835815</v>
       </c>
       <c r="H204" t="n">
         <v>115779</v>
@@ -6343,7 +6343,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G206" t="n">
-        <v>14.0960102081299</v>
+        <v>14.0960092544556</v>
       </c>
       <c r="H206" t="n">
         <v>98359</v>
@@ -6401,7 +6401,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>13.9294137954712</v>
+        <v>13.9294128417969</v>
       </c>
       <c r="H208" t="n">
         <v>113474</v>
@@ -6430,7 +6430,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G209" t="n">
-        <v>13.8090934753418</v>
+        <v>13.8090925216675</v>
       </c>
       <c r="H209" t="n">
         <v>116682</v>
@@ -6459,7 +6459,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G210" t="n">
-        <v>13.5777082443237</v>
+        <v>13.5777063369751</v>
       </c>
       <c r="H210" t="n">
         <v>197027</v>
@@ -6488,7 +6488,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G211" t="n">
-        <v>13.7350492477417</v>
+        <v>13.735050201416</v>
       </c>
       <c r="H211" t="n">
         <v>124521</v>
@@ -6517,7 +6517,7 @@
         <v>14.75</v>
       </c>
       <c r="G212" t="n">
-        <v>13.6517496109009</v>
+        <v>13.6517505645752</v>
       </c>
       <c r="H212" t="n">
         <v>121463</v>
@@ -6575,7 +6575,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G214" t="n">
-        <v>13.5314273834229</v>
+        <v>13.5314283370972</v>
       </c>
       <c r="H214" t="n">
         <v>121908</v>
@@ -6604,7 +6604,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.2722778320312</v>
+        <v>13.2722768783569</v>
       </c>
       <c r="H215" t="n">
         <v>90367</v>
@@ -6633,7 +6633,7 @@
         <v>14.25</v>
       </c>
       <c r="G216" t="n">
-        <v>13.1889781951904</v>
+        <v>13.1889791488647</v>
       </c>
       <c r="H216" t="n">
         <v>274207</v>
@@ -6691,7 +6691,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>13.0964241027832</v>
+        <v>13.0964231491089</v>
       </c>
       <c r="H218" t="n">
         <v>179745</v>
@@ -6720,7 +6720,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>13.2815341949463</v>
+        <v>13.281533241272</v>
       </c>
       <c r="H219" t="n">
         <v>98510</v>
@@ -6749,7 +6749,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G220" t="n">
-        <v>13.2167463302612</v>
+        <v>13.2167453765869</v>
       </c>
       <c r="H220" t="n">
         <v>60673</v>
@@ -6778,7 +6778,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G221" t="n">
-        <v>13.0501489639282</v>
+        <v>13.0501480102539</v>
       </c>
       <c r="H221" t="n">
         <v>228920</v>
@@ -6807,7 +6807,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G222" t="n">
-        <v>13.6702613830566</v>
+        <v>13.6702604293823</v>
       </c>
       <c r="H222" t="n">
         <v>309835</v>
@@ -6865,7 +6865,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>13.5962171554565</v>
+        <v>13.5962181091309</v>
       </c>
       <c r="H224" t="n">
         <v>150782</v>
@@ -6894,7 +6894,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G225" t="n">
-        <v>13.5129194259644</v>
+        <v>13.5129175186157</v>
       </c>
       <c r="H225" t="n">
         <v>112869</v>
@@ -6923,7 +6923,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>13.5129194259644</v>
+        <v>13.5129175186157</v>
       </c>
       <c r="H226" t="n">
         <v>74211</v>
@@ -6981,7 +6981,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G228" t="n">
-        <v>13.6239852905273</v>
+        <v>13.623984336853</v>
       </c>
       <c r="H228" t="n">
         <v>103850</v>
@@ -7010,7 +7010,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G229" t="n">
-        <v>13.5962171554565</v>
+        <v>13.5962181091309</v>
       </c>
       <c r="H229" t="n">
         <v>84362</v>
@@ -7039,7 +7039,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G230" t="n">
-        <v>13.7165365219116</v>
+        <v>13.7165374755859</v>
       </c>
       <c r="H230" t="n">
         <v>113257</v>
@@ -7126,7 +7126,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G233" t="n">
-        <v>14.2348413467407</v>
+        <v>14.2348432540894</v>
       </c>
       <c r="H233" t="n">
         <v>164593</v>
@@ -7155,7 +7155,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G234" t="n">
-        <v>14.3551626205444</v>
+        <v>14.3551616668701</v>
       </c>
       <c r="H234" t="n">
         <v>394911</v>
@@ -7242,7 +7242,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G237" t="n">
-        <v>13.9386692047119</v>
+        <v>13.9386682510376</v>
       </c>
       <c r="H237" t="n">
         <v>142842</v>
@@ -7329,7 +7329,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G240" t="n">
-        <v>14.2348413467407</v>
+        <v>14.2348432540894</v>
       </c>
       <c r="H240" t="n">
         <v>199441</v>
@@ -7358,7 +7358,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G241" t="n">
-        <v>14.3273973464966</v>
+        <v>14.3273954391479</v>
       </c>
       <c r="H241" t="n">
         <v>196309</v>
@@ -7416,7 +7416,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G243" t="n">
-        <v>14.2070760726929</v>
+        <v>14.2070751190186</v>
       </c>
       <c r="H243" t="n">
         <v>187792</v>
@@ -7445,7 +7445,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G244" t="n">
-        <v>14.2533512115479</v>
+        <v>14.2533521652222</v>
       </c>
       <c r="H244" t="n">
         <v>119643</v>
@@ -7474,7 +7474,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G245" t="n">
-        <v>14.2996292114258</v>
+        <v>14.2996311187744</v>
       </c>
       <c r="H245" t="n">
         <v>293973</v>
@@ -7503,7 +7503,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>14.2533512115479</v>
+        <v>14.2533521652222</v>
       </c>
       <c r="H246" t="n">
         <v>116899</v>
@@ -7532,7 +7532,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G247" t="n">
-        <v>14.2348413467407</v>
+        <v>14.2348432540894</v>
       </c>
       <c r="H247" t="n">
         <v>79002</v>
@@ -7561,7 +7561,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>14.4384622573853</v>
+        <v>14.4384632110596</v>
       </c>
       <c r="H248" t="n">
         <v>194905</v>
@@ -7590,7 +7590,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G249" t="n">
-        <v>14.2163305282593</v>
+        <v>14.216329574585</v>
       </c>
       <c r="H249" t="n">
         <v>105554</v>
@@ -7619,7 +7619,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G250" t="n">
-        <v>14.1978206634521</v>
+        <v>14.1978197097778</v>
       </c>
       <c r="H250" t="n">
         <v>78711</v>
@@ -7648,7 +7648,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G251" t="n">
-        <v>14.2163305282593</v>
+        <v>14.216329574585</v>
       </c>
       <c r="H251" t="n">
         <v>123421</v>
@@ -7677,7 +7677,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G252" t="n">
-        <v>14.1793088912964</v>
+        <v>14.1793098449707</v>
       </c>
       <c r="H252" t="n">
         <v>214272</v>
@@ -7735,7 +7735,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G254" t="n">
-        <v>14.0404767990112</v>
+        <v>14.0404796600342</v>
       </c>
       <c r="H254" t="n">
         <v>152510</v>
@@ -7764,7 +7764,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G255" t="n">
-        <v>14.5402688980103</v>
+        <v>14.5402698516846</v>
       </c>
       <c r="H255" t="n">
         <v>225170</v>
@@ -7822,7 +7822,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G257" t="n">
-        <v>14.3921842575073</v>
+        <v>14.3921852111816</v>
       </c>
       <c r="H257" t="n">
         <v>50692</v>
@@ -7880,7 +7880,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G259" t="n">
-        <v>14.8642091751099</v>
+        <v>14.8642110824585</v>
       </c>
       <c r="H259" t="n">
         <v>272984</v>
@@ -7909,7 +7909,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G260" t="n">
-        <v>14.8457021713257</v>
+        <v>14.8457012176514</v>
       </c>
       <c r="H260" t="n">
         <v>222768</v>
@@ -7938,7 +7938,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G261" t="n">
-        <v>14.8271903991699</v>
+        <v>14.8271884918213</v>
       </c>
       <c r="H261" t="n">
         <v>142340</v>
@@ -7967,7 +7967,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G262" t="n">
-        <v>14.8642091751099</v>
+        <v>14.8642110824585</v>
       </c>
       <c r="H262" t="n">
         <v>115229</v>
@@ -7996,7 +7996,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>14.9012308120728</v>
+        <v>14.9012317657471</v>
       </c>
       <c r="H263" t="n">
         <v>237810</v>
@@ -8025,7 +8025,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G264" t="n">
-        <v>14.8642091751099</v>
+        <v>14.8642110824585</v>
       </c>
       <c r="H264" t="n">
         <v>194714</v>
@@ -8054,7 +8054,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G265" t="n">
-        <v>14.9382524490356</v>
+        <v>14.9382543563843</v>
       </c>
       <c r="H265" t="n">
         <v>84054</v>
@@ -8083,7 +8083,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G266" t="n">
-        <v>15.0678310394287</v>
+        <v>15.0678300857544</v>
       </c>
       <c r="H266" t="n">
         <v>183182</v>
@@ -8141,7 +8141,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>15.3640041351318</v>
+        <v>15.3640060424805</v>
       </c>
       <c r="H268" t="n">
         <v>184706</v>
@@ -8170,7 +8170,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>15.4287919998169</v>
+        <v>15.4287910461426</v>
       </c>
       <c r="H269" t="n">
         <v>249349</v>
@@ -8199,7 +8199,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G270" t="n">
-        <v>15.4010229110718</v>
+        <v>15.4010248184204</v>
       </c>
       <c r="H270" t="n">
         <v>214222</v>
@@ -8257,7 +8257,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G272" t="n">
-        <v>15.6786890029907</v>
+        <v>15.678689956665</v>
       </c>
       <c r="H272" t="n">
         <v>142263</v>
@@ -8286,7 +8286,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G273" t="n">
-        <v>15.8545398712158</v>
+        <v>15.8545389175415</v>
       </c>
       <c r="H273" t="n">
         <v>485866</v>
@@ -8344,7 +8344,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G275" t="n">
-        <v>16.5764636993408</v>
+        <v>16.5764617919922</v>
       </c>
       <c r="H275" t="n">
         <v>359618</v>
@@ -8373,7 +8373,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G276" t="n">
-        <v>16.4006099700928</v>
+        <v>16.4006118774414</v>
       </c>
       <c r="H276" t="n">
         <v>344927</v>
@@ -8402,7 +8402,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G277" t="n">
-        <v>16.3080615997314</v>
+        <v>16.3080577850342</v>
       </c>
       <c r="H277" t="n">
         <v>141198</v>
@@ -8518,7 +8518,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G281" t="n">
-        <v>16.3913555145264</v>
+        <v>16.391357421875</v>
       </c>
       <c r="H281" t="n">
         <v>242348</v>
@@ -8547,7 +8547,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G282" t="n">
-        <v>16.8541278839111</v>
+        <v>16.8541259765625</v>
       </c>
       <c r="H282" t="n">
         <v>534383</v>
@@ -8634,7 +8634,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="n">
-        <v>17.2983894348145</v>
+        <v>17.2983856201172</v>
       </c>
       <c r="H285" t="n">
         <v>332215</v>
@@ -8663,7 +8663,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G286" t="n">
-        <v>17.1595554351807</v>
+        <v>17.1595573425293</v>
       </c>
       <c r="H286" t="n">
         <v>282752</v>
@@ -8692,7 +8692,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G287" t="n">
-        <v>17.1132793426514</v>
+        <v>17.1132774353027</v>
       </c>
       <c r="H287" t="n">
         <v>193817</v>
@@ -8721,7 +8721,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>17.2150897979736</v>
+        <v>17.215087890625</v>
       </c>
       <c r="H288" t="n">
         <v>470418</v>
@@ -8808,7 +8808,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G291" t="n">
-        <v>17.5390281677246</v>
+        <v>17.5390300750732</v>
       </c>
       <c r="H291" t="n">
         <v>307454</v>
@@ -8837,7 +8837,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G292" t="n">
-        <v>17.548282623291</v>
+        <v>17.5482845306396</v>
       </c>
       <c r="H292" t="n">
         <v>166524</v>
@@ -8866,7 +8866,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G293" t="n">
-        <v>17.5760478973389</v>
+        <v>17.5760498046875</v>
       </c>
       <c r="H293" t="n">
         <v>113751</v>
@@ -8924,7 +8924,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G295" t="n">
-        <v>17.5390281677246</v>
+        <v>17.5390300750732</v>
       </c>
       <c r="H295" t="n">
         <v>200776</v>
@@ -8953,7 +8953,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G296" t="n">
-        <v>17.4187088012695</v>
+        <v>17.4187068939209</v>
       </c>
       <c r="H296" t="n">
         <v>153749</v>
@@ -8982,7 +8982,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4464721679688</v>
+        <v>17.4464740753174</v>
       </c>
       <c r="H297" t="n">
         <v>178799</v>
@@ -9011,7 +9011,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G298" t="n">
-        <v>17.6038112640381</v>
+        <v>17.6038131713867</v>
       </c>
       <c r="H298" t="n">
         <v>214811</v>
@@ -9040,7 +9040,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G299" t="n">
-        <v>17.7889232635498</v>
+        <v>17.7889213562012</v>
       </c>
       <c r="H299" t="n">
         <v>219079</v>
@@ -9069,7 +9069,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G300" t="n">
-        <v>17.7889232635498</v>
+        <v>17.7889213562012</v>
       </c>
       <c r="H300" t="n">
         <v>155757</v>
@@ -9098,7 +9098,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G301" t="n">
-        <v>17.8351993560791</v>
+        <v>17.8352031707764</v>
       </c>
       <c r="H301" t="n">
         <v>154759</v>
@@ -9127,7 +9127,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G302" t="n">
-        <v>17.7241382598877</v>
+        <v>17.7241363525391</v>
       </c>
       <c r="H302" t="n">
         <v>129579</v>
@@ -9214,7 +9214,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G305" t="n">
-        <v>17.8537120819092</v>
+        <v>17.8537139892578</v>
       </c>
       <c r="H305" t="n">
         <v>195960</v>
@@ -9301,7 +9301,7 @@
         <v>20</v>
       </c>
       <c r="G308" t="n">
-        <v>18.5108451843262</v>
+        <v>18.5108470916748</v>
       </c>
       <c r="H308" t="n">
         <v>345979</v>
@@ -9330,7 +9330,7 @@
         <v>20.0100002288818</v>
       </c>
       <c r="G309" t="n">
-        <v>18.5201015472412</v>
+        <v>18.5201034545898</v>
       </c>
       <c r="H309" t="n">
         <v>407657</v>
@@ -9359,7 +9359,7 @@
         <v>20</v>
       </c>
       <c r="G310" t="n">
-        <v>18.5108451843262</v>
+        <v>18.5108470916748</v>
       </c>
       <c r="H310" t="n">
         <v>559522</v>
@@ -9388,7 +9388,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G311" t="n">
-        <v>18.7700042724609</v>
+        <v>18.769998550415</v>
       </c>
       <c r="H311" t="n">
         <v>205735</v>
@@ -9446,7 +9446,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.1587295532227</v>
+        <v>19.1587257385254</v>
       </c>
       <c r="H313" t="n">
         <v>422235</v>
@@ -9475,7 +9475,7 @@
         <v>21</v>
       </c>
       <c r="G314" t="n">
-        <v>19.4363918304443</v>
+        <v>19.4363880157471</v>
       </c>
       <c r="H314" t="n">
         <v>348430</v>
@@ -9504,7 +9504,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G315" t="n">
-        <v>19.5659637451172</v>
+        <v>19.5659656524658</v>
       </c>
       <c r="H315" t="n">
         <v>341898</v>
@@ -9533,7 +9533,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>19.9917163848877</v>
+        <v>19.9917144775391</v>
       </c>
       <c r="H316" t="n">
         <v>349110</v>
@@ -9591,7 +9591,7 @@
         <v>22.25</v>
       </c>
       <c r="G318" t="n">
-        <v>20.5933170318604</v>
+        <v>20.593318939209</v>
       </c>
       <c r="H318" t="n">
         <v>480624</v>
@@ -9620,7 +9620,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G319" t="n">
-        <v>20.3064022064209</v>
+        <v>20.3064002990723</v>
       </c>
       <c r="H319" t="n">
         <v>432912</v>
@@ -9678,7 +9678,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G321" t="n">
-        <v>20.3064022064209</v>
+        <v>20.3064002990723</v>
       </c>
       <c r="H321" t="n">
         <v>201544</v>
@@ -9736,7 +9736,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G323" t="n">
-        <v>20.1953372955322</v>
+        <v>20.1953353881836</v>
       </c>
       <c r="H323" t="n">
         <v>265425</v>
@@ -9765,7 +9765,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>20.547046661377</v>
+        <v>20.5470428466797</v>
       </c>
       <c r="H324" t="n">
         <v>335643</v>
@@ -9823,7 +9823,7 @@
         <v>22.1100006103516</v>
       </c>
       <c r="G326" t="n">
-        <v>20.4637413024902</v>
+        <v>20.4637451171875</v>
       </c>
       <c r="H326" t="n">
         <v>156355</v>
@@ -9852,7 +9852,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>20.547046661377</v>
+        <v>20.5470428466797</v>
       </c>
       <c r="H327" t="n">
         <v>156579</v>
@@ -9881,7 +9881,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G328" t="n">
-        <v>20.4544849395752</v>
+        <v>20.4544868469238</v>
       </c>
       <c r="H328" t="n">
         <v>168939</v>
@@ -9910,7 +9910,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G329" t="n">
-        <v>20.9727878570557</v>
+        <v>20.9727916717529</v>
       </c>
       <c r="H329" t="n">
         <v>296171</v>
@@ -10026,7 +10026,7 @@
         <v>22</v>
       </c>
       <c r="G333" t="n">
-        <v>20.361930847168</v>
+        <v>20.3619365692139</v>
       </c>
       <c r="H333" t="n">
         <v>381662</v>
@@ -10084,7 +10084,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>20.2878894805908</v>
+        <v>20.2878875732422</v>
       </c>
       <c r="H335" t="n">
         <v>280641</v>
@@ -10113,7 +10113,7 @@
         <v>22.8299999237061</v>
       </c>
       <c r="G336" t="n">
-        <v>21.1301345825195</v>
+        <v>21.1301307678223</v>
       </c>
       <c r="H336" t="n">
         <v>429265</v>
@@ -10142,7 +10142,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G337" t="n">
-        <v>21.3059883117676</v>
+        <v>21.3059864044189</v>
       </c>
       <c r="H337" t="n">
         <v>270933</v>
@@ -10171,7 +10171,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G338" t="n">
-        <v>22.0464153289795</v>
+        <v>22.0464191436768</v>
       </c>
       <c r="H338" t="n">
         <v>926428</v>
@@ -10200,7 +10200,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G339" t="n">
-        <v>22.36110496521</v>
+        <v>22.3611030578613</v>
       </c>
       <c r="H339" t="n">
         <v>260306</v>
@@ -10229,7 +10229,7 @@
         <v>24.3500003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>22.536958694458</v>
+        <v>22.5369567871094</v>
       </c>
       <c r="H340" t="n">
         <v>256515</v>
@@ -10258,7 +10258,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G341" t="n">
-        <v>22.5462112426758</v>
+        <v>22.5462131500244</v>
       </c>
       <c r="H341" t="n">
         <v>412185</v>
@@ -10287,7 +10287,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G342" t="n">
-        <v>22.3333358764648</v>
+        <v>22.3333396911621</v>
       </c>
       <c r="H342" t="n">
         <v>198084</v>
@@ -10345,7 +10345,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G344" t="n">
-        <v>22.7405776977539</v>
+        <v>22.7405738830566</v>
       </c>
       <c r="H344" t="n">
         <v>355440</v>
@@ -10374,7 +10374,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G345" t="n">
-        <v>22.3981227874756</v>
+        <v>22.3981266021729</v>
       </c>
       <c r="H345" t="n">
         <v>382139</v>
@@ -10403,7 +10403,7 @@
         <v>25</v>
       </c>
       <c r="G346" t="n">
-        <v>23.1385555267334</v>
+        <v>23.138557434082</v>
       </c>
       <c r="H346" t="n">
         <v>298486</v>
@@ -10432,7 +10432,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G347" t="n">
-        <v>23.09228515625</v>
+        <v>23.0922832489014</v>
       </c>
       <c r="H347" t="n">
         <v>205946</v>
@@ -10461,7 +10461,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G348" t="n">
-        <v>23.8789882659912</v>
+        <v>23.8789901733398</v>
       </c>
       <c r="H348" t="n">
         <v>1017953</v>
@@ -10490,7 +10490,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>23.9160175323486</v>
+        <v>23.9160137176514</v>
       </c>
       <c r="H349" t="n">
         <v>465594</v>
@@ -10548,7 +10548,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G351" t="n">
-        <v>24.345085144043</v>
+        <v>24.3450870513916</v>
       </c>
       <c r="H351" t="n">
         <v>399034</v>
@@ -10635,7 +10635,7 @@
         <v>25.3199996948242</v>
       </c>
       <c r="G354" t="n">
-        <v>23.6175327301025</v>
+        <v>23.6175308227539</v>
       </c>
       <c r="H354" t="n">
         <v>378226</v>
@@ -10664,7 +10664,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>23.4589653015137</v>
+        <v>23.458963394165</v>
       </c>
       <c r="H355" t="n">
         <v>523536</v>
@@ -10693,7 +10693,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G356" t="n">
-        <v>24.0092906951904</v>
+        <v>24.0092926025391</v>
       </c>
       <c r="H356" t="n">
         <v>499096</v>
@@ -10722,7 +10722,7 @@
         <v>26</v>
       </c>
       <c r="G357" t="n">
-        <v>24.2518100738525</v>
+        <v>24.2518081665039</v>
       </c>
       <c r="H357" t="n">
         <v>648998</v>
@@ -10751,7 +10751,7 @@
         <v>26</v>
       </c>
       <c r="G358" t="n">
-        <v>24.2518100738525</v>
+        <v>24.2518081665039</v>
       </c>
       <c r="H358" t="n">
         <v>336827</v>
@@ -10780,7 +10780,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G359" t="n">
-        <v>24.6435699462891</v>
+        <v>24.6435718536377</v>
       </c>
       <c r="H359" t="n">
         <v>221417</v>
@@ -10809,7 +10809,7 @@
         <v>26.2700004577637</v>
       </c>
       <c r="G360" t="n">
-        <v>24.5036563873291</v>
+        <v>24.5036544799805</v>
       </c>
       <c r="H360" t="n">
         <v>205880</v>
@@ -10838,7 +10838,7 @@
         <v>26.4300003051758</v>
       </c>
       <c r="G361" t="n">
-        <v>24.6528949737549</v>
+        <v>24.6528987884521</v>
       </c>
       <c r="H361" t="n">
         <v>298971</v>
@@ -10896,7 +10896,7 @@
         <v>26.8299999237061</v>
       </c>
       <c r="G363" t="n">
-        <v>25.0260028839111</v>
+        <v>25.0259990692139</v>
       </c>
       <c r="H363" t="n">
         <v>354157</v>
@@ -10925,7 +10925,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>24.9980220794678</v>
+        <v>24.9980201721191</v>
       </c>
       <c r="H364" t="n">
         <v>248636</v>
@@ -10983,7 +10983,7 @@
         <v>26.6900005340576</v>
       </c>
       <c r="G366" t="n">
-        <v>24.8954181671143</v>
+        <v>24.895414352417</v>
       </c>
       <c r="H366" t="n">
         <v>292631</v>
@@ -11012,7 +11012,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G367" t="n">
-        <v>24.4663467407227</v>
+        <v>24.466344833374</v>
       </c>
       <c r="H367" t="n">
         <v>297581</v>
@@ -11041,7 +11041,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G368" t="n">
-        <v>24.0092906951904</v>
+        <v>24.0092926025391</v>
       </c>
       <c r="H368" t="n">
         <v>457435</v>
@@ -11070,7 +11070,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G369" t="n">
-        <v>23.5615634918213</v>
+        <v>23.5615692138672</v>
       </c>
       <c r="H369" t="n">
         <v>388762</v>
@@ -11099,7 +11099,7 @@
         <v>24.3700008392334</v>
       </c>
       <c r="G370" t="n">
-        <v>22.7314109802246</v>
+        <v>22.731409072876</v>
       </c>
       <c r="H370" t="n">
         <v>477757</v>
@@ -11128,7 +11128,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G371" t="n">
-        <v>23.4776172637939</v>
+        <v>23.4776153564453</v>
       </c>
       <c r="H371" t="n">
         <v>605390</v>
@@ -11157,7 +11157,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>23.8413944244385</v>
+        <v>23.8413925170898</v>
       </c>
       <c r="H372" t="n">
         <v>276439</v>
@@ -11186,7 +11186,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>23.1418209075928</v>
+        <v>23.1418228149414</v>
       </c>
       <c r="H373" t="n">
         <v>221337</v>
@@ -11244,7 +11244,7 @@
         <v>25.9300003051758</v>
       </c>
       <c r="G375" t="n">
-        <v>24.1865158081055</v>
+        <v>24.1865177154541</v>
       </c>
       <c r="H375" t="n">
         <v>192731</v>
@@ -11273,7 +11273,7 @@
         <v>25.5</v>
       </c>
       <c r="G376" t="n">
-        <v>23.7854290008545</v>
+        <v>23.7854270935059</v>
       </c>
       <c r="H376" t="n">
         <v>200864</v>
@@ -11302,7 +11302,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G377" t="n">
-        <v>23.8413944244385</v>
+        <v>23.8413925170898</v>
       </c>
       <c r="H377" t="n">
         <v>92681</v>
@@ -11360,7 +11360,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G379" t="n">
-        <v>23.8413944244385</v>
+        <v>23.8413925170898</v>
       </c>
       <c r="H379" t="n">
         <v>169002</v>
@@ -11389,7 +11389,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G380" t="n">
-        <v>23.6455135345459</v>
+        <v>23.6455173492432</v>
       </c>
       <c r="H380" t="n">
         <v>162627</v>
@@ -11418,7 +11418,7 @@
         <v>25.1200008392334</v>
       </c>
       <c r="G381" t="n">
-        <v>23.430980682373</v>
+        <v>23.4309825897217</v>
       </c>
       <c r="H381" t="n">
         <v>125922</v>
@@ -11534,7 +11534,7 @@
         <v>23.4300003051758</v>
       </c>
       <c r="G385" t="n">
-        <v>21.8546123504639</v>
+        <v>21.8546104431152</v>
       </c>
       <c r="H385" t="n">
         <v>323003</v>
@@ -11592,7 +11592,7 @@
         <v>23.4500007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>21.8732681274414</v>
+        <v>21.8732662200928</v>
       </c>
       <c r="H387" t="n">
         <v>166389</v>
@@ -11737,7 +11737,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G392" t="n">
-        <v>22.1064567565918</v>
+        <v>22.1064586639404</v>
       </c>
       <c r="H392" t="n">
         <v>226098</v>
@@ -11882,7 +11882,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>23.5056018829346</v>
+        <v>23.5055980682373</v>
       </c>
       <c r="H397" t="n">
         <v>220304</v>
@@ -11940,7 +11940,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G399" t="n">
-        <v>23.3936672210693</v>
+        <v>23.3936653137207</v>
       </c>
       <c r="H399" t="n">
         <v>196952</v>
@@ -11969,7 +11969,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G400" t="n">
-        <v>23.8134136199951</v>
+        <v>23.8134117126465</v>
       </c>
       <c r="H400" t="n">
         <v>223261</v>
@@ -12027,7 +12027,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G402" t="n">
-        <v>23.8413944244385</v>
+        <v>23.8413925170898</v>
       </c>
       <c r="H402" t="n">
         <v>167522</v>
@@ -12172,7 +12172,7 @@
         <v>25.6900005340576</v>
       </c>
       <c r="G407" t="n">
-        <v>23.9626522064209</v>
+        <v>23.9626541137695</v>
       </c>
       <c r="H407" t="n">
         <v>143136</v>
@@ -12201,7 +12201,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G408" t="n">
-        <v>23.710807800293</v>
+        <v>23.7108058929443</v>
       </c>
       <c r="H408" t="n">
         <v>292562</v>
@@ -12375,7 +12375,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G414" t="n">
-        <v>22.3116664886475</v>
+        <v>22.3116645812988</v>
       </c>
       <c r="H414" t="n">
         <v>249259</v>
@@ -12404,7 +12404,7 @@
         <v>24.2800006866455</v>
       </c>
       <c r="G415" t="n">
-        <v>22.6474609375</v>
+        <v>22.6474590301514</v>
       </c>
       <c r="H415" t="n">
         <v>165083</v>
@@ -12520,7 +12520,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G419" t="n">
-        <v>22.5448570251465</v>
+        <v>22.5448589324951</v>
       </c>
       <c r="H419" t="n">
         <v>85965</v>
@@ -12549,7 +12549,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G420" t="n">
-        <v>22.5448570251465</v>
+        <v>22.5448589324951</v>
       </c>
       <c r="H420" t="n">
         <v>148217</v>
@@ -12607,7 +12607,7 @@
         <v>24.1900005340576</v>
       </c>
       <c r="G422" t="n">
-        <v>22.5635108947754</v>
+        <v>22.563512802124</v>
       </c>
       <c r="H422" t="n">
         <v>171176</v>
@@ -12694,7 +12694,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G425" t="n">
-        <v>22.1437683105469</v>
+        <v>22.1437702178955</v>
       </c>
       <c r="H425" t="n">
         <v>305758</v>
@@ -12723,7 +12723,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>22.8993034362793</v>
+        <v>22.8993053436279</v>
       </c>
       <c r="H426" t="n">
         <v>243435</v>
@@ -12752,7 +12752,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G427" t="n">
-        <v>22.7967014312744</v>
+        <v>22.7966995239258</v>
       </c>
       <c r="H427" t="n">
         <v>352708</v>
@@ -12810,7 +12810,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G429" t="n">
-        <v>23.1324920654297</v>
+        <v>23.1324939727783</v>
       </c>
       <c r="H429" t="n">
         <v>186760</v>
@@ -12926,7 +12926,7 @@
         <v>24.5699996948242</v>
       </c>
       <c r="G433" t="n">
-        <v>22.9179592132568</v>
+        <v>22.9179611206055</v>
       </c>
       <c r="H433" t="n">
         <v>182778</v>
@@ -12955,7 +12955,7 @@
         <v>24.9300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>23.253755569458</v>
+        <v>23.2537574768066</v>
       </c>
       <c r="H434" t="n">
         <v>170720</v>
@@ -12984,7 +12984,7 @@
         <v>24.9300003051758</v>
       </c>
       <c r="G435" t="n">
-        <v>23.253755569458</v>
+        <v>23.2537574768066</v>
       </c>
       <c r="H435" t="n">
         <v>229321</v>
@@ -13013,7 +13013,7 @@
         <v>24.9500007629395</v>
       </c>
       <c r="G436" t="n">
-        <v>23.2724132537842</v>
+        <v>23.2724094390869</v>
       </c>
       <c r="H436" t="n">
         <v>441068</v>
@@ -13042,7 +13042,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G437" t="n">
-        <v>23.3843421936035</v>
+        <v>23.3843441009521</v>
       </c>
       <c r="H437" t="n">
         <v>291265</v>
@@ -13100,7 +13100,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G439" t="n">
-        <v>23.0019092559814</v>
+        <v>23.0019073486328</v>
       </c>
       <c r="H439" t="n">
         <v>231922</v>
@@ -13158,7 +13158,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G441" t="n">
-        <v>23.1324920654297</v>
+        <v>23.1324939727783</v>
       </c>
       <c r="H441" t="n">
         <v>141177</v>
@@ -13187,7 +13187,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G442" t="n">
-        <v>23.6455135345459</v>
+        <v>23.6455173492432</v>
       </c>
       <c r="H442" t="n">
         <v>214205</v>
@@ -13245,7 +13245,7 @@
         <v>25.9099998474121</v>
       </c>
       <c r="G444" t="n">
-        <v>24.1678600311279</v>
+        <v>24.1678638458252</v>
       </c>
       <c r="H444" t="n">
         <v>218815</v>
@@ -13274,7 +13274,7 @@
         <v>25.75</v>
       </c>
       <c r="G445" t="n">
-        <v>24.0186176300049</v>
+        <v>24.0186157226562</v>
       </c>
       <c r="H445" t="n">
         <v>246312</v>
@@ -13303,7 +13303,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G446" t="n">
-        <v>23.9813079833984</v>
+        <v>23.9813098907471</v>
       </c>
       <c r="H446" t="n">
         <v>219593</v>
@@ -13332,7 +13332,7 @@
         <v>26</v>
       </c>
       <c r="G447" t="n">
-        <v>24.2518100738525</v>
+        <v>24.2518081665039</v>
       </c>
       <c r="H447" t="n">
         <v>169892</v>
@@ -13361,7 +13361,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G448" t="n">
-        <v>24.5502910614014</v>
+        <v>24.55029296875</v>
       </c>
       <c r="H448" t="n">
         <v>242287</v>
@@ -13390,7 +13390,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G449" t="n">
-        <v>24.6249141693115</v>
+        <v>24.6249160766602</v>
       </c>
       <c r="H449" t="n">
         <v>206947</v>
@@ -13506,7 +13506,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G453" t="n">
-        <v>24.1398773193359</v>
+        <v>24.1398754119873</v>
       </c>
       <c r="H453" t="n">
         <v>137142</v>
@@ -13564,7 +13564,7 @@
         <v>25.75</v>
       </c>
       <c r="G455" t="n">
-        <v>24.0186176300049</v>
+        <v>24.0186157226562</v>
       </c>
       <c r="H455" t="n">
         <v>120771</v>
@@ -13680,7 +13680,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G459" t="n">
-        <v>24.578275680542</v>
+        <v>24.5782775878906</v>
       </c>
       <c r="H459" t="n">
         <v>117322</v>
@@ -13709,7 +13709,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G460" t="n">
-        <v>25.790864944458</v>
+        <v>25.7908668518066</v>
       </c>
       <c r="H460" t="n">
         <v>1064605</v>
@@ -13738,7 +13738,7 @@
         <v>27.5</v>
       </c>
       <c r="G461" t="n">
-        <v>25.6509532928467</v>
+        <v>25.650951385498</v>
       </c>
       <c r="H461" t="n">
         <v>598817</v>
@@ -13796,7 +13796,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G463" t="n">
-        <v>25.8375034332275</v>
+        <v>25.8375072479248</v>
       </c>
       <c r="H463" t="n">
         <v>238036</v>
@@ -13854,7 +13854,7 @@
         <v>28.1700000762939</v>
       </c>
       <c r="G465" t="n">
-        <v>26.2759056091309</v>
+        <v>26.2759037017822</v>
       </c>
       <c r="H465" t="n">
         <v>203166</v>
@@ -13912,7 +13912,7 @@
         <v>28.5</v>
       </c>
       <c r="G467" t="n">
-        <v>26.5837116241455</v>
+        <v>26.5837154388428</v>
       </c>
       <c r="H467" t="n">
         <v>321132</v>
@@ -13999,7 +13999,7 @@
         <v>28.9099998474121</v>
       </c>
       <c r="G470" t="n">
-        <v>26.9661464691162</v>
+        <v>26.9661445617676</v>
       </c>
       <c r="H470" t="n">
         <v>145913</v>
@@ -14028,7 +14028,7 @@
         <v>28.5</v>
       </c>
       <c r="G471" t="n">
-        <v>26.5837116241455</v>
+        <v>26.5837154388428</v>
       </c>
       <c r="H471" t="n">
         <v>271543</v>
@@ -14086,7 +14086,7 @@
         <v>28.1900005340576</v>
       </c>
       <c r="G473" t="n">
-        <v>26.2945594787598</v>
+        <v>26.2945556640625</v>
       </c>
       <c r="H473" t="n">
         <v>353671</v>
@@ -14115,7 +14115,7 @@
         <v>28.4300003051758</v>
       </c>
       <c r="G474" t="n">
-        <v>26.5184230804443</v>
+        <v>26.5184192657471</v>
       </c>
       <c r="H474" t="n">
         <v>180072</v>
@@ -14144,7 +14144,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G475" t="n">
-        <v>26.3411979675293</v>
+        <v>26.3411960601807</v>
       </c>
       <c r="H475" t="n">
         <v>168771</v>
@@ -14173,7 +14173,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G476" t="n">
-        <v>25.4643974304199</v>
+        <v>25.4643993377686</v>
       </c>
       <c r="H476" t="n">
         <v>720970</v>
@@ -14231,7 +14231,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G478" t="n">
-        <v>25.1752433776855</v>
+        <v>25.1752452850342</v>
       </c>
       <c r="H478" t="n">
         <v>326491</v>
@@ -14260,7 +14260,7 @@
         <v>27.1700000762939</v>
       </c>
       <c r="G479" t="n">
-        <v>25.3431396484375</v>
+        <v>25.3431415557861</v>
       </c>
       <c r="H479" t="n">
         <v>300397</v>
@@ -14318,7 +14318,7 @@
         <v>27.2299995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>25.3991069793701</v>
+        <v>25.3991088867188</v>
       </c>
       <c r="H481" t="n">
         <v>265960</v>
@@ -14347,7 +14347,7 @@
         <v>27.1700000762939</v>
       </c>
       <c r="G482" t="n">
-        <v>25.3431396484375</v>
+        <v>25.3431415557861</v>
       </c>
       <c r="H482" t="n">
         <v>147227</v>
@@ -14376,7 +14376,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G483" t="n">
-        <v>25.2405338287354</v>
+        <v>25.2405376434326</v>
       </c>
       <c r="H483" t="n">
         <v>139148</v>
@@ -14405,7 +14405,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G484" t="n">
-        <v>25.9867458343506</v>
+        <v>25.9867477416992</v>
       </c>
       <c r="H484" t="n">
         <v>200824</v>
@@ -14434,7 +14434,7 @@
         <v>28.5900001525879</v>
       </c>
       <c r="G485" t="n">
-        <v>26.667667388916</v>
+        <v>26.6676654815674</v>
       </c>
       <c r="H485" t="n">
         <v>211725</v>
@@ -14521,7 +14521,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>26.5650596618652</v>
+        <v>26.5650577545166</v>
       </c>
       <c r="H488" t="n">
         <v>111607</v>
@@ -14579,7 +14579,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G490" t="n">
-        <v>26.0613670349121</v>
+        <v>26.0613708496094</v>
       </c>
       <c r="H490" t="n">
         <v>136299</v>
@@ -14608,7 +14608,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G491" t="n">
-        <v>25.9867458343506</v>
+        <v>25.9867477416992</v>
       </c>
       <c r="H491" t="n">
         <v>85547</v>
@@ -14637,7 +14637,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G492" t="n">
-        <v>25.8375034332275</v>
+        <v>25.8375072479248</v>
       </c>
       <c r="H492" t="n">
         <v>180849</v>
@@ -14666,7 +14666,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G493" t="n">
-        <v>25.3151569366455</v>
+        <v>25.3151588439941</v>
       </c>
       <c r="H493" t="n">
         <v>222428</v>
@@ -14695,7 +14695,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>25.8375034332275</v>
+        <v>25.8375072479248</v>
       </c>
       <c r="H494" t="n">
         <v>174491</v>
@@ -14724,7 +14724,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G495" t="n">
-        <v>25.6975917816162</v>
+        <v>25.6975860595703</v>
       </c>
       <c r="H495" t="n">
         <v>193290</v>
@@ -14753,7 +14753,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G496" t="n">
-        <v>25.5483474731445</v>
+        <v>25.5483493804932</v>
       </c>
       <c r="H496" t="n">
         <v>198532</v>
@@ -14811,7 +14811,7 @@
         <v>27.2099990844727</v>
       </c>
       <c r="G498" t="n">
-        <v>25.3804550170898</v>
+        <v>25.3804512023926</v>
       </c>
       <c r="H498" t="n">
         <v>125023</v>
@@ -14840,7 +14840,7 @@
         <v>27.4099998474121</v>
       </c>
       <c r="G499" t="n">
-        <v>25.5670070648193</v>
+        <v>25.5670013427734</v>
       </c>
       <c r="H499" t="n">
         <v>163600</v>
@@ -14869,7 +14869,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G500" t="n">
-        <v>25.1659126281738</v>
+        <v>25.1659183502197</v>
       </c>
       <c r="H500" t="n">
         <v>131395</v>
@@ -14898,7 +14898,7 @@
         <v>27.0699996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>25.2498683929443</v>
+        <v>25.2498664855957</v>
       </c>
       <c r="H501" t="n">
         <v>132276</v>
@@ -14927,7 +14927,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>24.9980220794678</v>
+        <v>24.9980201721191</v>
       </c>
       <c r="H502" t="n">
         <v>181232</v>
@@ -14985,7 +14985,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="n">
-        <v>25.5296936035156</v>
+        <v>25.5296955108643</v>
       </c>
       <c r="H504" t="n">
         <v>169699</v>
@@ -15014,7 +15014,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G505" t="n">
-        <v>25.4830532073975</v>
+        <v>25.4830570220947</v>
       </c>
       <c r="H505" t="n">
         <v>206047</v>
@@ -15043,7 +15043,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>25.2312107086182</v>
+        <v>25.2312068939209</v>
       </c>
       <c r="H506" t="n">
         <v>105610</v>
@@ -15101,7 +15101,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>24.8581008911133</v>
+        <v>24.8581027984619</v>
       </c>
       <c r="H508" t="n">
         <v>127973</v>
@@ -15130,7 +15130,7 @@
         <v>26.6700000762939</v>
       </c>
       <c r="G509" t="n">
-        <v>24.8767623901367</v>
+        <v>24.8767642974854</v>
       </c>
       <c r="H509" t="n">
         <v>165895</v>
@@ -15159,7 +15159,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G510" t="n">
-        <v>24.7741546630859</v>
+        <v>24.7741584777832</v>
       </c>
       <c r="H510" t="n">
         <v>173105</v>
@@ -15217,7 +15217,7 @@
         <v>26.6499996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>24.8581008911133</v>
+        <v>24.8581027984619</v>
       </c>
       <c r="H512" t="n">
         <v>202574</v>
@@ -15246,7 +15246,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>25.4643974304199</v>
+        <v>25.4643993377686</v>
       </c>
       <c r="H513" t="n">
         <v>173058</v>
@@ -15333,7 +15333,7 @@
         <v>29.1200008392334</v>
       </c>
       <c r="G516" t="n">
-        <v>27.1620311737061</v>
+        <v>27.1620254516602</v>
       </c>
       <c r="H516" t="n">
         <v>255787</v>
@@ -15362,7 +15362,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G517" t="n">
-        <v>28.0015144348145</v>
+        <v>28.0015125274658</v>
       </c>
       <c r="H517" t="n">
         <v>612711</v>
@@ -15420,7 +15420,7 @@
         <v>29.5799999237061</v>
       </c>
       <c r="G519" t="n">
-        <v>27.5910987854004</v>
+        <v>27.5910968780518</v>
       </c>
       <c r="H519" t="n">
         <v>313171</v>
@@ -15478,7 +15478,7 @@
         <v>29.5799999237061</v>
       </c>
       <c r="G521" t="n">
-        <v>27.5910987854004</v>
+        <v>27.5910968780518</v>
       </c>
       <c r="H521" t="n">
         <v>138523</v>
@@ -15507,7 +15507,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G522" t="n">
-        <v>27.5351295471191</v>
+        <v>27.5351314544678</v>
       </c>
       <c r="H522" t="n">
         <v>182562</v>
@@ -15565,7 +15565,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G524" t="n">
-        <v>28.1507549285889</v>
+        <v>28.1507568359375</v>
       </c>
       <c r="H524" t="n">
         <v>248757</v>
@@ -15594,7 +15594,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G525" t="n">
-        <v>28.6357917785645</v>
+        <v>28.6357936859131</v>
       </c>
       <c r="H525" t="n">
         <v>239916</v>
@@ -15623,7 +15623,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>28.7290668487549</v>
+        <v>28.7290687561035</v>
       </c>
       <c r="H526" t="n">
         <v>241734</v>
@@ -15652,7 +15652,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>28.7290668487549</v>
+        <v>28.7290687561035</v>
       </c>
       <c r="H527" t="n">
         <v>289910</v>
@@ -15681,7 +15681,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G528" t="n">
-        <v>28.2813415527344</v>
+        <v>28.2813396453857</v>
       </c>
       <c r="H528" t="n">
         <v>278631</v>
@@ -15710,7 +15710,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G529" t="n">
-        <v>27.8709278106689</v>
+        <v>27.8709259033203</v>
       </c>
       <c r="H529" t="n">
         <v>173848</v>
@@ -15739,7 +15739,7 @@
         <v>30.2800006866455</v>
       </c>
       <c r="G530" t="n">
-        <v>28.2440319061279</v>
+        <v>28.2440299987793</v>
       </c>
       <c r="H530" t="n">
         <v>333684</v>
@@ -15768,7 +15768,7 @@
         <v>30</v>
       </c>
       <c r="G531" t="n">
-        <v>27.9828567504883</v>
+        <v>27.9828586578369</v>
       </c>
       <c r="H531" t="n">
         <v>199960</v>
@@ -15826,7 +15826,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G533" t="n">
-        <v>27.0874061584473</v>
+        <v>27.0874042510986</v>
       </c>
       <c r="H533" t="n">
         <v>382439</v>
@@ -15855,7 +15855,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G534" t="n">
-        <v>27.1993389129639</v>
+        <v>27.1993370056152</v>
       </c>
       <c r="H534" t="n">
         <v>177129</v>
@@ -15884,7 +15884,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>26.4904384613037</v>
+        <v>26.4904365539551</v>
       </c>
       <c r="H535" t="n">
         <v>200099</v>
@@ -15913,7 +15913,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G536" t="n">
-        <v>25.9867458343506</v>
+        <v>25.9867477416992</v>
       </c>
       <c r="H536" t="n">
         <v>299413</v>
@@ -15942,7 +15942,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G537" t="n">
-        <v>25.8748168945312</v>
+        <v>25.874813079834</v>
       </c>
       <c r="H537" t="n">
         <v>408925</v>
@@ -15971,7 +15971,7 @@
         <v>28.9400005340576</v>
       </c>
       <c r="G538" t="n">
-        <v>26.9941272735596</v>
+        <v>26.9941291809082</v>
       </c>
       <c r="H538" t="n">
         <v>322618</v>
@@ -16087,7 +16087,7 @@
         <v>27.4400005340576</v>
       </c>
       <c r="G542" t="n">
-        <v>25.5949878692627</v>
+        <v>25.5949897766113</v>
       </c>
       <c r="H542" t="n">
         <v>146026</v>
@@ -16116,7 +16116,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G543" t="n">
-        <v>27.0314426422119</v>
+        <v>27.0314407348633</v>
       </c>
       <c r="H543" t="n">
         <v>418405</v>
@@ -16174,7 +16174,7 @@
         <v>29.4200000762939</v>
       </c>
       <c r="G545" t="n">
-        <v>27.4418544769287</v>
+        <v>27.4418563842773</v>
       </c>
       <c r="H545" t="n">
         <v>337189</v>
@@ -16203,7 +16203,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G546" t="n">
-        <v>27.1433734893799</v>
+        <v>27.1433715820312</v>
       </c>
       <c r="H546" t="n">
         <v>128767</v>
@@ -16261,7 +16261,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G548" t="n">
-        <v>26.5090942382812</v>
+        <v>26.5090923309326</v>
       </c>
       <c r="H548" t="n">
         <v>118593</v>
@@ -16290,7 +16290,7 @@
         <v>27.7800006866455</v>
       </c>
       <c r="G549" t="n">
-        <v>25.9121265411377</v>
+        <v>25.9121284484863</v>
       </c>
       <c r="H549" t="n">
         <v>168991</v>
@@ -16319,7 +16319,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G550" t="n">
-        <v>26.0613670349121</v>
+        <v>26.0613708496094</v>
       </c>
       <c r="H550" t="n">
         <v>168173</v>
@@ -16348,7 +16348,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G551" t="n">
-        <v>25.9867458343506</v>
+        <v>25.9867477416992</v>
       </c>
       <c r="H551" t="n">
         <v>123957</v>
@@ -16377,7 +16377,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G552" t="n">
-        <v>25.7442264556885</v>
+        <v>25.7442283630371</v>
       </c>
       <c r="H552" t="n">
         <v>242085</v>
@@ -16406,7 +16406,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G553" t="n">
-        <v>25.4830532073975</v>
+        <v>25.4830570220947</v>
       </c>
       <c r="H553" t="n">
         <v>154498</v>
@@ -16435,7 +16435,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G554" t="n">
-        <v>25.0166759490967</v>
+        <v>25.016674041748</v>
       </c>
       <c r="H554" t="n">
         <v>249508</v>
@@ -16493,7 +16493,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G556" t="n">
-        <v>24.5689487457275</v>
+        <v>24.5689506530762</v>
       </c>
       <c r="H556" t="n">
         <v>157145</v>
@@ -16522,7 +16522,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G557" t="n">
-        <v>25.296501159668</v>
+        <v>25.2965049743652</v>
       </c>
       <c r="H557" t="n">
         <v>240950</v>
@@ -16580,7 +16580,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G559" t="n">
-        <v>25.8001956939697</v>
+        <v>25.8001937866211</v>
       </c>
       <c r="H559" t="n">
         <v>162448</v>
@@ -16638,7 +16638,7 @@
         <v>28.1200008392334</v>
       </c>
       <c r="G561" t="n">
-        <v>26.2292652130127</v>
+        <v>26.2292671203613</v>
       </c>
       <c r="H561" t="n">
         <v>103699</v>
@@ -16696,7 +16696,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G563" t="n">
-        <v>26.3785057067871</v>
+        <v>26.3785095214844</v>
       </c>
       <c r="H563" t="n">
         <v>188421</v>
@@ -16725,7 +16725,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G564" t="n">
-        <v>26.8635425567627</v>
+        <v>26.8635406494141</v>
       </c>
       <c r="H564" t="n">
         <v>160384</v>
@@ -16754,7 +16754,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G565" t="n">
-        <v>26.0986824035645</v>
+        <v>26.0986785888672</v>
       </c>
       <c r="H565" t="n">
         <v>225534</v>
@@ -16841,7 +16841,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G568" t="n">
-        <v>25.4457454681396</v>
+        <v>25.4457492828369</v>
       </c>
       <c r="H568" t="n">
         <v>152576</v>
@@ -16870,7 +16870,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G569" t="n">
-        <v>24.8674354553223</v>
+        <v>24.8674335479736</v>
       </c>
       <c r="H569" t="n">
         <v>197315</v>
@@ -16899,7 +16899,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G570" t="n">
-        <v>25.0166759490967</v>
+        <v>25.016674041748</v>
       </c>
       <c r="H570" t="n">
         <v>123616</v>
@@ -16928,7 +16928,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G571" t="n">
-        <v>24.4756679534912</v>
+        <v>24.4756717681885</v>
       </c>
       <c r="H571" t="n">
         <v>141915</v>
@@ -16957,7 +16957,7 @@
         <v>26.5</v>
       </c>
       <c r="G572" t="n">
-        <v>24.7181930541992</v>
+        <v>24.718189239502</v>
       </c>
       <c r="H572" t="n">
         <v>148619</v>
@@ -17015,7 +17015,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G574" t="n">
-        <v>25.613639831543</v>
+        <v>25.6136436462402</v>
       </c>
       <c r="H574" t="n">
         <v>356555</v>
@@ -17102,7 +17102,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G577" t="n">
-        <v>24.8674354553223</v>
+        <v>24.8674335479736</v>
       </c>
       <c r="H577" t="n">
         <v>148604</v>
@@ -17131,7 +17131,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G578" t="n">
-        <v>24.5876045227051</v>
+        <v>24.5876026153564</v>
       </c>
       <c r="H578" t="n">
         <v>187025</v>
@@ -17160,7 +17160,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G579" t="n">
-        <v>24.6249141693115</v>
+        <v>24.6249160766602</v>
       </c>
       <c r="H579" t="n">
         <v>154464</v>
@@ -17189,7 +17189,7 @@
         <v>26.5</v>
       </c>
       <c r="G580" t="n">
-        <v>24.7181930541992</v>
+        <v>24.718189239502</v>
       </c>
       <c r="H580" t="n">
         <v>108863</v>
@@ -17247,7 +17247,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>24.9980220794678</v>
+        <v>24.9980201721191</v>
       </c>
       <c r="H582" t="n">
         <v>93645</v>
@@ -17276,7 +17276,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G583" t="n">
-        <v>25.1659126281738</v>
+        <v>25.1659183502197</v>
       </c>
       <c r="H583" t="n">
         <v>118550</v>
@@ -17305,7 +17305,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>24.6249141693115</v>
+        <v>24.6249160766602</v>
       </c>
       <c r="H584" t="n">
         <v>137701</v>
@@ -17392,7 +17392,7 @@
         <v>26.2600002288818</v>
       </c>
       <c r="G587" t="n">
-        <v>24.4943313598633</v>
+        <v>24.4943294525146</v>
       </c>
       <c r="H587" t="n">
         <v>227888</v>
@@ -17421,7 +17421,7 @@
         <v>25.9599990844727</v>
       </c>
       <c r="G588" t="n">
-        <v>24.2144947052002</v>
+        <v>24.2144985198975</v>
       </c>
       <c r="H588" t="n">
         <v>1048458</v>
@@ -17450,7 +17450,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>24.1585330963135</v>
+        <v>24.1585350036621</v>
       </c>
       <c r="H589" t="n">
         <v>290652</v>
@@ -17479,7 +17479,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>24.9980220794678</v>
+        <v>24.9980201721191</v>
       </c>
       <c r="H590" t="n">
         <v>277561</v>
@@ -17537,7 +17537,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G592" t="n">
-        <v>24.5316390991211</v>
+        <v>24.5316371917725</v>
       </c>
       <c r="H592" t="n">
         <v>171596</v>
@@ -17566,7 +17566,7 @@
         <v>26.2600002288818</v>
       </c>
       <c r="G593" t="n">
-        <v>24.4943313598633</v>
+        <v>24.4943294525146</v>
       </c>
       <c r="H593" t="n">
         <v>178346</v>
@@ -17624,7 +17624,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G595" t="n">
-        <v>25.3338146209717</v>
+        <v>25.333812713623</v>
       </c>
       <c r="H595" t="n">
         <v>438418</v>
@@ -17653,7 +17653,7 @@
         <v>27.2399997711182</v>
       </c>
       <c r="G596" t="n">
-        <v>25.4084358215332</v>
+        <v>25.4084339141846</v>
       </c>
       <c r="H596" t="n">
         <v>163979</v>
@@ -17682,7 +17682,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G597" t="n">
-        <v>25.7628860473633</v>
+        <v>25.7628879547119</v>
       </c>
       <c r="H597" t="n">
         <v>165030</v>
@@ -17711,7 +17711,7 @@
         <v>28</v>
       </c>
       <c r="G598" t="n">
-        <v>26.1173343658447</v>
+        <v>26.1173362731934</v>
       </c>
       <c r="H598" t="n">
         <v>195162</v>
@@ -17740,7 +17740,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G599" t="n">
-        <v>25.7069187164307</v>
+        <v>25.7069206237793</v>
       </c>
       <c r="H599" t="n">
         <v>202938</v>
@@ -17769,7 +17769,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G600" t="n">
-        <v>25.9867458343506</v>
+        <v>25.9867477416992</v>
       </c>
       <c r="H600" t="n">
         <v>188005</v>
@@ -17798,7 +17798,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G601" t="n">
-        <v>26.6956481933594</v>
+        <v>26.6956462860107</v>
       </c>
       <c r="H601" t="n">
         <v>424733</v>
@@ -17827,7 +17827,7 @@
         <v>29.2800006866455</v>
       </c>
       <c r="G602" t="n">
-        <v>27.3112697601318</v>
+        <v>27.3112678527832</v>
       </c>
       <c r="H602" t="n">
         <v>351365</v>
@@ -17856,7 +17856,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>26.6396808624268</v>
+        <v>26.6396770477295</v>
       </c>
       <c r="H603" t="n">
         <v>251122</v>
@@ -17885,7 +17885,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G604" t="n">
-        <v>26.3411979675293</v>
+        <v>26.3411960601807</v>
       </c>
       <c r="H604" t="n">
         <v>234145</v>
@@ -17943,7 +17943,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G606" t="n">
-        <v>26.2852306365967</v>
+        <v>26.2852325439453</v>
       </c>
       <c r="H606" t="n">
         <v>326393</v>
@@ -17972,7 +17972,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>26.2106132507324</v>
+        <v>26.2106094360352</v>
       </c>
       <c r="H607" t="n">
         <v>360965</v>
@@ -18001,7 +18001,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G608" t="n">
-        <v>26.1824150085449</v>
+        <v>26.1824188232422</v>
       </c>
       <c r="H608" t="n">
         <v>140902</v>
@@ -18030,7 +18030,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G609" t="n">
-        <v>26.3703708648682</v>
+        <v>26.3703746795654</v>
       </c>
       <c r="H609" t="n">
         <v>199580</v>
@@ -18059,7 +18059,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G610" t="n">
-        <v>26.2763957977295</v>
+        <v>26.2763919830322</v>
       </c>
       <c r="H610" t="n">
         <v>240043</v>
@@ -18088,7 +18088,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G611" t="n">
-        <v>26.1448249816895</v>
+        <v>26.1448230743408</v>
       </c>
       <c r="H611" t="n">
         <v>183487</v>
@@ -18117,7 +18117,7 @@
         <v>28.6599998474121</v>
       </c>
       <c r="G612" t="n">
-        <v>26.9342403411865</v>
+        <v>26.9342422485352</v>
       </c>
       <c r="H612" t="n">
         <v>379086</v>
@@ -18146,7 +18146,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>26.0320491790771</v>
+        <v>26.0320510864258</v>
       </c>
       <c r="H613" t="n">
         <v>274664</v>
@@ -18175,7 +18175,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G614" t="n">
-        <v>24.8667163848877</v>
+        <v>24.8667144775391</v>
       </c>
       <c r="H614" t="n">
         <v>569549</v>
@@ -18204,7 +18204,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G615" t="n">
-        <v>25.1110572814941</v>
+        <v>25.1110591888428</v>
       </c>
       <c r="H615" t="n">
         <v>333046</v>
@@ -18233,7 +18233,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G616" t="n">
-        <v>25.2050380706787</v>
+        <v>25.2050399780273</v>
       </c>
       <c r="H616" t="n">
         <v>350241</v>
@@ -18291,7 +18291,7 @@
         <v>27.7800006866455</v>
       </c>
       <c r="G618" t="n">
-        <v>26.1072330474854</v>
+        <v>26.107234954834</v>
       </c>
       <c r="H618" t="n">
         <v>170505</v>
@@ -18320,7 +18320,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G619" t="n">
-        <v>26.0508441925049</v>
+        <v>26.0508460998535</v>
       </c>
       <c r="H619" t="n">
         <v>274657</v>
@@ -18465,7 +18465,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="n">
-        <v>26.5019435882568</v>
+        <v>26.5019474029541</v>
       </c>
       <c r="H624" t="n">
         <v>95204</v>
@@ -18494,7 +18494,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G625" t="n">
-        <v>26.3891677856445</v>
+        <v>26.3891658782959</v>
       </c>
       <c r="H625" t="n">
         <v>140637</v>
@@ -18523,7 +18523,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G626" t="n">
-        <v>26.4455547332764</v>
+        <v>26.445556640625</v>
       </c>
       <c r="H626" t="n">
         <v>156399</v>
@@ -18552,7 +18552,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G627" t="n">
-        <v>26.2388000488281</v>
+        <v>26.2388038635254</v>
       </c>
       <c r="H627" t="n">
         <v>147182</v>
@@ -18581,7 +18581,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G628" t="n">
-        <v>26.1824150085449</v>
+        <v>26.1824188232422</v>
       </c>
       <c r="H628" t="n">
         <v>111958</v>
@@ -18610,7 +18610,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G629" t="n">
-        <v>25.8628883361816</v>
+        <v>25.8628902435303</v>
       </c>
       <c r="H629" t="n">
         <v>112950</v>
@@ -18639,7 +18639,7 @@
         <v>27.4200000762939</v>
       </c>
       <c r="G630" t="n">
-        <v>25.768913269043</v>
+        <v>25.7689113616943</v>
       </c>
       <c r="H630" t="n">
         <v>100909</v>
@@ -18668,7 +18668,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G631" t="n">
-        <v>25.5433597564697</v>
+        <v>25.5433616638184</v>
       </c>
       <c r="H631" t="n">
         <v>151582</v>
@@ -18697,7 +18697,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G632" t="n">
-        <v>25.7125244140625</v>
+        <v>25.7125225067139</v>
       </c>
       <c r="H632" t="n">
         <v>130929</v>
@@ -18784,7 +18784,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G635" t="n">
-        <v>24.8103294372559</v>
+        <v>24.8103313446045</v>
       </c>
       <c r="H635" t="n">
         <v>366949</v>
@@ -18813,7 +18813,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G636" t="n">
-        <v>24.3780288696289</v>
+        <v>24.3780269622803</v>
       </c>
       <c r="H636" t="n">
         <v>142185</v>
@@ -18842,7 +18842,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G637" t="n">
-        <v>25.0358772277832</v>
+        <v>25.0358791351318</v>
       </c>
       <c r="H637" t="n">
         <v>166323</v>
@@ -18871,7 +18871,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G638" t="n">
-        <v>24.5847778320312</v>
+        <v>24.5847816467285</v>
       </c>
       <c r="H638" t="n">
         <v>96997</v>
@@ -18900,7 +18900,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G639" t="n">
-        <v>24.6411685943604</v>
+        <v>24.6411647796631</v>
       </c>
       <c r="H639" t="n">
         <v>77102</v>
@@ -18929,7 +18929,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G640" t="n">
-        <v>23.8893413543701</v>
+        <v>23.8893394470215</v>
       </c>
       <c r="H640" t="n">
         <v>189346</v>
@@ -18987,7 +18987,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G642" t="n">
-        <v>24.4156169891357</v>
+        <v>24.4156150817871</v>
       </c>
       <c r="H642" t="n">
         <v>106994</v>
@@ -19016,7 +19016,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G643" t="n">
-        <v>24.7351455688477</v>
+        <v>24.735143661499</v>
       </c>
       <c r="H643" t="n">
         <v>93127</v>
@@ -19074,7 +19074,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G645" t="n">
-        <v>24.6975574493408</v>
+        <v>24.6975536346436</v>
       </c>
       <c r="H645" t="n">
         <v>75218</v>
@@ -19103,7 +19103,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G646" t="n">
-        <v>24.9418964385986</v>
+        <v>24.9419021606445</v>
       </c>
       <c r="H646" t="n">
         <v>64574</v>
@@ -19132,7 +19132,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>25.2050380706787</v>
+        <v>25.2050399780273</v>
       </c>
       <c r="H647" t="n">
         <v>79973</v>
@@ -19161,7 +19161,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G648" t="n">
-        <v>25.1110572814941</v>
+        <v>25.1110591888428</v>
       </c>
       <c r="H648" t="n">
         <v>61914</v>
@@ -19277,7 +19277,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G652" t="n">
-        <v>25.3929996490479</v>
+        <v>25.3929977416992</v>
       </c>
       <c r="H652" t="n">
         <v>140970</v>
@@ -19306,7 +19306,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G653" t="n">
-        <v>25.0358772277832</v>
+        <v>25.0358791351318</v>
       </c>
       <c r="H653" t="n">
         <v>59746</v>
@@ -19335,7 +19335,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G654" t="n">
-        <v>25.1674499511719</v>
+        <v>25.1674480438232</v>
       </c>
       <c r="H654" t="n">
         <v>77186</v>
@@ -19393,7 +19393,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G656" t="n">
-        <v>25.1486511230469</v>
+        <v>25.1486530303955</v>
       </c>
       <c r="H656" t="n">
         <v>262688</v>
@@ -19480,7 +19480,7 @@
         <v>26.9400005340576</v>
       </c>
       <c r="G659" t="n">
-        <v>25.317813873291</v>
+        <v>25.3178119659424</v>
       </c>
       <c r="H659" t="n">
         <v>71202</v>
@@ -19509,7 +19509,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G660" t="n">
-        <v>25.2050380706787</v>
+        <v>25.2050399780273</v>
       </c>
       <c r="H660" t="n">
         <v>51288</v>
@@ -19538,7 +19538,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G661" t="n">
-        <v>24.753942489624</v>
+        <v>24.7539463043213</v>
       </c>
       <c r="H661" t="n">
         <v>112585</v>
@@ -19596,7 +19596,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>25.9380722045898</v>
+        <v>25.9380702972412</v>
       </c>
       <c r="H663" t="n">
         <v>524148</v>
@@ -19654,7 +19654,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G665" t="n">
-        <v>25.5433597564697</v>
+        <v>25.5433616638184</v>
       </c>
       <c r="H665" t="n">
         <v>94397</v>
@@ -19683,7 +19683,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>25.2802200317383</v>
+        <v>25.2802238464355</v>
       </c>
       <c r="H666" t="n">
         <v>125485</v>
@@ -19857,7 +19857,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>24.8103294372559</v>
+        <v>24.8103313446045</v>
       </c>
       <c r="H672" t="n">
         <v>52600</v>
@@ -19886,7 +19886,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G673" t="n">
-        <v>25.1674499511719</v>
+        <v>25.1674480438232</v>
       </c>
       <c r="H673" t="n">
         <v>111338</v>
@@ -19915,7 +19915,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G674" t="n">
-        <v>24.7351455688477</v>
+        <v>24.735143661499</v>
       </c>
       <c r="H674" t="n">
         <v>55665</v>
@@ -19944,7 +19944,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G675" t="n">
-        <v>24.9418964385986</v>
+        <v>24.9419021606445</v>
       </c>
       <c r="H675" t="n">
         <v>73939</v>
@@ -19973,7 +19973,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G676" t="n">
-        <v>24.6411685943604</v>
+        <v>24.6411647796631</v>
       </c>
       <c r="H676" t="n">
         <v>53748</v>
@@ -20002,7 +20002,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G677" t="n">
-        <v>24.8667163848877</v>
+        <v>24.8667144775391</v>
       </c>
       <c r="H677" t="n">
         <v>70827</v>
@@ -20031,7 +20031,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G678" t="n">
-        <v>24.3780288696289</v>
+        <v>24.3780269622803</v>
       </c>
       <c r="H678" t="n">
         <v>123580</v>
@@ -20060,7 +20060,7 @@
         <v>26.6200008392334</v>
       </c>
       <c r="G679" t="n">
-        <v>25.0170822143555</v>
+        <v>25.0170841217041</v>
       </c>
       <c r="H679" t="n">
         <v>115135</v>
@@ -20147,7 +20147,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G682" t="n">
-        <v>25.3554058074951</v>
+        <v>25.3554039001465</v>
       </c>
       <c r="H682" t="n">
         <v>49509</v>
@@ -20176,7 +20176,7 @@
         <v>26.8400001525879</v>
       </c>
       <c r="G683" t="n">
-        <v>25.2238368988037</v>
+        <v>25.2238349914551</v>
       </c>
       <c r="H683" t="n">
         <v>81617</v>
@@ -20205,7 +20205,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G684" t="n">
-        <v>25.1486511230469</v>
+        <v>25.1486530303955</v>
       </c>
       <c r="H684" t="n">
         <v>127196</v>
@@ -20234,7 +20234,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G685" t="n">
-        <v>25.8628883361816</v>
+        <v>25.8628902435303</v>
       </c>
       <c r="H685" t="n">
         <v>232160</v>
@@ -20263,7 +20263,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G686" t="n">
-        <v>25.9380722045898</v>
+        <v>25.9380702972412</v>
       </c>
       <c r="H686" t="n">
         <v>95490</v>
@@ -20321,7 +20321,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G688" t="n">
-        <v>26.2763957977295</v>
+        <v>26.2763919830322</v>
       </c>
       <c r="H688" t="n">
         <v>152932</v>
@@ -20350,7 +20350,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>26.6898994445801</v>
+        <v>26.6899032592773</v>
       </c>
       <c r="H689" t="n">
         <v>198605</v>
@@ -20408,7 +20408,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G691" t="n">
-        <v>26.2763957977295</v>
+        <v>26.2763919830322</v>
       </c>
       <c r="H691" t="n">
         <v>123944</v>
@@ -20437,7 +20437,7 @@
         <v>28.2600002288818</v>
       </c>
       <c r="G692" t="n">
-        <v>26.5583305358887</v>
+        <v>26.5583324432373</v>
       </c>
       <c r="H692" t="n">
         <v>73367</v>
@@ -20495,7 +20495,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G694" t="n">
-        <v>26.9530372619629</v>
+        <v>26.9530391693115</v>
       </c>
       <c r="H694" t="n">
         <v>185635</v>
@@ -20524,7 +20524,7 @@
         <v>28.9400005340576</v>
       </c>
       <c r="G695" t="n">
-        <v>27.1973819732666</v>
+        <v>27.1973857879639</v>
       </c>
       <c r="H695" t="n">
         <v>134990</v>
@@ -20553,7 +20553,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G696" t="n">
-        <v>27.234977722168</v>
+        <v>27.2349720001221</v>
       </c>
       <c r="H696" t="n">
         <v>159495</v>
@@ -20582,7 +20582,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G697" t="n">
-        <v>27.122200012207</v>
+        <v>27.1222019195557</v>
       </c>
       <c r="H697" t="n">
         <v>106322</v>
@@ -20698,7 +20698,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G701" t="n">
-        <v>26.5019435882568</v>
+        <v>26.5019474029541</v>
       </c>
       <c r="H701" t="n">
         <v>234287</v>
@@ -20756,7 +20756,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G703" t="n">
-        <v>27.0094242095947</v>
+        <v>27.009428024292</v>
       </c>
       <c r="H703" t="n">
         <v>107790</v>
@@ -20814,7 +20814,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G705" t="n">
-        <v>26.8590621948242</v>
+        <v>26.8590602874756</v>
       </c>
       <c r="H705" t="n">
         <v>60685</v>
@@ -20872,7 +20872,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G707" t="n">
-        <v>25.2050380706787</v>
+        <v>25.2050399780273</v>
       </c>
       <c r="H707" t="n">
         <v>237394</v>
@@ -20959,7 +20959,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G710" t="n">
-        <v>23.6637916564941</v>
+        <v>23.6637935638428</v>
       </c>
       <c r="H710" t="n">
         <v>309386</v>
@@ -20988,7 +20988,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G711" t="n">
-        <v>23.926929473877</v>
+        <v>23.9269313812256</v>
       </c>
       <c r="H711" t="n">
         <v>270697</v>
@@ -21017,7 +21017,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G712" t="n">
-        <v>23.0811233520508</v>
+        <v>23.0811252593994</v>
       </c>
       <c r="H712" t="n">
         <v>161117</v>
@@ -21046,7 +21046,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>23.7389736175537</v>
+        <v>23.7389755249023</v>
       </c>
       <c r="H713" t="n">
         <v>228938</v>
@@ -21133,7 +21133,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G716" t="n">
-        <v>24.0960922241211</v>
+        <v>24.0960903167725</v>
       </c>
       <c r="H716" t="n">
         <v>247180</v>
@@ -21162,7 +21162,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G717" t="n">
-        <v>23.5698127746582</v>
+        <v>23.5698108673096</v>
       </c>
       <c r="H717" t="n">
         <v>93420</v>
@@ -21191,7 +21191,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G718" t="n">
-        <v>22.7803936004639</v>
+        <v>22.7803916931152</v>
       </c>
       <c r="H718" t="n">
         <v>194347</v>
@@ -21220,7 +21220,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G719" t="n">
-        <v>22.9871463775635</v>
+        <v>22.9871444702148</v>
       </c>
       <c r="H719" t="n">
         <v>215638</v>
@@ -21278,7 +21278,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G721" t="n">
-        <v>23.0623321533203</v>
+        <v>23.062328338623</v>
       </c>
       <c r="H721" t="n">
         <v>131570</v>
@@ -21307,7 +21307,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G722" t="n">
-        <v>23.8893413543701</v>
+        <v>23.8893394470215</v>
       </c>
       <c r="H722" t="n">
         <v>145719</v>
@@ -21336,7 +21336,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G723" t="n">
-        <v>23.945728302002</v>
+        <v>23.9457244873047</v>
       </c>
       <c r="H723" t="n">
         <v>76074</v>
@@ -21365,7 +21365,7 @@
         <v>25.5</v>
       </c>
       <c r="G724" t="n">
-        <v>23.9645252227783</v>
+        <v>23.9645233154297</v>
       </c>
       <c r="H724" t="n">
         <v>154815</v>
@@ -21394,7 +21394,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G725" t="n">
-        <v>23.945728302002</v>
+        <v>23.9457244873047</v>
       </c>
       <c r="H725" t="n">
         <v>72163</v>
@@ -21423,7 +21423,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G726" t="n">
-        <v>23.926929473877</v>
+        <v>23.9269313812256</v>
       </c>
       <c r="H726" t="n">
         <v>135737</v>
@@ -21510,7 +21510,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G729" t="n">
-        <v>25.5809535980225</v>
+        <v>25.5809497833252</v>
       </c>
       <c r="H729" t="n">
         <v>383489</v>
@@ -21568,7 +21568,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>25.2802200317383</v>
+        <v>25.2802238464355</v>
       </c>
       <c r="H731" t="n">
         <v>868214</v>
@@ -21597,7 +21597,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G732" t="n">
-        <v>24.622371673584</v>
+        <v>24.6223773956299</v>
       </c>
       <c r="H732" t="n">
         <v>316042</v>
@@ -21655,7 +21655,7 @@
         <v>27</v>
       </c>
       <c r="G734" t="n">
-        <v>25.3741989135742</v>
+        <v>25.3742008209229</v>
       </c>
       <c r="H734" t="n">
         <v>86244</v>
@@ -21713,7 +21713,7 @@
         <v>26.8799991607666</v>
       </c>
       <c r="G736" t="n">
-        <v>25.2614269256592</v>
+        <v>25.2614250183105</v>
       </c>
       <c r="H736" t="n">
         <v>180102</v>
@@ -21742,7 +21742,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G737" t="n">
-        <v>25.411792755127</v>
+        <v>25.4117965698242</v>
       </c>
       <c r="H737" t="n">
         <v>146278</v>
@@ -21771,7 +21771,7 @@
         <v>25.9200000762939</v>
       </c>
       <c r="G738" t="n">
-        <v>24.3592338562012</v>
+        <v>24.3592357635498</v>
       </c>
       <c r="H738" t="n">
         <v>304231</v>
@@ -21800,7 +21800,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G739" t="n">
-        <v>24.3780288696289</v>
+        <v>24.3780269622803</v>
       </c>
       <c r="H739" t="n">
         <v>171556</v>
@@ -21887,7 +21887,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G742" t="n">
-        <v>24.9231052398682</v>
+        <v>24.9231033325195</v>
       </c>
       <c r="H742" t="n">
         <v>193565</v>
@@ -21916,7 +21916,7 @@
         <v>26.0599994659424</v>
       </c>
       <c r="G743" t="n">
-        <v>24.4908027648926</v>
+        <v>24.4908046722412</v>
       </c>
       <c r="H743" t="n">
         <v>184013</v>
@@ -21945,7 +21945,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G744" t="n">
-        <v>24.2276630401611</v>
+        <v>24.2276611328125</v>
       </c>
       <c r="H744" t="n">
         <v>120421</v>
@@ -21974,7 +21974,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G745" t="n">
-        <v>24.84792137146</v>
+        <v>24.8479232788086</v>
       </c>
       <c r="H745" t="n">
         <v>202100</v>
@@ -22003,7 +22003,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G746" t="n">
-        <v>24.6411685943604</v>
+        <v>24.6411647796631</v>
       </c>
       <c r="H746" t="n">
         <v>161938</v>
@@ -22119,7 +22119,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G750" t="n">
-        <v>23.926929473877</v>
+        <v>23.9269313812256</v>
       </c>
       <c r="H750" t="n">
         <v>310493</v>
@@ -22148,7 +22148,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G751" t="n">
-        <v>24.1712760925293</v>
+        <v>24.1712779998779</v>
       </c>
       <c r="H751" t="n">
         <v>154616</v>
@@ -22177,7 +22177,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G752" t="n">
-        <v>23.4382457733154</v>
+        <v>23.4382400512695</v>
       </c>
       <c r="H752" t="n">
         <v>277706</v>
@@ -22206,7 +22206,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G753" t="n">
-        <v>24.0021171569824</v>
+        <v>24.0021152496338</v>
       </c>
       <c r="H753" t="n">
         <v>245029</v>
@@ -22235,7 +22235,7 @@
         <v>26</v>
       </c>
       <c r="G754" t="n">
-        <v>24.4344158172607</v>
+        <v>24.4344177246094</v>
       </c>
       <c r="H754" t="n">
         <v>144024</v>
@@ -22264,7 +22264,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G755" t="n">
-        <v>24.5659866333008</v>
+        <v>24.5659847259521</v>
       </c>
       <c r="H755" t="n">
         <v>83822</v>
@@ -22293,7 +22293,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G756" t="n">
-        <v>24.0397033691406</v>
+        <v>24.0397071838379</v>
       </c>
       <c r="H756" t="n">
         <v>155187</v>
@@ -22322,7 +22322,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G757" t="n">
-        <v>23.6449928283691</v>
+        <v>23.6449947357178</v>
       </c>
       <c r="H757" t="n">
         <v>190289</v>
@@ -22351,7 +22351,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G758" t="n">
-        <v>23.62619972229</v>
+        <v>23.6261978149414</v>
       </c>
       <c r="H758" t="n">
         <v>127185</v>
@@ -22380,7 +22380,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G759" t="n">
-        <v>24.0397033691406</v>
+        <v>24.0397071838379</v>
       </c>
       <c r="H759" t="n">
         <v>244285</v>
@@ -22409,7 +22409,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G760" t="n">
-        <v>23.7389736175537</v>
+        <v>23.7389755249023</v>
       </c>
       <c r="H760" t="n">
         <v>158306</v>
@@ -22438,7 +22438,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G761" t="n">
-        <v>23.4194469451904</v>
+        <v>23.4194488525391</v>
       </c>
       <c r="H761" t="n">
         <v>794698</v>
@@ -22467,7 +22467,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G762" t="n">
-        <v>23.8893413543701</v>
+        <v>23.8893394470215</v>
       </c>
       <c r="H762" t="n">
         <v>252947</v>
@@ -22496,7 +22496,7 @@
         <v>26</v>
       </c>
       <c r="G763" t="n">
-        <v>24.4344158172607</v>
+        <v>24.4344177246094</v>
       </c>
       <c r="H763" t="n">
         <v>204816</v>
@@ -22525,7 +22525,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G764" t="n">
-        <v>24.753942489624</v>
+        <v>24.7539463043213</v>
       </c>
       <c r="H764" t="n">
         <v>208124</v>
@@ -22583,7 +22583,7 @@
         <v>27</v>
       </c>
       <c r="G766" t="n">
-        <v>25.3741989135742</v>
+        <v>25.3742008209229</v>
       </c>
       <c r="H766" t="n">
         <v>165799</v>
@@ -22612,7 +22612,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G767" t="n">
-        <v>25.5809535980225</v>
+        <v>25.5809497833252</v>
       </c>
       <c r="H767" t="n">
         <v>135144</v>
@@ -22670,7 +22670,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G769" t="n">
-        <v>26.1824150085449</v>
+        <v>26.1824188232422</v>
       </c>
       <c r="H769" t="n">
         <v>227413</v>
@@ -22815,7 +22815,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>25.9192752838135</v>
+        <v>25.9192771911621</v>
       </c>
       <c r="H774" t="n">
         <v>143865</v>
@@ -22844,7 +22844,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G775" t="n">
-        <v>26.3891677856445</v>
+        <v>26.3891658782959</v>
       </c>
       <c r="H775" t="n">
         <v>121548</v>
@@ -22931,7 +22931,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>26.4455547332764</v>
+        <v>26.445556640625</v>
       </c>
       <c r="H778" t="n">
         <v>86979</v>
@@ -22960,7 +22960,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G779" t="n">
-        <v>26.7086982727051</v>
+        <v>26.7086944580078</v>
       </c>
       <c r="H779" t="n">
         <v>151038</v>
@@ -23163,7 +23163,7 @@
         <v>27.9799995422363</v>
       </c>
       <c r="G786" t="n">
-        <v>26.2951908111572</v>
+        <v>26.2951889038086</v>
       </c>
       <c r="H786" t="n">
         <v>183895</v>
@@ -23192,7 +23192,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G787" t="n">
-        <v>26.2763957977295</v>
+        <v>26.2763919830322</v>
       </c>
       <c r="H787" t="n">
         <v>159402</v>
@@ -23279,7 +23279,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>26.2200088500977</v>
+        <v>26.220006942749</v>
       </c>
       <c r="H790" t="n">
         <v>137880</v>
@@ -23308,7 +23308,7 @@
         <v>27.4200000762939</v>
       </c>
       <c r="G791" t="n">
-        <v>25.768913269043</v>
+        <v>25.7689113616943</v>
       </c>
       <c r="H791" t="n">
         <v>115443</v>
@@ -23337,7 +23337,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G792" t="n">
-        <v>26.2012119293213</v>
+        <v>26.2012100219727</v>
       </c>
       <c r="H792" t="n">
         <v>117985</v>
@@ -23366,7 +23366,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G793" t="n">
-        <v>26.5019435882568</v>
+        <v>26.5019474029541</v>
       </c>
       <c r="H793" t="n">
         <v>104826</v>
@@ -23395,7 +23395,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G794" t="n">
-        <v>25.3554058074951</v>
+        <v>25.3554039001465</v>
       </c>
       <c r="H794" t="n">
         <v>416033</v>
@@ -23424,7 +23424,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G795" t="n">
-        <v>26.8590621948242</v>
+        <v>26.8590602874756</v>
       </c>
       <c r="H795" t="n">
         <v>788074</v>
@@ -23453,7 +23453,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G796" t="n">
-        <v>26.9718399047852</v>
+        <v>26.9718379974365</v>
       </c>
       <c r="H796" t="n">
         <v>434902</v>
@@ -23482,7 +23482,7 @@
         <v>29.1200008392334</v>
       </c>
       <c r="G797" t="n">
-        <v>27.3665466308594</v>
+        <v>27.3665428161621</v>
       </c>
       <c r="H797" t="n">
         <v>390105</v>
@@ -23511,7 +23511,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G798" t="n">
-        <v>26.9530372619629</v>
+        <v>26.9530391693115</v>
       </c>
       <c r="H798" t="n">
         <v>233060</v>
@@ -23598,7 +23598,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G801" t="n">
-        <v>26.7086982727051</v>
+        <v>26.7086944580078</v>
       </c>
       <c r="H801" t="n">
         <v>93853</v>
@@ -23627,7 +23627,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>27.0658111572266</v>
+        <v>27.0658130645752</v>
       </c>
       <c r="H802" t="n">
         <v>190105</v>
@@ -23656,7 +23656,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G803" t="n">
-        <v>27.0094242095947</v>
+        <v>27.009428024292</v>
       </c>
       <c r="H803" t="n">
         <v>153108</v>
@@ -23859,7 +23859,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G810" t="n">
-        <v>26.2388000488281</v>
+        <v>26.2388038635254</v>
       </c>
       <c r="H810" t="n">
         <v>157514</v>
@@ -23888,7 +23888,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G811" t="n">
-        <v>25.7501125335693</v>
+        <v>25.750114440918</v>
       </c>
       <c r="H811" t="n">
         <v>184431</v>
@@ -23917,7 +23917,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G812" t="n">
-        <v>25.9192752838135</v>
+        <v>25.9192771911621</v>
       </c>
       <c r="H812" t="n">
         <v>147304</v>
@@ -23975,7 +23975,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>26.2200088500977</v>
+        <v>26.220006942749</v>
       </c>
       <c r="H814" t="n">
         <v>251300</v>
@@ -24120,7 +24120,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>26.6898994445801</v>
+        <v>26.6899032592773</v>
       </c>
       <c r="H819" t="n">
         <v>151739</v>
@@ -24149,7 +24149,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G820" t="n">
-        <v>27.4229335784912</v>
+        <v>27.4229316711426</v>
       </c>
       <c r="H820" t="n">
         <v>403665</v>
@@ -24178,7 +24178,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G821" t="n">
-        <v>26.9718399047852</v>
+        <v>26.9718379974365</v>
       </c>
       <c r="H821" t="n">
         <v>272697</v>
@@ -24207,7 +24207,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>26.6898994445801</v>
+        <v>26.6899032592773</v>
       </c>
       <c r="H822" t="n">
         <v>158251</v>
@@ -24236,7 +24236,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G823" t="n">
-        <v>26.8966541290283</v>
+        <v>26.8966522216797</v>
       </c>
       <c r="H823" t="n">
         <v>180944</v>
@@ -24265,7 +24265,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G824" t="n">
-        <v>26.5771236419678</v>
+        <v>26.5771255493164</v>
       </c>
       <c r="H824" t="n">
         <v>249547</v>
@@ -24294,7 +24294,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G825" t="n">
-        <v>26.5771236419678</v>
+        <v>26.5771255493164</v>
       </c>
       <c r="H825" t="n">
         <v>114618</v>
@@ -24323,7 +24323,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G826" t="n">
-        <v>27.328950881958</v>
+        <v>27.3289527893066</v>
       </c>
       <c r="H826" t="n">
         <v>273361</v>
@@ -24352,7 +24352,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>27.8176403045654</v>
+        <v>27.8176422119141</v>
       </c>
       <c r="H827" t="n">
         <v>354450</v>
@@ -24381,7 +24381,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G828" t="n">
-        <v>28.2875347137451</v>
+        <v>28.2875366210938</v>
       </c>
       <c r="H828" t="n">
         <v>498651</v>
@@ -24410,7 +24410,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G829" t="n">
-        <v>29.0581607818604</v>
+        <v>29.0581588745117</v>
       </c>
       <c r="H829" t="n">
         <v>462618</v>
@@ -24439,7 +24439,7 @@
         <v>30.9599990844727</v>
       </c>
       <c r="G830" t="n">
-        <v>29.0957489013672</v>
+        <v>29.0957508087158</v>
       </c>
       <c r="H830" t="n">
         <v>306081</v>
@@ -24526,7 +24526,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G833" t="n">
-        <v>29.5656452178955</v>
+        <v>29.5656433105469</v>
       </c>
       <c r="H833" t="n">
         <v>373173</v>
@@ -24555,7 +24555,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G834" t="n">
-        <v>29.7160091400146</v>
+        <v>29.716007232666</v>
       </c>
       <c r="H834" t="n">
         <v>223269</v>
@@ -24613,7 +24613,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G836" t="n">
-        <v>30.1295146942139</v>
+        <v>30.1295127868652</v>
       </c>
       <c r="H836" t="n">
         <v>229985</v>
@@ -24642,7 +24642,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G837" t="n">
-        <v>30.6369972229004</v>
+        <v>30.6369953155518</v>
       </c>
       <c r="H837" t="n">
         <v>307079</v>
@@ -24671,7 +24671,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G838" t="n">
-        <v>30.6745853424072</v>
+        <v>30.6745872497559</v>
       </c>
       <c r="H838" t="n">
         <v>249987</v>
@@ -24700,7 +24700,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G839" t="n">
-        <v>30.824951171875</v>
+        <v>30.8249530792236</v>
       </c>
       <c r="H839" t="n">
         <v>213168</v>
@@ -24729,7 +24729,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G840" t="n">
-        <v>30.5806159973145</v>
+        <v>30.5806121826172</v>
       </c>
       <c r="H840" t="n">
         <v>200186</v>
@@ -24758,7 +24758,7 @@
         <v>32.8400001525879</v>
       </c>
       <c r="G841" t="n">
-        <v>30.8625469207764</v>
+        <v>30.8625450134277</v>
       </c>
       <c r="H841" t="n">
         <v>144181</v>
@@ -24816,7 +24816,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G843" t="n">
-        <v>31.2572574615479</v>
+        <v>31.2572555541992</v>
       </c>
       <c r="H843" t="n">
         <v>217282</v>
@@ -24845,7 +24845,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G844" t="n">
-        <v>31.2572574615479</v>
+        <v>31.2572555541992</v>
       </c>
       <c r="H844" t="n">
         <v>220052</v>
@@ -24932,7 +24932,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G847" t="n">
-        <v>31.2948436737061</v>
+        <v>31.2948474884033</v>
       </c>
       <c r="H847" t="n">
         <v>262113</v>
@@ -24961,7 +24961,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G848" t="n">
-        <v>31.0317058563232</v>
+        <v>31.0317096710205</v>
       </c>
       <c r="H848" t="n">
         <v>263305</v>
@@ -24990,7 +24990,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G849" t="n">
-        <v>29.9791488647461</v>
+        <v>29.9791469573975</v>
       </c>
       <c r="H849" t="n">
         <v>389764</v>
@@ -25048,7 +25048,7 @@
         <v>32.5</v>
       </c>
       <c r="G851" t="n">
-        <v>30.5430221557617</v>
+        <v>30.5430183410645</v>
       </c>
       <c r="H851" t="n">
         <v>147865</v>
@@ -25077,7 +25077,7 @@
         <v>31.6599998474121</v>
       </c>
       <c r="G852" t="n">
-        <v>29.7536029815674</v>
+        <v>29.7536010742188</v>
       </c>
       <c r="H852" t="n">
         <v>247192</v>
@@ -25135,7 +25135,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G854" t="n">
-        <v>26.4455547332764</v>
+        <v>26.445556640625</v>
       </c>
       <c r="H854" t="n">
         <v>712987</v>
@@ -25193,7 +25193,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G856" t="n">
-        <v>26.3703708648682</v>
+        <v>26.3703746795654</v>
       </c>
       <c r="H856" t="n">
         <v>527466</v>
@@ -25222,7 +25222,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G857" t="n">
-        <v>26.2388000488281</v>
+        <v>26.2388038635254</v>
       </c>
       <c r="H857" t="n">
         <v>406587</v>
@@ -25251,7 +25251,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>26.2200088500977</v>
+        <v>26.220006942749</v>
       </c>
       <c r="H858" t="n">
         <v>245239</v>
@@ -25309,7 +25309,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>25.9547729492188</v>
+        <v>25.9547748565674</v>
       </c>
       <c r="H860" t="n">
         <v>361156</v>
@@ -25454,7 +25454,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G865" t="n">
-        <v>26.0684452056885</v>
+        <v>26.0684471130371</v>
       </c>
       <c r="H865" t="n">
         <v>190131</v>
@@ -25483,7 +25483,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G866" t="n">
-        <v>25.3674793243408</v>
+        <v>25.3674774169922</v>
       </c>
       <c r="H866" t="n">
         <v>248956</v>
@@ -25512,7 +25512,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G867" t="n">
-        <v>24.8180694580078</v>
+        <v>24.8180732727051</v>
       </c>
       <c r="H867" t="n">
         <v>432544</v>
@@ -25541,7 +25541,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G868" t="n">
-        <v>24.7801780700684</v>
+        <v>24.780179977417</v>
       </c>
       <c r="H868" t="n">
         <v>243692</v>
@@ -25599,7 +25599,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G870" t="n">
-        <v>25.2727546691895</v>
+        <v>25.2727527618408</v>
       </c>
       <c r="H870" t="n">
         <v>443807</v>
@@ -25628,7 +25628,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>25.3864231109619</v>
+        <v>25.3864212036133</v>
       </c>
       <c r="H871" t="n">
         <v>376395</v>
@@ -25802,7 +25802,7 @@
         <v>27.2399997711182</v>
       </c>
       <c r="G877" t="n">
-        <v>25.8032150268555</v>
+        <v>25.8032169342041</v>
       </c>
       <c r="H877" t="n">
         <v>229656</v>
@@ -25860,7 +25860,7 @@
         <v>26.8600006103516</v>
       </c>
       <c r="G879" t="n">
-        <v>25.4432582855225</v>
+        <v>25.4432563781738</v>
       </c>
       <c r="H879" t="n">
         <v>279093</v>
@@ -25918,7 +25918,7 @@
         <v>27.2399997711182</v>
       </c>
       <c r="G881" t="n">
-        <v>25.8032150268555</v>
+        <v>25.8032169342041</v>
       </c>
       <c r="H881" t="n">
         <v>310823</v>
@@ -25976,7 +25976,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G883" t="n">
-        <v>25.7842693328857</v>
+        <v>25.7842655181885</v>
       </c>
       <c r="H883" t="n">
         <v>284952</v>
@@ -26005,7 +26005,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G884" t="n">
-        <v>25.5569267272949</v>
+        <v>25.5569286346436</v>
       </c>
       <c r="H884" t="n">
         <v>139322</v>
@@ -26266,7 +26266,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G893" t="n">
-        <v>26.0684452056885</v>
+        <v>26.0684471130371</v>
       </c>
       <c r="H893" t="n">
         <v>365065</v>
@@ -26382,7 +26382,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G897" t="n">
-        <v>24.6665096282959</v>
+        <v>24.6665077209473</v>
       </c>
       <c r="H897" t="n">
         <v>186080</v>
@@ -26411,7 +26411,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G898" t="n">
-        <v>24.7612342834473</v>
+        <v>24.7612323760986</v>
       </c>
       <c r="H898" t="n">
         <v>150697</v>
@@ -26440,7 +26440,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G899" t="n">
-        <v>25.1401348114014</v>
+        <v>25.1401405334473</v>
       </c>
       <c r="H899" t="n">
         <v>298881</v>
@@ -26469,7 +26469,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>25.3864231109619</v>
+        <v>25.3864212036133</v>
       </c>
       <c r="H900" t="n">
         <v>166235</v>
@@ -26527,7 +26527,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G902" t="n">
-        <v>24.8180694580078</v>
+        <v>24.8180732727051</v>
       </c>
       <c r="H902" t="n">
         <v>177888</v>
@@ -26585,7 +26585,7 @@
         <v>25.9200000762939</v>
       </c>
       <c r="G904" t="n">
-        <v>24.5528411865234</v>
+        <v>24.5528430938721</v>
       </c>
       <c r="H904" t="n">
         <v>154403</v>
@@ -26701,7 +26701,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G908" t="n">
-        <v>24.6665096282959</v>
+        <v>24.6665077209473</v>
       </c>
       <c r="H908" t="n">
         <v>179146</v>
@@ -26759,7 +26759,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>23.8708171844482</v>
+        <v>23.870813369751</v>
       </c>
       <c r="H910" t="n">
         <v>248984</v>
@@ -26788,7 +26788,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G911" t="n">
-        <v>24.1360473632812</v>
+        <v>24.1360454559326</v>
       </c>
       <c r="H911" t="n">
         <v>176259</v>
@@ -26817,7 +26817,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G912" t="n">
-        <v>24.1739387512207</v>
+        <v>24.1739368438721</v>
       </c>
       <c r="H912" t="n">
         <v>159748</v>
@@ -26875,7 +26875,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G914" t="n">
-        <v>24.7422904968262</v>
+        <v>24.7422885894775</v>
       </c>
       <c r="H914" t="n">
         <v>411750</v>
@@ -26904,7 +26904,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G915" t="n">
-        <v>23.6624183654785</v>
+        <v>23.6624202728271</v>
       </c>
       <c r="H915" t="n">
         <v>354511</v>
@@ -26962,7 +26962,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G917" t="n">
-        <v>24.2876071929932</v>
+        <v>24.2876033782959</v>
       </c>
       <c r="H917" t="n">
         <v>179973</v>
@@ -26991,7 +26991,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G918" t="n">
-        <v>23.624532699585</v>
+        <v>23.6245288848877</v>
       </c>
       <c r="H918" t="n">
         <v>162608</v>
@@ -27020,7 +27020,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G919" t="n">
-        <v>23.4729690551758</v>
+        <v>23.4729709625244</v>
       </c>
       <c r="H919" t="n">
         <v>78348</v>
@@ -27107,7 +27107,7 @@
         <v>24.5</v>
       </c>
       <c r="G922" t="n">
-        <v>23.2077350616455</v>
+        <v>23.2077388763428</v>
       </c>
       <c r="H922" t="n">
         <v>143739</v>
@@ -27165,7 +27165,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G924" t="n">
-        <v>23.624532699585</v>
+        <v>23.6245288848877</v>
       </c>
       <c r="H924" t="n">
         <v>118263</v>
@@ -27194,7 +27194,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G925" t="n">
-        <v>24.4012775421143</v>
+        <v>24.4012794494629</v>
       </c>
       <c r="H925" t="n">
         <v>179334</v>
@@ -27223,7 +27223,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G926" t="n">
-        <v>24.3254985809326</v>
+        <v>24.325496673584</v>
       </c>
       <c r="H926" t="n">
         <v>172578</v>
@@ -27281,7 +27281,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G928" t="n">
-        <v>23.6624183654785</v>
+        <v>23.6624202728271</v>
       </c>
       <c r="H928" t="n">
         <v>116505</v>
@@ -27310,7 +27310,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G929" t="n">
-        <v>23.9276504516602</v>
+        <v>23.9276523590088</v>
       </c>
       <c r="H929" t="n">
         <v>116984</v>
@@ -27339,7 +27339,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G930" t="n">
-        <v>23.7192535400391</v>
+        <v>23.7192554473877</v>
       </c>
       <c r="H930" t="n">
         <v>251927</v>
@@ -27368,7 +27368,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G931" t="n">
-        <v>24.3254985809326</v>
+        <v>24.325496673584</v>
       </c>
       <c r="H931" t="n">
         <v>167992</v>
@@ -27455,7 +27455,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G934" t="n">
-        <v>24.6096725463867</v>
+        <v>24.6096706390381</v>
       </c>
       <c r="H934" t="n">
         <v>108161</v>
@@ -27484,7 +27484,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G935" t="n">
-        <v>25.0454139709473</v>
+        <v>25.0454120635986</v>
       </c>
       <c r="H935" t="n">
         <v>311460</v>
@@ -27542,7 +27542,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G937" t="n">
-        <v>25.8411045074463</v>
+        <v>25.8411064147949</v>
       </c>
       <c r="H937" t="n">
         <v>341715</v>
@@ -27571,7 +27571,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G938" t="n">
-        <v>26.4473457336426</v>
+        <v>26.4473476409912</v>
       </c>
       <c r="H938" t="n">
         <v>635855</v>
@@ -27629,7 +27629,7 @@
         <v>28.5</v>
       </c>
       <c r="G940" t="n">
-        <v>26.996753692627</v>
+        <v>26.9967555999756</v>
       </c>
       <c r="H940" t="n">
         <v>495066</v>
@@ -27658,7 +27658,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G941" t="n">
-        <v>27.1104278564453</v>
+        <v>27.1104259490967</v>
       </c>
       <c r="H941" t="n">
         <v>276869</v>
@@ -27687,7 +27687,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G942" t="n">
-        <v>27.4514389038086</v>
+        <v>27.45143699646</v>
       </c>
       <c r="H942" t="n">
         <v>229694</v>
@@ -27716,7 +27716,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G943" t="n">
-        <v>27.2998752593994</v>
+        <v>27.299877166748</v>
       </c>
       <c r="H943" t="n">
         <v>206597</v>
@@ -27774,7 +27774,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G945" t="n">
-        <v>27.1104278564453</v>
+        <v>27.1104259490967</v>
       </c>
       <c r="H945" t="n">
         <v>167753</v>
@@ -27803,7 +27803,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>27.2809295654297</v>
+        <v>27.2809314727783</v>
       </c>
       <c r="H946" t="n">
         <v>203759</v>
@@ -27832,7 +27832,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G947" t="n">
-        <v>27.2619895935059</v>
+        <v>27.2619876861572</v>
       </c>
       <c r="H947" t="n">
         <v>290836</v>
@@ -27861,7 +27861,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G948" t="n">
-        <v>26.7125797271729</v>
+        <v>26.7125816345215</v>
       </c>
       <c r="H948" t="n">
         <v>239270</v>
@@ -27890,7 +27890,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G949" t="n">
-        <v>26.655740737915</v>
+        <v>26.6557426452637</v>
       </c>
       <c r="H949" t="n">
         <v>262802</v>
@@ -27919,7 +27919,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G950" t="n">
-        <v>26.390510559082</v>
+        <v>26.3905143737793</v>
       </c>
       <c r="H950" t="n">
         <v>368520</v>
@@ -27948,7 +27948,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G951" t="n">
-        <v>26.6936359405518</v>
+        <v>26.6936340332031</v>
       </c>
       <c r="H951" t="n">
         <v>166272</v>
@@ -27977,7 +27977,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G952" t="n">
-        <v>27.2809295654297</v>
+        <v>27.2809314727783</v>
       </c>
       <c r="H952" t="n">
         <v>232493</v>
@@ -28006,7 +28006,7 @@
         <v>29</v>
       </c>
       <c r="G953" t="n">
-        <v>27.4703826904297</v>
+        <v>27.4703807830811</v>
       </c>
       <c r="H953" t="n">
         <v>252521</v>
@@ -28093,7 +28093,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G956" t="n">
-        <v>25.4811477661133</v>
+        <v>25.4811496734619</v>
       </c>
       <c r="H956" t="n">
         <v>270449</v>
@@ -28151,7 +28151,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G958" t="n">
-        <v>25.9547729492188</v>
+        <v>25.9547748565674</v>
       </c>
       <c r="H958" t="n">
         <v>180194</v>
@@ -28180,7 +28180,7 @@
         <v>26.8799991607666</v>
       </c>
       <c r="G959" t="n">
-        <v>25.4622020721436</v>
+        <v>25.4622001647949</v>
       </c>
       <c r="H959" t="n">
         <v>206520</v>
@@ -28209,7 +28209,7 @@
         <v>27</v>
       </c>
       <c r="G960" t="n">
-        <v>25.5758724212646</v>
+        <v>25.5758743286133</v>
       </c>
       <c r="H960" t="n">
         <v>188374</v>
@@ -28267,7 +28267,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G962" t="n">
-        <v>26.3526229858398</v>
+        <v>26.3526210784912</v>
       </c>
       <c r="H962" t="n">
         <v>161957</v>
@@ -28296,7 +28296,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G963" t="n">
-        <v>26.4473457336426</v>
+        <v>26.4473476409912</v>
       </c>
       <c r="H963" t="n">
         <v>362958</v>
@@ -28325,7 +28325,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G964" t="n">
-        <v>24.3254985809326</v>
+        <v>24.325496673584</v>
       </c>
       <c r="H964" t="n">
         <v>1267380</v>
@@ -28441,7 +28441,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G968" t="n">
-        <v>24.0413188934326</v>
+        <v>24.0413208007812</v>
       </c>
       <c r="H968" t="n">
         <v>362334</v>
@@ -28470,7 +28470,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>24.3065509796143</v>
+        <v>24.3065528869629</v>
       </c>
       <c r="H969" t="n">
         <v>697776</v>
@@ -28499,7 +28499,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>24.060266494751</v>
+        <v>24.0602645874023</v>
       </c>
       <c r="H970" t="n">
         <v>183027</v>
@@ -28528,7 +28528,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G971" t="n">
-        <v>24.3633880615234</v>
+        <v>24.3633899688721</v>
       </c>
       <c r="H971" t="n">
         <v>149732</v>
@@ -28586,7 +28586,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>24.3254985809326</v>
+        <v>24.325496673584</v>
       </c>
       <c r="H973" t="n">
         <v>222479</v>
@@ -28615,7 +28615,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G974" t="n">
-        <v>23.7192535400391</v>
+        <v>23.7192554473877</v>
       </c>
       <c r="H974" t="n">
         <v>342801</v>
@@ -28673,7 +28673,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G976" t="n">
-        <v>23.2645702362061</v>
+        <v>23.2645740509033</v>
       </c>
       <c r="H976" t="n">
         <v>315490</v>
@@ -28702,7 +28702,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G977" t="n">
-        <v>23.6624183654785</v>
+        <v>23.6624202728271</v>
       </c>
       <c r="H977" t="n">
         <v>149145</v>
@@ -28731,7 +28731,7 @@
         <v>25.9599990844727</v>
       </c>
       <c r="G978" t="n">
-        <v>24.590726852417</v>
+        <v>24.5907287597656</v>
       </c>
       <c r="H978" t="n">
         <v>371938</v>
@@ -28760,7 +28760,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G979" t="n">
-        <v>24.8938541412354</v>
+        <v>24.8938503265381</v>
       </c>
       <c r="H979" t="n">
         <v>398178</v>
@@ -28818,7 +28818,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G981" t="n">
-        <v>25.5000915527344</v>
+        <v>25.500093460083</v>
       </c>
       <c r="H981" t="n">
         <v>357348</v>
@@ -28847,7 +28847,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G982" t="n">
-        <v>25.8789939880371</v>
+        <v>25.8789958953857</v>
       </c>
       <c r="H982" t="n">
         <v>480228</v>
@@ -28876,7 +28876,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G983" t="n">
-        <v>25.6895427703857</v>
+        <v>25.6895446777344</v>
       </c>
       <c r="H983" t="n">
         <v>251674</v>
@@ -28963,7 +28963,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G986" t="n">
-        <v>25.3674793243408</v>
+        <v>25.3674774169922</v>
       </c>
       <c r="H986" t="n">
         <v>246782</v>
@@ -28992,7 +28992,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G987" t="n">
-        <v>25.5948219299316</v>
+        <v>25.5948181152344</v>
       </c>
       <c r="H987" t="n">
         <v>202426</v>
@@ -29021,7 +29021,7 @@
         <v>26.8600006103516</v>
       </c>
       <c r="G988" t="n">
-        <v>25.4432582855225</v>
+        <v>25.4432563781738</v>
       </c>
       <c r="H988" t="n">
         <v>135841</v>
@@ -29079,7 +29079,7 @@
         <v>26.8600006103516</v>
       </c>
       <c r="G990" t="n">
-        <v>25.4432582855225</v>
+        <v>25.4432563781738</v>
       </c>
       <c r="H990" t="n">
         <v>175526</v>
@@ -29108,7 +29108,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G991" t="n">
-        <v>25.1401348114014</v>
+        <v>25.1401405334473</v>
       </c>
       <c r="H991" t="n">
         <v>215206</v>
@@ -29137,7 +29137,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G992" t="n">
-        <v>25.1401348114014</v>
+        <v>25.1401405334473</v>
       </c>
       <c r="H992" t="n">
         <v>247345</v>
@@ -29253,7 +29253,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G996" t="n">
-        <v>27.1862087249756</v>
+        <v>27.186206817627</v>
       </c>
       <c r="H996" t="n">
         <v>479565</v>
@@ -29282,7 +29282,7 @@
         <v>28.3600006103516</v>
       </c>
       <c r="G997" t="n">
-        <v>26.8641395568848</v>
+        <v>26.8641414642334</v>
       </c>
       <c r="H997" t="n">
         <v>340599</v>
@@ -29311,7 +29311,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G998" t="n">
-        <v>26.390510559082</v>
+        <v>26.3905143737793</v>
       </c>
       <c r="H998" t="n">
         <v>207116</v>
@@ -29427,7 +29427,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1002" t="n">
-        <v>26.4094562530518</v>
+        <v>26.4094543457031</v>
       </c>
       <c r="H1002" t="n">
         <v>167323</v>
@@ -29456,7 +29456,7 @@
         <v>27.5400009155273</v>
       </c>
       <c r="G1003" t="n">
-        <v>26.0873928070068</v>
+        <v>26.0873908996582</v>
       </c>
       <c r="H1003" t="n">
         <v>97826</v>
@@ -29514,7 +29514,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G1005" t="n">
-        <v>25.8411045074463</v>
+        <v>25.8411064147949</v>
       </c>
       <c r="H1005" t="n">
         <v>132463</v>
@@ -29572,7 +29572,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1007" t="n">
-        <v>26.7315235137939</v>
+        <v>26.7315254211426</v>
       </c>
       <c r="H1007" t="n">
         <v>321623</v>
@@ -29601,7 +29601,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1008" t="n">
-        <v>26.7315235137939</v>
+        <v>26.7315254211426</v>
       </c>
       <c r="H1008" t="n">
         <v>100641</v>
@@ -29630,7 +29630,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1009" t="n">
-        <v>26.4852390289307</v>
+        <v>26.4852352142334</v>
       </c>
       <c r="H1009" t="n">
         <v>133137</v>
@@ -29688,7 +29688,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G1011" t="n">
-        <v>26.3526229858398</v>
+        <v>26.3526210784912</v>
       </c>
       <c r="H1011" t="n">
         <v>177836</v>
@@ -29717,7 +29717,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>26.4473457336426</v>
+        <v>26.4473476409912</v>
       </c>
       <c r="H1012" t="n">
         <v>185048</v>
@@ -29746,7 +29746,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>26.7125797271729</v>
+        <v>26.7125816345215</v>
       </c>
       <c r="H1013" t="n">
         <v>107123</v>
@@ -29775,7 +29775,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1014" t="n">
-        <v>26.7504711151123</v>
+        <v>26.7504692077637</v>
       </c>
       <c r="H1014" t="n">
         <v>150214</v>
@@ -29804,7 +29804,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1015" t="n">
-        <v>26.7504711151123</v>
+        <v>26.7504692077637</v>
       </c>
       <c r="H1015" t="n">
         <v>98243</v>
@@ -29833,7 +29833,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1016" t="n">
-        <v>27.6598339080811</v>
+        <v>27.6598320007324</v>
       </c>
       <c r="H1016" t="n">
         <v>419116</v>
@@ -29862,7 +29862,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1017" t="n">
-        <v>27.2240943908691</v>
+        <v>27.2240982055664</v>
       </c>
       <c r="H1017" t="n">
         <v>181176</v>
@@ -29891,7 +29891,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1018" t="n">
-        <v>26.7504711151123</v>
+        <v>26.7504692077637</v>
       </c>
       <c r="H1018" t="n">
         <v>146261</v>
@@ -29949,7 +29949,7 @@
         <v>28.5</v>
       </c>
       <c r="G1020" t="n">
-        <v>26.996753692627</v>
+        <v>26.9967555999756</v>
       </c>
       <c r="H1020" t="n">
         <v>132754</v>
@@ -29978,7 +29978,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1021" t="n">
-        <v>27.35671043396</v>
+        <v>27.3567123413086</v>
       </c>
       <c r="H1021" t="n">
         <v>157348</v>
@@ -30007,7 +30007,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>26.939920425415</v>
+        <v>26.9399185180664</v>
       </c>
       <c r="H1022" t="n">
         <v>116088</v>
@@ -30036,7 +30036,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1023" t="n">
-        <v>27.2619895935059</v>
+        <v>27.2619876861572</v>
       </c>
       <c r="H1023" t="n">
         <v>74030</v>
@@ -30065,7 +30065,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G1024" t="n">
-        <v>27.2430438995361</v>
+        <v>27.2430419921875</v>
       </c>
       <c r="H1024" t="n">
         <v>148130</v>
@@ -30094,7 +30094,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1025" t="n">
-        <v>27.35671043396</v>
+        <v>27.3567123413086</v>
       </c>
       <c r="H1025" t="n">
         <v>135366</v>
@@ -30152,7 +30152,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1027" t="n">
-        <v>27.35671043396</v>
+        <v>27.3567123413086</v>
       </c>
       <c r="H1027" t="n">
         <v>162175</v>
@@ -30181,7 +30181,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1028" t="n">
-        <v>27.5461597442627</v>
+        <v>27.54616355896</v>
       </c>
       <c r="H1028" t="n">
         <v>220136</v>
@@ -30210,7 +30210,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G1029" t="n">
-        <v>27.394603729248</v>
+        <v>27.3946018218994</v>
       </c>
       <c r="H1029" t="n">
         <v>95337</v>
@@ -30239,7 +30239,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1030" t="n">
-        <v>27.35671043396</v>
+        <v>27.3567123413086</v>
       </c>
       <c r="H1030" t="n">
         <v>101367</v>
@@ -30268,7 +30268,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1031" t="n">
-        <v>26.8262481689453</v>
+        <v>26.8262500762939</v>
       </c>
       <c r="H1031" t="n">
         <v>126068</v>
@@ -30326,7 +30326,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1033" t="n">
-        <v>25.7842693328857</v>
+        <v>25.7842655181885</v>
       </c>
       <c r="H1033" t="n">
         <v>233919</v>
@@ -30413,7 +30413,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1036" t="n">
-        <v>25.0454139709473</v>
+        <v>25.0454120635986</v>
       </c>
       <c r="H1036" t="n">
         <v>326861</v>
@@ -30442,7 +30442,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1037" t="n">
-        <v>24.1171016693115</v>
+        <v>24.1171035766602</v>
       </c>
       <c r="H1037" t="n">
         <v>429177</v>
@@ -30587,7 +30587,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>25.9547729492188</v>
+        <v>25.9547748565674</v>
       </c>
       <c r="H1042" t="n">
         <v>141777</v>
@@ -30645,7 +30645,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1044" t="n">
-        <v>26.4852390289307</v>
+        <v>26.4852352142334</v>
       </c>
       <c r="H1044" t="n">
         <v>153580</v>
@@ -30703,7 +30703,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1046" t="n">
-        <v>26.125280380249</v>
+        <v>26.1252841949463</v>
       </c>
       <c r="H1046" t="n">
         <v>179144</v>
@@ -30732,7 +30732,7 @@
         <v>29.4799995422363</v>
       </c>
       <c r="G1047" t="n">
-        <v>27.9250621795654</v>
+        <v>27.9250640869141</v>
       </c>
       <c r="H1047" t="n">
         <v>809519</v>
@@ -30761,7 +30761,7 @@
         <v>31.9200000762939</v>
       </c>
       <c r="G1048" t="n">
-        <v>30.236364364624</v>
+        <v>30.2363662719727</v>
       </c>
       <c r="H1048" t="n">
         <v>1683988</v>
@@ -30819,7 +30819,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1050" t="n">
-        <v>30.3879280090332</v>
+        <v>30.3879299163818</v>
       </c>
       <c r="H1050" t="n">
         <v>433015</v>
@@ -30993,7 +30993,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G1056" t="n">
-        <v>27.394603729248</v>
+        <v>27.3946018218994</v>
       </c>
       <c r="H1056" t="n">
         <v>269117</v>
@@ -31051,7 +31051,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G1058" t="n">
-        <v>25.2538051605225</v>
+        <v>25.2538070678711</v>
       </c>
       <c r="H1058" t="n">
         <v>388604</v>
@@ -31080,7 +31080,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1059" t="n">
-        <v>25.4811477661133</v>
+        <v>25.4811496734619</v>
       </c>
       <c r="H1059" t="n">
         <v>472731</v>
@@ -31109,7 +31109,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1060" t="n">
-        <v>24.6665096282959</v>
+        <v>24.6665077209473</v>
       </c>
       <c r="H1060" t="n">
         <v>407543</v>
@@ -31138,7 +31138,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G1061" t="n">
-        <v>23.5108585357666</v>
+        <v>23.510856628418</v>
       </c>
       <c r="H1061" t="n">
         <v>370193</v>
@@ -31167,7 +31167,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>23.4350776672363</v>
+        <v>23.4350757598877</v>
       </c>
       <c r="H1062" t="n">
         <v>405648</v>
@@ -31196,7 +31196,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>21.5974063873291</v>
+        <v>21.5974044799805</v>
       </c>
       <c r="H1063" t="n">
         <v>498978</v>
@@ -31312,7 +31312,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1067" t="n">
-        <v>20.5743675231934</v>
+        <v>20.574369430542</v>
       </c>
       <c r="H1067" t="n">
         <v>492903</v>
@@ -31428,7 +31428,7 @@
         <v>22</v>
       </c>
       <c r="G1071" t="n">
-        <v>20.839599609375</v>
+        <v>20.8396015167236</v>
       </c>
       <c r="H1071" t="n">
         <v>270719</v>
@@ -31457,7 +31457,7 @@
         <v>21.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>20.3659725189209</v>
+        <v>20.3659744262695</v>
       </c>
       <c r="H1072" t="n">
         <v>374024</v>
@@ -31486,7 +31486,7 @@
         <v>19.5100002288818</v>
       </c>
       <c r="G1073" t="n">
-        <v>18.4809379577637</v>
+        <v>18.4809398651123</v>
       </c>
       <c r="H1073" t="n">
         <v>548208</v>
@@ -31544,7 +31544,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1075" t="n">
-        <v>19.7028942108154</v>
+        <v>19.7028923034668</v>
       </c>
       <c r="H1075" t="n">
         <v>369948</v>
@@ -31602,7 +31602,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G1077" t="n">
-        <v>20.7069854736328</v>
+        <v>20.7069873809814</v>
       </c>
       <c r="H1077" t="n">
         <v>213149</v>
@@ -31631,7 +31631,7 @@
         <v>21</v>
       </c>
       <c r="G1078" t="n">
-        <v>19.8923454284668</v>
+        <v>19.8923473358154</v>
       </c>
       <c r="H1078" t="n">
         <v>166482</v>
@@ -31689,7 +31689,7 @@
         <v>21.5</v>
       </c>
       <c r="G1080" t="n">
-        <v>20.3659725189209</v>
+        <v>20.3659744262695</v>
       </c>
       <c r="H1080" t="n">
         <v>196449</v>
@@ -31718,7 +31718,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1081" t="n">
-        <v>21.5974063873291</v>
+        <v>21.5974044799805</v>
       </c>
       <c r="H1081" t="n">
         <v>149841</v>
@@ -31776,7 +31776,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G1083" t="n">
-        <v>22.1278686523438</v>
+        <v>22.1278667449951</v>
       </c>
       <c r="H1083" t="n">
         <v>134326</v>
@@ -31805,7 +31805,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1084" t="n">
-        <v>22.5067653656006</v>
+        <v>22.5067691802979</v>
       </c>
       <c r="H1084" t="n">
         <v>269645</v>
@@ -31834,7 +31834,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1085" t="n">
-        <v>23.3024654388428</v>
+        <v>23.3024635314941</v>
       </c>
       <c r="H1085" t="n">
         <v>279969</v>
@@ -31863,7 +31863,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>23.8708171844482</v>
+        <v>23.870813369751</v>
       </c>
       <c r="H1086" t="n">
         <v>253131</v>
@@ -31892,7 +31892,7 @@
         <v>26</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.6286182403564</v>
+        <v>24.6286201477051</v>
       </c>
       <c r="H1087" t="n">
         <v>234179</v>
@@ -31921,7 +31921,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>23.3024654388428</v>
+        <v>23.3024635314941</v>
       </c>
       <c r="H1088" t="n">
         <v>199373</v>
@@ -32008,7 +32008,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1091" t="n">
-        <v>24.3444442749023</v>
+        <v>24.3444404602051</v>
       </c>
       <c r="H1091" t="n">
         <v>131024</v>
@@ -32066,7 +32066,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1093" t="n">
-        <v>23.9087028503418</v>
+        <v>23.9087047576904</v>
       </c>
       <c r="H1093" t="n">
         <v>116671</v>
@@ -32095,7 +32095,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.4012775421143</v>
+        <v>24.4012794494629</v>
       </c>
       <c r="H1094" t="n">
         <v>109504</v>
@@ -32153,7 +32153,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1096" t="n">
-        <v>24.8370151519775</v>
+        <v>24.8370132446289</v>
       </c>
       <c r="H1096" t="n">
         <v>290918</v>
@@ -32182,7 +32182,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G1097" t="n">
-        <v>24.6096725463867</v>
+        <v>24.6096706390381</v>
       </c>
       <c r="H1097" t="n">
         <v>163626</v>
@@ -32211,7 +32211,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1098" t="n">
-        <v>25.0643558502197</v>
+        <v>25.0643539428711</v>
       </c>
       <c r="H1098" t="n">
         <v>88742</v>
@@ -32327,7 +32327,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1102" t="n">
-        <v>25.405366897583</v>
+        <v>25.4053688049316</v>
       </c>
       <c r="H1102" t="n">
         <v>174154</v>
@@ -32356,7 +32356,7 @@
         <v>26.2800006866455</v>
       </c>
       <c r="G1103" t="n">
-        <v>24.8938541412354</v>
+        <v>24.8938503265381</v>
       </c>
       <c r="H1103" t="n">
         <v>122906</v>
@@ -32385,7 +32385,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1104" t="n">
-        <v>25.5000915527344</v>
+        <v>25.500093460083</v>
       </c>
       <c r="H1104" t="n">
         <v>101194</v>
@@ -32588,7 +32588,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G1111" t="n">
-        <v>25.213695526123</v>
+        <v>25.2136974334717</v>
       </c>
       <c r="H1111" t="n">
         <v>337502</v>
@@ -32704,7 +32704,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G1115" t="n">
-        <v>26.6282634735107</v>
+        <v>26.628267288208</v>
       </c>
       <c r="H1115" t="n">
         <v>148084</v>
@@ -32762,7 +32762,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1117" t="n">
-        <v>26.0165615081787</v>
+        <v>26.0165576934814</v>
       </c>
       <c r="H1117" t="n">
         <v>387149</v>
@@ -32820,7 +32820,7 @@
         <v>26.8799991607666</v>
       </c>
       <c r="G1119" t="n">
-        <v>25.691593170166</v>
+        <v>25.6915912628174</v>
       </c>
       <c r="H1119" t="n">
         <v>461795</v>
@@ -32849,7 +32849,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1120" t="n">
-        <v>25.8827533721924</v>
+        <v>25.8827514648438</v>
       </c>
       <c r="H1120" t="n">
         <v>439606</v>
@@ -32878,7 +32878,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1121" t="n">
-        <v>27.1635093688965</v>
+        <v>27.1635074615479</v>
       </c>
       <c r="H1121" t="n">
         <v>545626</v>
@@ -32907,7 +32907,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1122" t="n">
-        <v>27.9472541809082</v>
+        <v>27.9472522735596</v>
       </c>
       <c r="H1122" t="n">
         <v>671183</v>
@@ -32965,7 +32965,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1124" t="n">
-        <v>27.5840530395508</v>
+        <v>27.5840549468994</v>
       </c>
       <c r="H1124" t="n">
         <v>344129</v>
@@ -32994,7 +32994,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1125" t="n">
-        <v>27.6987495422363</v>
+        <v>27.6987476348877</v>
       </c>
       <c r="H1125" t="n">
         <v>371735</v>
@@ -33023,7 +33023,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>27.1443920135498</v>
+        <v>27.1443939208984</v>
       </c>
       <c r="H1126" t="n">
         <v>510560</v>
@@ -33139,7 +33139,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1130" t="n">
-        <v>25.1754665374756</v>
+        <v>25.1754684448242</v>
       </c>
       <c r="H1130" t="n">
         <v>480689</v>
@@ -33168,7 +33168,7 @@
         <v>26.8799991607666</v>
       </c>
       <c r="G1131" t="n">
-        <v>25.691593170166</v>
+        <v>25.6915912628174</v>
       </c>
       <c r="H1131" t="n">
         <v>454943</v>
@@ -33255,7 +33255,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>24.1814460754395</v>
+        <v>24.1814479827881</v>
       </c>
       <c r="H1134" t="n">
         <v>2151896</v>
@@ -33284,7 +33284,7 @@
         <v>26.8799991607666</v>
       </c>
       <c r="G1135" t="n">
-        <v>25.691593170166</v>
+        <v>25.6915912628174</v>
       </c>
       <c r="H1135" t="n">
         <v>907454</v>
@@ -33400,7 +33400,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.3666248321533</v>
+        <v>25.3666286468506</v>
       </c>
       <c r="H1139" t="n">
         <v>210910</v>
@@ -33429,7 +33429,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1140" t="n">
-        <v>25.3666248321533</v>
+        <v>25.3666286468506</v>
       </c>
       <c r="H1140" t="n">
         <v>137121</v>
@@ -33487,7 +33487,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1142" t="n">
-        <v>25.1754665374756</v>
+        <v>25.1754684448242</v>
       </c>
       <c r="H1142" t="n">
         <v>204191</v>
@@ -33603,7 +33603,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>25.6151294708252</v>
+        <v>25.6151275634766</v>
       </c>
       <c r="H1146" t="n">
         <v>173435</v>
@@ -33632,7 +33632,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G1147" t="n">
-        <v>25.844518661499</v>
+        <v>25.8445224761963</v>
       </c>
       <c r="H1147" t="n">
         <v>226043</v>
@@ -33748,7 +33748,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G1151" t="n">
-        <v>25.4813213348389</v>
+        <v>25.4813194274902</v>
       </c>
       <c r="H1151" t="n">
         <v>304843</v>
@@ -33835,7 +33835,7 @@
         <v>27.8600006103516</v>
       </c>
       <c r="G1154" t="n">
-        <v>26.6282634735107</v>
+        <v>26.628267288208</v>
       </c>
       <c r="H1154" t="n">
         <v>258727</v>
@@ -33864,7 +33864,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G1155" t="n">
-        <v>26.8194198608398</v>
+        <v>26.8194236755371</v>
       </c>
       <c r="H1155" t="n">
         <v>266931</v>
@@ -33893,7 +33893,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1156" t="n">
-        <v>26.9341201782227</v>
+        <v>26.934118270874</v>
       </c>
       <c r="H1156" t="n">
         <v>260060</v>
@@ -33922,7 +33922,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>26.9532337188721</v>
+        <v>26.9532356262207</v>
       </c>
       <c r="H1157" t="n">
         <v>191908</v>
@@ -33951,7 +33951,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1158" t="n">
-        <v>27.0679264068604</v>
+        <v>27.067928314209</v>
       </c>
       <c r="H1158" t="n">
         <v>155908</v>
@@ -33980,7 +33980,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1159" t="n">
-        <v>26.3797607421875</v>
+        <v>26.3797588348389</v>
       </c>
       <c r="H1159" t="n">
         <v>205432</v>
@@ -34009,7 +34009,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1160" t="n">
-        <v>26.8385410308838</v>
+        <v>26.8385391235352</v>
       </c>
       <c r="H1160" t="n">
         <v>124565</v>
@@ -34067,7 +34067,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1162" t="n">
-        <v>26.5135707855225</v>
+        <v>26.5135688781738</v>
       </c>
       <c r="H1162" t="n">
         <v>143447</v>
@@ -34125,7 +34125,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1164" t="n">
-        <v>26.4562244415283</v>
+        <v>26.4562225341797</v>
       </c>
       <c r="H1164" t="n">
         <v>257317</v>
@@ -34154,7 +34154,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G1165" t="n">
-        <v>26.5326881408691</v>
+        <v>26.5326862335205</v>
       </c>
       <c r="H1165" t="n">
         <v>128134</v>
@@ -34183,7 +34183,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1166" t="n">
-        <v>26.3415260314941</v>
+        <v>26.3415279388428</v>
       </c>
       <c r="H1166" t="n">
         <v>191713</v>
@@ -34212,7 +34212,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1167" t="n">
-        <v>26.7238445281982</v>
+        <v>26.7238426208496</v>
       </c>
       <c r="H1167" t="n">
         <v>165591</v>
@@ -34241,7 +34241,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1168" t="n">
-        <v>26.3415260314941</v>
+        <v>26.3415279388428</v>
       </c>
       <c r="H1168" t="n">
         <v>168767</v>
@@ -34299,7 +34299,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1170" t="n">
-        <v>26.9341201782227</v>
+        <v>26.934118270874</v>
       </c>
       <c r="H1170" t="n">
         <v>147830</v>
@@ -34328,7 +34328,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1171" t="n">
-        <v>28.2531089782715</v>
+        <v>28.2531051635742</v>
       </c>
       <c r="H1171" t="n">
         <v>454667</v>
@@ -34357,7 +34357,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1172" t="n">
-        <v>28.3295669555664</v>
+        <v>28.329568862915</v>
       </c>
       <c r="H1172" t="n">
         <v>246071</v>
@@ -34386,7 +34386,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G1173" t="n">
-        <v>28.3104515075684</v>
+        <v>28.310453414917</v>
       </c>
       <c r="H1173" t="n">
         <v>232768</v>
@@ -34415,7 +34415,7 @@
         <v>28.9400005340576</v>
       </c>
       <c r="G1174" t="n">
-        <v>27.6605167388916</v>
+        <v>27.6605186462402</v>
       </c>
       <c r="H1174" t="n">
         <v>130262</v>
@@ -34444,7 +34444,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1175" t="n">
-        <v>27.7943248748779</v>
+        <v>27.7943267822266</v>
       </c>
       <c r="H1175" t="n">
         <v>76843</v>
@@ -34531,7 +34531,7 @@
         <v>29.1200008392334</v>
       </c>
       <c r="G1178" t="n">
-        <v>27.8325595855713</v>
+        <v>27.8325576782227</v>
       </c>
       <c r="H1178" t="n">
         <v>135517</v>
@@ -34560,7 +34560,7 @@
         <v>29.1200008392334</v>
       </c>
       <c r="G1179" t="n">
-        <v>27.8325595855713</v>
+        <v>27.8325576782227</v>
       </c>
       <c r="H1179" t="n">
         <v>199679</v>
@@ -34589,7 +34589,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1180" t="n">
-        <v>28.3677978515625</v>
+        <v>28.3678016662598</v>
       </c>
       <c r="H1180" t="n">
         <v>404790</v>
@@ -34647,7 +34647,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1182" t="n">
-        <v>28.482494354248</v>
+        <v>28.4824924468994</v>
       </c>
       <c r="H1182" t="n">
         <v>221168</v>
@@ -34676,7 +34676,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1183" t="n">
-        <v>28.1384124755859</v>
+        <v>28.1384143829346</v>
       </c>
       <c r="H1183" t="n">
         <v>216073</v>
@@ -34705,7 +34705,7 @@
         <v>29.1200008392334</v>
       </c>
       <c r="G1184" t="n">
-        <v>27.8325595855713</v>
+        <v>27.8325576782227</v>
       </c>
       <c r="H1184" t="n">
         <v>203844</v>
@@ -34734,7 +34734,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1185" t="n">
-        <v>28.0045986175537</v>
+        <v>28.0046005249023</v>
       </c>
       <c r="H1185" t="n">
         <v>218897</v>
@@ -34821,7 +34821,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1188" t="n">
-        <v>29.7059059143066</v>
+        <v>29.7059020996094</v>
       </c>
       <c r="H1188" t="n">
         <v>520225</v>
@@ -34879,7 +34879,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>30.2029151916504</v>
+        <v>30.2029132843018</v>
       </c>
       <c r="H1190" t="n">
         <v>256214</v>
@@ -34908,7 +34908,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1191" t="n">
-        <v>29.7250194549561</v>
+        <v>29.7250213623047</v>
       </c>
       <c r="H1191" t="n">
         <v>411152</v>
@@ -34937,7 +34937,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>29.8205966949463</v>
+        <v>29.8205986022949</v>
       </c>
       <c r="H1192" t="n">
         <v>219951</v>
@@ -35082,7 +35082,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1197" t="n">
-        <v>29.8205966949463</v>
+        <v>29.8205986022949</v>
       </c>
       <c r="H1197" t="n">
         <v>223760</v>
@@ -35111,7 +35111,7 @@
         <v>31.3799991607666</v>
       </c>
       <c r="G1198" t="n">
-        <v>29.9926414489746</v>
+        <v>29.9926433563232</v>
       </c>
       <c r="H1198" t="n">
         <v>219789</v>
@@ -35169,7 +35169,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1200" t="n">
-        <v>28.769229888916</v>
+        <v>28.7692317962646</v>
       </c>
       <c r="H1200" t="n">
         <v>286776</v>
@@ -35198,7 +35198,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G1201" t="n">
-        <v>29.3809375762939</v>
+        <v>29.3809356689453</v>
       </c>
       <c r="H1201" t="n">
         <v>166120</v>
@@ -35285,7 +35285,7 @@
         <v>30.9599990844727</v>
       </c>
       <c r="G1204" t="n">
-        <v>29.5912075042725</v>
+        <v>29.5912094116211</v>
       </c>
       <c r="H1204" t="n">
         <v>202936</v>
@@ -35401,7 +35401,7 @@
         <v>31.3600006103516</v>
       </c>
       <c r="G1208" t="n">
-        <v>29.9735221862793</v>
+        <v>29.9735240936279</v>
       </c>
       <c r="H1208" t="n">
         <v>210199</v>
@@ -35459,7 +35459,7 @@
         <v>32.2400016784668</v>
       </c>
       <c r="G1210" t="n">
-        <v>30.8146190643311</v>
+        <v>30.8146209716797</v>
       </c>
       <c r="H1210" t="n">
         <v>225968</v>
@@ -35488,7 +35488,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G1211" t="n">
-        <v>30.7572727203369</v>
+        <v>30.7572708129883</v>
       </c>
       <c r="H1211" t="n">
         <v>218715</v>
@@ -35517,7 +35517,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G1212" t="n">
-        <v>31.0248928070068</v>
+        <v>31.0248947143555</v>
       </c>
       <c r="H1212" t="n">
         <v>213409</v>
@@ -35546,7 +35546,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G1213" t="n">
-        <v>31.2925148010254</v>
+        <v>31.2925186157227</v>
       </c>
       <c r="H1213" t="n">
         <v>167819</v>
@@ -35604,7 +35604,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G1215" t="n">
-        <v>33.6819877624512</v>
+        <v>33.6819839477539</v>
       </c>
       <c r="H1215" t="n">
         <v>628073</v>
@@ -35662,7 +35662,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G1217" t="n">
-        <v>33.0129318237305</v>
+        <v>33.0129356384277</v>
       </c>
       <c r="H1217" t="n">
         <v>348623</v>
@@ -35720,7 +35720,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G1219" t="n">
-        <v>33.2423210144043</v>
+        <v>33.2423286437988</v>
       </c>
       <c r="H1219" t="n">
         <v>1440638</v>
@@ -35749,7 +35749,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>32.7835388183594</v>
+        <v>32.7835426330566</v>
       </c>
       <c r="H1220" t="n">
         <v>202521</v>
@@ -35836,7 +35836,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1223" t="n">
-        <v>31.1969318389893</v>
+        <v>31.1969337463379</v>
       </c>
       <c r="H1223" t="n">
         <v>269645</v>
@@ -35865,7 +35865,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G1224" t="n">
-        <v>31.674825668335</v>
+        <v>31.6748294830322</v>
       </c>
       <c r="H1224" t="n">
         <v>233157</v>
@@ -35894,7 +35894,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G1225" t="n">
-        <v>31.2351627349854</v>
+        <v>31.235164642334</v>
       </c>
       <c r="H1225" t="n">
         <v>164367</v>
@@ -36010,7 +36010,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1229" t="n">
-        <v>30.9675483703613</v>
+        <v>30.9675445556641</v>
       </c>
       <c r="H1229" t="n">
         <v>184368</v>
@@ -36039,7 +36039,7 @@
         <v>32.5800018310547</v>
       </c>
       <c r="G1230" t="n">
-        <v>31.1395835876465</v>
+        <v>31.1395893096924</v>
       </c>
       <c r="H1230" t="n">
         <v>217654</v>
@@ -36097,7 +36097,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G1232" t="n">
-        <v>32.7835388183594</v>
+        <v>32.7835426330566</v>
       </c>
       <c r="H1232" t="n">
         <v>256273</v>
@@ -36126,7 +36126,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1233" t="n">
-        <v>33.5864067077637</v>
+        <v>33.5863990783691</v>
       </c>
       <c r="H1233" t="n">
         <v>335351</v>
@@ -36155,7 +36155,7 @@
         <v>35.2999992370605</v>
       </c>
       <c r="G1234" t="n">
-        <v>33.7393341064453</v>
+        <v>33.739330291748</v>
       </c>
       <c r="H1234" t="n">
         <v>237896</v>
@@ -36184,7 +36184,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>34.6951179504395</v>
+        <v>34.6951217651367</v>
       </c>
       <c r="H1235" t="n">
         <v>573745</v>
@@ -36271,7 +36271,7 @@
         <v>35.2200012207031</v>
       </c>
       <c r="G1238" t="n">
-        <v>33.6628723144531</v>
+        <v>33.6628684997559</v>
       </c>
       <c r="H1238" t="n">
         <v>276018</v>
@@ -36300,7 +36300,7 @@
         <v>35.0200004577637</v>
       </c>
       <c r="G1239" t="n">
-        <v>33.4717140197754</v>
+        <v>33.4717102050781</v>
       </c>
       <c r="H1239" t="n">
         <v>215491</v>
@@ -36329,7 +36329,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1240" t="n">
-        <v>35.1730155944824</v>
+        <v>35.1730079650879</v>
       </c>
       <c r="H1240" t="n">
         <v>500948</v>
@@ -36358,7 +36358,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1241" t="n">
-        <v>35.2685966491699</v>
+        <v>35.2685928344727</v>
       </c>
       <c r="H1241" t="n">
         <v>370513</v>
@@ -36387,7 +36387,7 @@
         <v>37.0800018310547</v>
       </c>
       <c r="G1242" t="n">
-        <v>35.4406356811523</v>
+        <v>35.4406318664551</v>
       </c>
       <c r="H1242" t="n">
         <v>476252</v>
@@ -36416,7 +36416,7 @@
         <v>36.5800018310547</v>
       </c>
       <c r="G1243" t="n">
-        <v>34.9627418518066</v>
+        <v>34.9627456665039</v>
       </c>
       <c r="H1243" t="n">
         <v>230073</v>
@@ -36445,7 +36445,7 @@
         <v>36.9799995422363</v>
       </c>
       <c r="G1244" t="n">
-        <v>35.3450546264648</v>
+        <v>35.3450584411621</v>
       </c>
       <c r="H1244" t="n">
         <v>161063</v>
@@ -36474,7 +36474,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1245" t="n">
-        <v>35.2685966491699</v>
+        <v>35.2685928344727</v>
       </c>
       <c r="H1245" t="n">
         <v>222811</v>
@@ -36532,7 +36532,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1247" t="n">
-        <v>34.6951179504395</v>
+        <v>34.6951217651367</v>
       </c>
       <c r="H1247" t="n">
         <v>223764</v>
@@ -36590,7 +36590,7 @@
         <v>36.5800018310547</v>
       </c>
       <c r="G1249" t="n">
-        <v>34.9627418518066</v>
+        <v>34.9627456665039</v>
       </c>
       <c r="H1249" t="n">
         <v>175303</v>
@@ -36619,7 +36619,7 @@
         <v>36.3800010681152</v>
       </c>
       <c r="G1250" t="n">
-        <v>34.7715873718262</v>
+        <v>34.7715835571289</v>
       </c>
       <c r="H1250" t="n">
         <v>204917</v>
@@ -36677,7 +36677,7 @@
         <v>37</v>
       </c>
       <c r="G1252" t="n">
-        <v>35.3641662597656</v>
+        <v>35.3641700744629</v>
       </c>
       <c r="H1252" t="n">
         <v>306404</v>
@@ -36764,7 +36764,7 @@
         <v>38.0800018310547</v>
       </c>
       <c r="G1255" t="n">
-        <v>36.3964195251465</v>
+        <v>36.396427154541</v>
       </c>
       <c r="H1255" t="n">
         <v>306900</v>
@@ -36793,7 +36793,7 @@
         <v>38.0800018310547</v>
       </c>
       <c r="G1256" t="n">
-        <v>36.3964195251465</v>
+        <v>36.396427154541</v>
       </c>
       <c r="H1256" t="n">
         <v>175827</v>
@@ -36822,7 +36822,7 @@
         <v>38.0400009155273</v>
       </c>
       <c r="G1257" t="n">
-        <v>36.3581886291504</v>
+        <v>36.3581924438477</v>
       </c>
       <c r="H1257" t="n">
         <v>179269</v>
@@ -36851,7 +36851,7 @@
         <v>37.4199981689453</v>
       </c>
       <c r="G1258" t="n">
-        <v>35.7656021118164</v>
+        <v>35.7656059265137</v>
       </c>
       <c r="H1258" t="n">
         <v>265346</v>
@@ -36938,7 +36938,7 @@
         <v>38.2000007629395</v>
       </c>
       <c r="G1261" t="n">
-        <v>36.5111198425293</v>
+        <v>36.511116027832</v>
       </c>
       <c r="H1261" t="n">
         <v>201748</v>
@@ -36967,7 +36967,7 @@
         <v>39.0800018310547</v>
       </c>
       <c r="G1262" t="n">
-        <v>37.3522148132324</v>
+        <v>37.3522109985352</v>
       </c>
       <c r="H1262" t="n">
         <v>289679</v>
@@ -36996,7 +36996,7 @@
         <v>38.9799995422363</v>
       </c>
       <c r="G1263" t="n">
-        <v>37.2566299438477</v>
+        <v>37.2566261291504</v>
       </c>
       <c r="H1263" t="n">
         <v>250104</v>
@@ -37025,7 +37025,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1264" t="n">
-        <v>37.6580619812012</v>
+        <v>37.6580657958984</v>
       </c>
       <c r="H1264" t="n">
         <v>450082</v>
@@ -37054,7 +37054,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G1265" t="n">
-        <v>37.0463562011719</v>
+        <v>37.0463600158691</v>
       </c>
       <c r="H1265" t="n">
         <v>326039</v>
@@ -37083,7 +37083,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G1266" t="n">
-        <v>37.6580619812012</v>
+        <v>37.6580657958984</v>
       </c>
       <c r="H1266" t="n">
         <v>154256</v>
@@ -37141,7 +37141,7 @@
         <v>39.8400001525879</v>
       </c>
       <c r="G1268" t="n">
-        <v>38.07861328125</v>
+        <v>38.0786094665527</v>
       </c>
       <c r="H1268" t="n">
         <v>117980</v>
@@ -37170,7 +37170,7 @@
         <v>40.0400009155273</v>
       </c>
       <c r="G1269" t="n">
-        <v>38.2697677612305</v>
+        <v>38.2697639465332</v>
       </c>
       <c r="H1269" t="n">
         <v>204641</v>
@@ -37199,7 +37199,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G1270" t="n">
-        <v>38.5565032958984</v>
+        <v>38.5565071105957</v>
       </c>
       <c r="H1270" t="n">
         <v>201729</v>
@@ -37228,7 +37228,7 @@
         <v>41</v>
       </c>
       <c r="G1271" t="n">
-        <v>39.1873245239258</v>
+        <v>39.187328338623</v>
       </c>
       <c r="H1271" t="n">
         <v>268449</v>
@@ -37257,7 +37257,7 @@
         <v>40.560001373291</v>
       </c>
       <c r="G1272" t="n">
-        <v>38.7667808532715</v>
+        <v>38.7667846679688</v>
       </c>
       <c r="H1272" t="n">
         <v>262126</v>
@@ -37286,7 +37286,7 @@
         <v>41.5200004577637</v>
       </c>
       <c r="G1273" t="n">
-        <v>39.6843299865723</v>
+        <v>39.6843338012695</v>
       </c>
       <c r="H1273" t="n">
         <v>310385</v>
@@ -37344,7 +37344,7 @@
         <v>40.0999984741211</v>
       </c>
       <c r="G1275" t="n">
-        <v>38.3271141052246</v>
+        <v>38.3271179199219</v>
       </c>
       <c r="H1275" t="n">
         <v>596715</v>
@@ -37373,7 +37373,7 @@
         <v>40.439998626709</v>
       </c>
       <c r="G1276" t="n">
-        <v>38.6520843505859</v>
+        <v>38.6520805358887</v>
       </c>
       <c r="H1276" t="n">
         <v>268614</v>
@@ -37402,7 +37402,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G1277" t="n">
-        <v>38.5182685852051</v>
+        <v>38.5182723999023</v>
       </c>
       <c r="H1277" t="n">
         <v>272701</v>
@@ -37460,7 +37460,7 @@
         <v>41</v>
       </c>
       <c r="G1279" t="n">
-        <v>39.1873245239258</v>
+        <v>39.187328338623</v>
       </c>
       <c r="H1279" t="n">
         <v>318673</v>
@@ -37489,7 +37489,7 @@
         <v>40.2999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>38.5182685852051</v>
+        <v>38.5182723999023</v>
       </c>
       <c r="H1280" t="n">
         <v>358488</v>
@@ -37518,7 +37518,7 @@
         <v>41.0400009155273</v>
       </c>
       <c r="G1281" t="n">
-        <v>39.2255592346191</v>
+        <v>39.2255554199219</v>
       </c>
       <c r="H1281" t="n">
         <v>219945</v>
@@ -37576,7 +37576,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G1283" t="n">
-        <v>38.5565032958984</v>
+        <v>38.5565071105957</v>
       </c>
       <c r="H1283" t="n">
         <v>216095</v>
@@ -37721,7 +37721,7 @@
         <v>37.2799987792969</v>
       </c>
       <c r="G1288" t="n">
-        <v>35.6317977905273</v>
+        <v>35.6317939758301</v>
       </c>
       <c r="H1288" t="n">
         <v>519040</v>
@@ -37808,7 +37808,7 @@
         <v>38.0800018310547</v>
       </c>
       <c r="G1291" t="n">
-        <v>36.3964195251465</v>
+        <v>36.396427154541</v>
       </c>
       <c r="H1291" t="n">
         <v>304365</v>
@@ -37953,7 +37953,7 @@
         <v>40.6800003051758</v>
       </c>
       <c r="G1296" t="n">
-        <v>38.8814697265625</v>
+        <v>38.8814735412598</v>
       </c>
       <c r="H1296" t="n">
         <v>343942</v>
@@ -37982,7 +37982,7 @@
         <v>40.560001373291</v>
       </c>
       <c r="G1297" t="n">
-        <v>38.7667808532715</v>
+        <v>38.7667846679688</v>
       </c>
       <c r="H1297" t="n">
         <v>187510</v>
@@ -38011,7 +38011,7 @@
         <v>40</v>
       </c>
       <c r="G1298" t="n">
-        <v>38.2315368652344</v>
+        <v>38.2315406799316</v>
       </c>
       <c r="H1298" t="n">
         <v>197862</v>
@@ -38098,7 +38098,7 @@
         <v>41.060001373291</v>
       </c>
       <c r="G1301" t="n">
-        <v>39.2446708679199</v>
+        <v>39.2446746826172</v>
       </c>
       <c r="H1301" t="n">
         <v>280272</v>
@@ -38127,7 +38127,7 @@
         <v>40.939998626709</v>
       </c>
       <c r="G1302" t="n">
-        <v>39.1299781799316</v>
+        <v>39.1299743652344</v>
       </c>
       <c r="H1302" t="n">
         <v>174236</v>
@@ -38156,7 +38156,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>38.4226951599121</v>
+        <v>38.4226913452148</v>
       </c>
       <c r="H1303" t="n">
         <v>210803</v>
@@ -38185,7 +38185,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G1304" t="n">
-        <v>37.4669036865234</v>
+        <v>37.4669075012207</v>
       </c>
       <c r="H1304" t="n">
         <v>190818</v>
@@ -38243,7 +38243,7 @@
         <v>39.439998626709</v>
       </c>
       <c r="G1306" t="n">
-        <v>37.6962966918945</v>
+        <v>37.6962928771973</v>
       </c>
       <c r="H1306" t="n">
         <v>111206</v>
@@ -38359,7 +38359,7 @@
         <v>38.0400009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>36.3581886291504</v>
+        <v>36.3581924438477</v>
       </c>
       <c r="H1310" t="n">
         <v>178712</v>
@@ -38388,7 +38388,7 @@
         <v>38.7000007629395</v>
       </c>
       <c r="G1311" t="n">
-        <v>36.989013671875</v>
+        <v>36.9890098571777</v>
       </c>
       <c r="H1311" t="n">
         <v>162459</v>
@@ -38562,7 +38562,7 @@
         <v>42.0200004577637</v>
       </c>
       <c r="G1317" t="n">
-        <v>40.1622314453125</v>
+        <v>40.1622276306152</v>
       </c>
       <c r="H1317" t="n">
         <v>505560</v>
@@ -38591,7 +38591,7 @@
         <v>43.4799995422363</v>
       </c>
       <c r="G1318" t="n">
-        <v>41.5576820373535</v>
+        <v>41.5576782226562</v>
       </c>
       <c r="H1318" t="n">
         <v>397078</v>
@@ -38620,7 +38620,7 @@
         <v>44.439998626709</v>
       </c>
       <c r="G1319" t="n">
-        <v>42.4752388000488</v>
+        <v>42.4752349853516</v>
       </c>
       <c r="H1319" t="n">
         <v>348085</v>
@@ -38678,7 +38678,7 @@
         <v>43.439998626709</v>
       </c>
       <c r="G1321" t="n">
-        <v>41.5194435119629</v>
+        <v>41.5194511413574</v>
       </c>
       <c r="H1321" t="n">
         <v>334576</v>
@@ -38736,7 +38736,7 @@
         <v>43.4199981689453</v>
       </c>
       <c r="G1323" t="n">
-        <v>41.5003318786621</v>
+        <v>41.5003280639648</v>
       </c>
       <c r="H1323" t="n">
         <v>287953</v>
@@ -38823,7 +38823,7 @@
         <v>42.939998626709</v>
       </c>
       <c r="G1326" t="n">
-        <v>41.0415534973145</v>
+        <v>41.0415496826172</v>
       </c>
       <c r="H1326" t="n">
         <v>128582</v>
@@ -38910,7 +38910,7 @@
         <v>42.1800003051758</v>
       </c>
       <c r="G1329" t="n">
-        <v>40.3151550292969</v>
+        <v>40.3151512145996</v>
       </c>
       <c r="H1329" t="n">
         <v>158047</v>
@@ -38968,7 +38968,7 @@
         <v>42.1800003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>40.3151550292969</v>
+        <v>40.3151512145996</v>
       </c>
       <c r="H1331" t="n">
         <v>217581</v>
@@ -39084,7 +39084,7 @@
         <v>43.3600006103516</v>
       </c>
       <c r="G1335" t="n">
-        <v>41.4429893493652</v>
+        <v>41.442985534668</v>
       </c>
       <c r="H1335" t="n">
         <v>232387</v>
@@ -39142,7 +39142,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G1337" t="n">
-        <v>41.251823425293</v>
+        <v>41.2518272399902</v>
       </c>
       <c r="H1337" t="n">
         <v>212665</v>
@@ -39200,7 +39200,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G1339" t="n">
-        <v>40.9077415466309</v>
+        <v>40.9077453613281</v>
       </c>
       <c r="H1339" t="n">
         <v>233030</v>
@@ -39229,7 +39229,7 @@
         <v>44</v>
       </c>
       <c r="G1340" t="n">
-        <v>42.0546875</v>
+        <v>42.0546913146973</v>
       </c>
       <c r="H1340" t="n">
         <v>214789</v>
@@ -39316,7 +39316,7 @@
         <v>44.439998626709</v>
       </c>
       <c r="G1343" t="n">
-        <v>42.4752388000488</v>
+        <v>42.4752349853516</v>
       </c>
       <c r="H1343" t="n">
         <v>319833</v>
@@ -39345,7 +39345,7 @@
         <v>44.9799995422363</v>
       </c>
       <c r="G1344" t="n">
-        <v>42.9913635253906</v>
+        <v>42.9913673400879</v>
       </c>
       <c r="H1344" t="n">
         <v>381398</v>
@@ -39374,7 +39374,7 @@
         <v>44.3800010681152</v>
       </c>
       <c r="G1345" t="n">
-        <v>42.4178886413574</v>
+        <v>42.4178924560547</v>
       </c>
       <c r="H1345" t="n">
         <v>279008</v>
@@ -39432,7 +39432,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G1347" t="n">
-        <v>42.6855087280273</v>
+        <v>42.6855125427246</v>
       </c>
       <c r="H1347" t="n">
         <v>219936</v>
@@ -39461,7 +39461,7 @@
         <v>44.7400016784668</v>
       </c>
       <c r="G1348" t="n">
-        <v>42.7619781494141</v>
+        <v>42.7619743347168</v>
       </c>
       <c r="H1348" t="n">
         <v>157176</v>
@@ -39548,7 +39548,7 @@
         <v>44.9599990844727</v>
       </c>
       <c r="G1351" t="n">
-        <v>42.9722442626953</v>
+        <v>42.9722518920898</v>
       </c>
       <c r="H1351" t="n">
         <v>167037</v>
@@ -39635,7 +39635,7 @@
         <v>44.5</v>
       </c>
       <c r="G1354" t="n">
-        <v>42.5325889587402</v>
+        <v>42.532585144043</v>
       </c>
       <c r="H1354" t="n">
         <v>171534</v>
@@ -39722,7 +39722,7 @@
         <v>43.439998626709</v>
       </c>
       <c r="G1357" t="n">
-        <v>41.5194435119629</v>
+        <v>41.5194511413574</v>
       </c>
       <c r="H1357" t="n">
         <v>306926</v>
@@ -39838,7 +39838,7 @@
         <v>42.5400009155273</v>
       </c>
       <c r="G1361" t="n">
-        <v>40.6592445373535</v>
+        <v>40.6592407226562</v>
       </c>
       <c r="H1361" t="n">
         <v>170605</v>
@@ -39867,7 +39867,7 @@
         <v>43.0999984741211</v>
       </c>
       <c r="G1362" t="n">
-        <v>41.1944770812988</v>
+        <v>41.1944808959961</v>
       </c>
       <c r="H1362" t="n">
         <v>141524</v>
@@ -39896,7 +39896,7 @@
         <v>44.5</v>
       </c>
       <c r="G1363" t="n">
-        <v>42.5325889587402</v>
+        <v>42.532585144043</v>
       </c>
       <c r="H1363" t="n">
         <v>333807</v>
@@ -39925,7 +39925,7 @@
         <v>44.9799995422363</v>
       </c>
       <c r="G1364" t="n">
-        <v>42.9913635253906</v>
+        <v>42.9913673400879</v>
       </c>
       <c r="H1364" t="n">
         <v>258701</v>
@@ -39954,7 +39954,7 @@
         <v>44.939998626709</v>
       </c>
       <c r="G1365" t="n">
-        <v>42.9531288146973</v>
+        <v>42.953125</v>
       </c>
       <c r="H1365" t="n">
         <v>177513</v>
@@ -39983,7 +39983,7 @@
         <v>44.7599983215332</v>
       </c>
       <c r="G1366" t="n">
-        <v>42.7810859680176</v>
+        <v>42.7810897827148</v>
       </c>
       <c r="H1366" t="n">
         <v>257125</v>
@@ -40012,7 +40012,7 @@
         <v>45.4000015258789</v>
       </c>
       <c r="G1367" t="n">
-        <v>43.3927993774414</v>
+        <v>43.3927917480469</v>
       </c>
       <c r="H1367" t="n">
         <v>172901</v>
@@ -40041,7 +40041,7 @@
         <v>45.7400016784668</v>
       </c>
       <c r="G1368" t="n">
-        <v>43.7177619934082</v>
+        <v>43.7177658081055</v>
       </c>
       <c r="H1368" t="n">
         <v>264545</v>
@@ -40099,7 +40099,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G1370" t="n">
-        <v>43.9484634399414</v>
+        <v>43.9484672546387</v>
       </c>
       <c r="H1370" t="n">
         <v>212289</v>
@@ -40128,7 +40128,7 @@
         <v>45.6800003051758</v>
       </c>
       <c r="G1371" t="n">
-        <v>43.9100151062012</v>
+        <v>43.9100112915039</v>
       </c>
       <c r="H1371" t="n">
         <v>147936</v>
@@ -40157,7 +40157,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G1372" t="n">
-        <v>43.9484634399414</v>
+        <v>43.9484672546387</v>
       </c>
       <c r="H1372" t="n">
         <v>405514</v>
@@ -40215,7 +40215,7 @@
         <v>46.7599983215332</v>
       </c>
       <c r="G1374" t="n">
-        <v>44.9481658935547</v>
+        <v>44.9481620788574</v>
       </c>
       <c r="H1374" t="n">
         <v>123692</v>
@@ -40244,7 +40244,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1375" t="n">
-        <v>45.1211891174316</v>
+        <v>45.1211929321289</v>
       </c>
       <c r="H1375" t="n">
         <v>264169</v>
@@ -40273,7 +40273,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1376" t="n">
-        <v>47.9665031433105</v>
+        <v>47.9664993286133</v>
       </c>
       <c r="H1376" t="n">
         <v>531789</v>
@@ -40331,7 +40331,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1378" t="n">
-        <v>48.351001739502</v>
+        <v>48.3509941101074</v>
       </c>
       <c r="H1378" t="n">
         <v>146302</v>
@@ -40389,7 +40389,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>48.351001739502</v>
+        <v>48.3509941101074</v>
       </c>
       <c r="H1380" t="n">
         <v>172621</v>
@@ -40418,7 +40418,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>48.351001739502</v>
+        <v>48.3509941101074</v>
       </c>
       <c r="H1381" t="n">
         <v>148801</v>
@@ -40505,7 +40505,7 @@
         <v>50.1500015258789</v>
       </c>
       <c r="G1384" t="n">
-        <v>48.2068138122559</v>
+        <v>48.2068176269531</v>
       </c>
       <c r="H1384" t="n">
         <v>116237</v>
@@ -40563,7 +40563,7 @@
         <v>51</v>
       </c>
       <c r="G1386" t="n">
-        <v>49.0238800048828</v>
+        <v>49.0238761901855</v>
       </c>
       <c r="H1386" t="n">
         <v>232527</v>
@@ -40621,7 +40621,7 @@
         <v>49.560001373291</v>
       </c>
       <c r="G1388" t="n">
-        <v>47.6396751403809</v>
+        <v>47.6396789550781</v>
       </c>
       <c r="H1388" t="n">
         <v>339715</v>
@@ -40650,7 +40650,7 @@
         <v>49.5800018310547</v>
       </c>
       <c r="G1389" t="n">
-        <v>47.6588973999023</v>
+        <v>47.6589012145996</v>
       </c>
       <c r="H1389" t="n">
         <v>301520</v>
@@ -40708,7 +40708,7 @@
         <v>48.7599983215332</v>
       </c>
       <c r="G1391" t="n">
-        <v>46.8706703186035</v>
+        <v>46.8706665039062</v>
       </c>
       <c r="H1391" t="n">
         <v>155351</v>
@@ -40737,7 +40737,7 @@
         <v>49.7400016784668</v>
       </c>
       <c r="G1392" t="n">
-        <v>47.8126983642578</v>
+        <v>47.8126945495605</v>
       </c>
       <c r="H1392" t="n">
         <v>197965</v>
@@ -40766,7 +40766,7 @@
         <v>50.5</v>
       </c>
       <c r="G1393" t="n">
-        <v>48.5432472229004</v>
+        <v>48.5432510375977</v>
       </c>
       <c r="H1393" t="n">
         <v>142240</v>
@@ -40853,7 +40853,7 @@
         <v>49.939998626709</v>
       </c>
       <c r="G1396" t="n">
-        <v>48.0049476623535</v>
+        <v>48.0049514770508</v>
       </c>
       <c r="H1396" t="n">
         <v>150946</v>
@@ -40940,7 +40940,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1399" t="n">
-        <v>48.6393775939941</v>
+        <v>48.6393737792969</v>
       </c>
       <c r="H1399" t="n">
         <v>112490</v>
@@ -40969,7 +40969,7 @@
         <v>50.5</v>
       </c>
       <c r="G1400" t="n">
-        <v>48.5432472229004</v>
+        <v>48.5432510375977</v>
       </c>
       <c r="H1400" t="n">
         <v>132747</v>
@@ -41056,7 +41056,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1403" t="n">
-        <v>49.2161293029785</v>
+        <v>49.2161254882812</v>
       </c>
       <c r="H1403" t="n">
         <v>151747</v>
@@ -41085,7 +41085,7 @@
         <v>51.8499984741211</v>
       </c>
       <c r="G1404" t="n">
-        <v>49.8409385681152</v>
+        <v>49.8409423828125</v>
       </c>
       <c r="H1404" t="n">
         <v>177259</v>
@@ -41143,7 +41143,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>49.6967544555664</v>
+        <v>49.6967506408691</v>
       </c>
       <c r="H1406" t="n">
         <v>101548</v>
@@ -41172,7 +41172,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1407" t="n">
-        <v>49.4083824157715</v>
+        <v>49.408374786377</v>
       </c>
       <c r="H1407" t="n">
         <v>160416</v>
@@ -41201,7 +41201,7 @@
         <v>51.5</v>
       </c>
       <c r="G1408" t="n">
-        <v>49.5045051574707</v>
+        <v>49.5045013427734</v>
       </c>
       <c r="H1408" t="n">
         <v>223081</v>
@@ -41288,7 +41288,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>49.4564437866211</v>
+        <v>49.4564399719238</v>
       </c>
       <c r="H1411" t="n">
         <v>204054</v>
@@ -41346,7 +41346,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G1413" t="n">
-        <v>50.5138130187988</v>
+        <v>50.5138168334961</v>
       </c>
       <c r="H1413" t="n">
         <v>233316</v>
@@ -41375,7 +41375,7 @@
         <v>52.5</v>
       </c>
       <c r="G1414" t="n">
-        <v>50.4657516479492</v>
+        <v>50.4657554626465</v>
       </c>
       <c r="H1414" t="n">
         <v>130674</v>
@@ -41404,7 +41404,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>50.0331878662109</v>
+        <v>50.0331954956055</v>
       </c>
       <c r="H1415" t="n">
         <v>144632</v>
@@ -41491,7 +41491,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1418" t="n">
-        <v>50.6099472045898</v>
+        <v>50.6099433898926</v>
       </c>
       <c r="H1418" t="n">
         <v>174865</v>
@@ -41520,7 +41520,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>51.2347602844238</v>
+        <v>51.2347564697266</v>
       </c>
       <c r="H1419" t="n">
         <v>149304</v>
@@ -41578,7 +41578,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1421" t="n">
-        <v>51.8115119934082</v>
+        <v>51.8115158081055</v>
       </c>
       <c r="H1421" t="n">
         <v>170395</v>
@@ -41607,7 +41607,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1422" t="n">
-        <v>51.8115119934082</v>
+        <v>51.8115158081055</v>
       </c>
       <c r="H1422" t="n">
         <v>322068</v>
@@ -41636,7 +41636,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G1423" t="n">
-        <v>52.0037612915039</v>
+        <v>52.0037574768066</v>
       </c>
       <c r="H1423" t="n">
         <v>222230</v>
@@ -41723,7 +41723,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G1426" t="n">
-        <v>53.0611381530762</v>
+        <v>53.0611343383789</v>
       </c>
       <c r="H1426" t="n">
         <v>197447</v>
@@ -41752,7 +41752,7 @@
         <v>56</v>
       </c>
       <c r="G1427" t="n">
-        <v>53.8301391601562</v>
+        <v>53.830135345459</v>
       </c>
       <c r="H1427" t="n">
         <v>193353</v>
@@ -41781,7 +41781,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G1428" t="n">
-        <v>54.4549598693848</v>
+        <v>54.4549560546875</v>
       </c>
       <c r="H1428" t="n">
         <v>222587</v>
@@ -41810,7 +41810,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G1429" t="n">
-        <v>54.4549598693848</v>
+        <v>54.4549560546875</v>
       </c>
       <c r="H1429" t="n">
         <v>184992</v>
@@ -41955,7 +41955,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G1434" t="n">
-        <v>55.608455657959</v>
+        <v>55.6084594726562</v>
       </c>
       <c r="H1434" t="n">
         <v>163237</v>
@@ -41984,7 +41984,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G1435" t="n">
-        <v>55.4642639160156</v>
+        <v>55.4642677307129</v>
       </c>
       <c r="H1435" t="n">
         <v>151968</v>
@@ -42071,7 +42071,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1438" t="n">
-        <v>57.0984001159668</v>
+        <v>57.0983963012695</v>
       </c>
       <c r="H1438" t="n">
         <v>272329</v>
@@ -42100,7 +42100,7 @@
         <v>60.75</v>
       </c>
       <c r="G1439" t="n">
-        <v>58.3960876464844</v>
+        <v>58.3960838317871</v>
       </c>
       <c r="H1439" t="n">
         <v>154164</v>
@@ -42129,7 +42129,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1440" t="n">
-        <v>57.8673973083496</v>
+        <v>57.8674011230469</v>
       </c>
       <c r="H1440" t="n">
         <v>280870</v>
@@ -42158,7 +42158,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1441" t="n">
-        <v>57.0984001159668</v>
+        <v>57.0983963012695</v>
       </c>
       <c r="H1441" t="n">
         <v>255472</v>
@@ -42216,7 +42216,7 @@
         <v>59.3499984741211</v>
       </c>
       <c r="G1443" t="n">
-        <v>57.0503349304199</v>
+        <v>57.0503311157227</v>
       </c>
       <c r="H1443" t="n">
         <v>165484</v>
@@ -42274,7 +42274,7 @@
         <v>59.75</v>
       </c>
       <c r="G1445" t="n">
-        <v>57.4348335266113</v>
+        <v>57.4348373413086</v>
       </c>
       <c r="H1445" t="n">
         <v>132975</v>
@@ -42303,7 +42303,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G1446" t="n">
-        <v>56.3293914794922</v>
+        <v>56.3293952941895</v>
       </c>
       <c r="H1446" t="n">
         <v>192651</v>
@@ -42390,7 +42390,7 @@
         <v>59.25</v>
       </c>
       <c r="G1449" t="n">
-        <v>56.954216003418</v>
+        <v>56.9542121887207</v>
       </c>
       <c r="H1449" t="n">
         <v>128105</v>
@@ -42477,7 +42477,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G1452" t="n">
-        <v>57.2425880432129</v>
+        <v>57.2425842285156</v>
       </c>
       <c r="H1452" t="n">
         <v>210667</v>
@@ -42564,7 +42564,7 @@
         <v>57.9000015258789</v>
       </c>
       <c r="G1455" t="n">
-        <v>55.6565208435059</v>
+        <v>55.6565170288086</v>
       </c>
       <c r="H1455" t="n">
         <v>192310</v>
@@ -42593,7 +42593,7 @@
         <v>58.9500007629395</v>
       </c>
       <c r="G1456" t="n">
-        <v>56.6658401489258</v>
+        <v>56.6658325195312</v>
       </c>
       <c r="H1456" t="n">
         <v>252123</v>
@@ -42651,7 +42651,7 @@
         <v>58.9500007629395</v>
       </c>
       <c r="G1458" t="n">
-        <v>56.6658401489258</v>
+        <v>56.6658325195312</v>
       </c>
       <c r="H1458" t="n">
         <v>138739</v>
@@ -42680,7 +42680,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G1459" t="n">
-        <v>55.608455657959</v>
+        <v>55.6084594726562</v>
       </c>
       <c r="H1459" t="n">
         <v>156244</v>
@@ -42709,7 +42709,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1460" t="n">
-        <v>53.4456405639648</v>
+        <v>53.4456367492676</v>
       </c>
       <c r="H1460" t="n">
         <v>330821</v>
@@ -42767,7 +42767,7 @@
         <v>56</v>
       </c>
       <c r="G1462" t="n">
-        <v>53.8301391601562</v>
+        <v>53.830135345459</v>
       </c>
       <c r="H1462" t="n">
         <v>169905</v>
@@ -42825,7 +42825,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G1464" t="n">
-        <v>52.2440719604492</v>
+        <v>52.244068145752</v>
       </c>
       <c r="H1464" t="n">
         <v>179506</v>
@@ -42854,7 +42854,7 @@
         <v>55.4500007629395</v>
       </c>
       <c r="G1465" t="n">
-        <v>53.3014526367188</v>
+        <v>53.3014488220215</v>
       </c>
       <c r="H1465" t="n">
         <v>250890</v>
@@ -42883,7 +42883,7 @@
         <v>54.75</v>
       </c>
       <c r="G1466" t="n">
-        <v>52.6285705566406</v>
+        <v>52.6285743713379</v>
       </c>
       <c r="H1466" t="n">
         <v>229801</v>
@@ -42912,7 +42912,7 @@
         <v>56.2000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>54.022388458252</v>
+        <v>54.0223846435547</v>
       </c>
       <c r="H1467" t="n">
         <v>175360</v>
@@ -42970,7 +42970,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1469" t="n">
-        <v>54.5991401672363</v>
+        <v>54.5991439819336</v>
       </c>
       <c r="H1469" t="n">
         <v>253594</v>
@@ -42999,7 +42999,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G1470" t="n">
-        <v>54.9355773925781</v>
+        <v>54.9355812072754</v>
       </c>
       <c r="H1470" t="n">
         <v>252544</v>
@@ -43028,7 +43028,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G1471" t="n">
-        <v>55.608455657959</v>
+        <v>55.6084594726562</v>
       </c>
       <c r="H1471" t="n">
         <v>156036</v>
@@ -43057,7 +43057,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G1472" t="n">
-        <v>57.2425880432129</v>
+        <v>57.2425842285156</v>
       </c>
       <c r="H1472" t="n">
         <v>205128</v>
@@ -43144,7 +43144,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G1475" t="n">
-        <v>57.2425880432129</v>
+        <v>57.2425842285156</v>
       </c>
       <c r="H1475" t="n">
         <v>105133</v>
@@ -43173,7 +43173,7 @@
         <v>60</v>
       </c>
       <c r="G1476" t="n">
-        <v>57.6751441955566</v>
+        <v>57.6751480102539</v>
       </c>
       <c r="H1476" t="n">
         <v>136714</v>
@@ -43202,7 +43202,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>58.1077156066895</v>
+        <v>58.1077117919922</v>
       </c>
       <c r="H1477" t="n">
         <v>177081</v>
@@ -43318,7 +43318,7 @@
         <v>63</v>
       </c>
       <c r="G1481" t="n">
-        <v>60.558910369873</v>
+        <v>60.5589065551758</v>
       </c>
       <c r="H1481" t="n">
         <v>364209</v>
@@ -43376,7 +43376,7 @@
         <v>63.75</v>
       </c>
       <c r="G1483" t="n">
-        <v>61.2798461914062</v>
+        <v>61.279842376709</v>
       </c>
       <c r="H1483" t="n">
         <v>223472</v>
@@ -43492,7 +43492,7 @@
         <v>68.25</v>
       </c>
       <c r="G1487" t="n">
-        <v>65.6054840087891</v>
+        <v>65.6054916381836</v>
       </c>
       <c r="H1487" t="n">
         <v>314059</v>
@@ -43550,7 +43550,7 @@
         <v>67.9000015258789</v>
       </c>
       <c r="G1489" t="n">
-        <v>65.26904296875</v>
+        <v>65.2690505981445</v>
       </c>
       <c r="H1489" t="n">
         <v>221608</v>
@@ -43608,7 +43608,7 @@
         <v>66.9499969482422</v>
       </c>
       <c r="G1491" t="n">
-        <v>64.355842590332</v>
+        <v>64.3558502197266</v>
       </c>
       <c r="H1491" t="n">
         <v>495189</v>
@@ -43637,7 +43637,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G1492" t="n">
-        <v>59.2131500244141</v>
+        <v>59.2131538391113</v>
       </c>
       <c r="H1492" t="n">
         <v>874418</v>
@@ -43782,7 +43782,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1497" t="n">
-        <v>59.8860244750977</v>
+        <v>59.8860282897949</v>
       </c>
       <c r="H1497" t="n">
         <v>193934</v>
@@ -43869,7 +43869,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>58.1077156066895</v>
+        <v>58.1077117919922</v>
       </c>
       <c r="H1500" t="n">
         <v>187391</v>
@@ -43898,7 +43898,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G1501" t="n">
-        <v>58.5883407592773</v>
+        <v>58.5883445739746</v>
       </c>
       <c r="H1501" t="n">
         <v>202380</v>
@@ -43927,7 +43927,7 @@
         <v>60.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>58.3960876464844</v>
+        <v>58.3960838317871</v>
       </c>
       <c r="H1502" t="n">
         <v>126334</v>
@@ -43956,7 +43956,7 @@
         <v>59</v>
       </c>
       <c r="G1503" t="n">
-        <v>56.7139015197754</v>
+        <v>56.7138977050781</v>
       </c>
       <c r="H1503" t="n">
         <v>280819</v>
@@ -44043,7 +44043,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G1506" t="n">
-        <v>58.5402755737305</v>
+        <v>58.5402793884277</v>
       </c>
       <c r="H1506" t="n">
         <v>208261</v>
@@ -44072,7 +44072,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G1507" t="n">
-        <v>58.1077156066895</v>
+        <v>58.1077117919922</v>
       </c>
       <c r="H1507" t="n">
         <v>199981</v>
@@ -44130,7 +44130,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1509" t="n">
-        <v>58.444149017334</v>
+        <v>58.4441452026367</v>
       </c>
       <c r="H1509" t="n">
         <v>144065</v>
@@ -44159,7 +44159,7 @@
         <v>63</v>
       </c>
       <c r="G1510" t="n">
-        <v>60.558910369873</v>
+        <v>60.5589065551758</v>
       </c>
       <c r="H1510" t="n">
         <v>212777</v>
@@ -44188,7 +44188,7 @@
         <v>62.5499992370605</v>
       </c>
       <c r="G1511" t="n">
-        <v>60.1263389587402</v>
+        <v>60.1263427734375</v>
       </c>
       <c r="H1511" t="n">
         <v>281860</v>
@@ -44246,7 +44246,7 @@
         <v>62.8499984741211</v>
       </c>
       <c r="G1513" t="n">
-        <v>60.4147148132324</v>
+        <v>60.4147186279297</v>
       </c>
       <c r="H1513" t="n">
         <v>172764</v>
@@ -44304,7 +44304,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1515" t="n">
-        <v>58.0596542358398</v>
+        <v>58.0596504211426</v>
       </c>
       <c r="H1515" t="n">
         <v>245949</v>
@@ -44420,7 +44420,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>57.8673973083496</v>
+        <v>57.8674011230469</v>
       </c>
       <c r="H1519" t="n">
         <v>150381</v>
@@ -44449,7 +44449,7 @@
         <v>61.2999992370605</v>
       </c>
       <c r="G1520" t="n">
-        <v>58.9247817993164</v>
+        <v>58.9247779846191</v>
       </c>
       <c r="H1520" t="n">
         <v>97599</v>
@@ -44478,7 +44478,7 @@
         <v>62.5</v>
       </c>
       <c r="G1521" t="n">
-        <v>60.0782775878906</v>
+        <v>60.0782814025879</v>
       </c>
       <c r="H1521" t="n">
         <v>136032</v>
@@ -44507,7 +44507,7 @@
         <v>62.5</v>
       </c>
       <c r="G1522" t="n">
-        <v>60.0782775878906</v>
+        <v>60.0782814025879</v>
       </c>
       <c r="H1522" t="n">
         <v>147492</v>
@@ -44565,7 +44565,7 @@
         <v>64.25</v>
       </c>
       <c r="G1524" t="n">
-        <v>61.7604751586914</v>
+        <v>61.7604713439941</v>
       </c>
       <c r="H1524" t="n">
         <v>141070</v>
@@ -44623,7 +44623,7 @@
         <v>64.4499969482422</v>
       </c>
       <c r="G1526" t="n">
-        <v>61.9527206420898</v>
+        <v>61.9527130126953</v>
       </c>
       <c r="H1526" t="n">
         <v>138905</v>
@@ -44681,7 +44681,7 @@
         <v>63.75</v>
       </c>
       <c r="G1528" t="n">
-        <v>61.2798461914062</v>
+        <v>61.279842376709</v>
       </c>
       <c r="H1528" t="n">
         <v>171880</v>
@@ -44710,7 +44710,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G1529" t="n">
-        <v>61.9046592712402</v>
+        <v>61.9046630859375</v>
       </c>
       <c r="H1529" t="n">
         <v>121552</v>
@@ -44739,7 +44739,7 @@
         <v>62.5499992370605</v>
       </c>
       <c r="G1530" t="n">
-        <v>60.1263389587402</v>
+        <v>60.1263427734375</v>
       </c>
       <c r="H1530" t="n">
         <v>182609</v>
@@ -44826,7 +44826,7 @@
         <v>60.2000007629395</v>
       </c>
       <c r="G1533" t="n">
-        <v>57.8673973083496</v>
+        <v>57.8674011230469</v>
       </c>
       <c r="H1533" t="n">
         <v>148592</v>
@@ -44855,7 +44855,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G1534" t="n">
-        <v>58.0115852355957</v>
+        <v>58.0115814208984</v>
       </c>
       <c r="H1534" t="n">
         <v>179167</v>
@@ -44913,7 +44913,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G1536" t="n">
-        <v>55.0797653198242</v>
+        <v>55.0797729492188</v>
       </c>
       <c r="H1536" t="n">
         <v>242708</v>
@@ -45000,7 +45000,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1539" t="n">
-        <v>54.6952705383301</v>
+        <v>54.6952743530273</v>
       </c>
       <c r="H1539" t="n">
         <v>246676</v>
@@ -45058,7 +45058,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1541" t="n">
-        <v>53.4456405639648</v>
+        <v>53.4456367492676</v>
       </c>
       <c r="H1541" t="n">
         <v>206244</v>
@@ -45087,7 +45087,7 @@
         <v>53.0499992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>50.9944458007812</v>
+        <v>50.9944496154785</v>
       </c>
       <c r="H1542" t="n">
         <v>303135</v>
@@ -45116,7 +45116,7 @@
         <v>52.5</v>
       </c>
       <c r="G1543" t="n">
-        <v>50.4657516479492</v>
+        <v>50.4657554626465</v>
       </c>
       <c r="H1543" t="n">
         <v>229525</v>
@@ -45145,7 +45145,7 @@
         <v>54.25</v>
       </c>
       <c r="G1544" t="n">
-        <v>52.14794921875</v>
+        <v>52.1479454040527</v>
       </c>
       <c r="H1544" t="n">
         <v>323344</v>
@@ -45174,7 +45174,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1545" t="n">
-        <v>51.3308792114258</v>
+        <v>51.330883026123</v>
       </c>
       <c r="H1545" t="n">
         <v>260026</v>
@@ -45203,7 +45203,7 @@
         <v>53.0499992370605</v>
       </c>
       <c r="G1546" t="n">
-        <v>50.9944458007812</v>
+        <v>50.9944496154785</v>
       </c>
       <c r="H1546" t="n">
         <v>304059</v>
@@ -45232,7 +45232,7 @@
         <v>54.3499984741211</v>
       </c>
       <c r="G1547" t="n">
-        <v>52.2440719604492</v>
+        <v>52.244068145752</v>
       </c>
       <c r="H1547" t="n">
         <v>190906</v>
@@ -45290,7 +45290,7 @@
         <v>55.75</v>
       </c>
       <c r="G1549" t="n">
-        <v>53.5898284912109</v>
+        <v>53.5898246765137</v>
       </c>
       <c r="H1549" t="n">
         <v>192479</v>
@@ -45348,7 +45348,7 @@
         <v>52.25</v>
       </c>
       <c r="G1551" t="n">
-        <v>50.2254371643066</v>
+        <v>50.2254409790039</v>
       </c>
       <c r="H1551" t="n">
         <v>234554</v>
@@ -45377,7 +45377,7 @@
         <v>51.5</v>
       </c>
       <c r="G1552" t="n">
-        <v>49.5045051574707</v>
+        <v>49.5045013427734</v>
       </c>
       <c r="H1552" t="n">
         <v>224340</v>
@@ -45406,7 +45406,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>49.2161293029785</v>
+        <v>49.2161254882812</v>
       </c>
       <c r="H1553" t="n">
         <v>206459</v>
@@ -45522,7 +45522,7 @@
         <v>47.9799995422363</v>
       </c>
       <c r="G1557" t="n">
-        <v>46.1208953857422</v>
+        <v>46.1208915710449</v>
       </c>
       <c r="H1557" t="n">
         <v>495672</v>
@@ -45638,7 +45638,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G1561" t="n">
-        <v>45.3903503417969</v>
+        <v>45.3903465270996</v>
       </c>
       <c r="H1561" t="n">
         <v>340636</v>
@@ -45754,7 +45754,7 @@
         <v>47.6199989318848</v>
       </c>
       <c r="G1565" t="n">
-        <v>45.7748374938965</v>
+        <v>45.774845123291</v>
       </c>
       <c r="H1565" t="n">
         <v>663748</v>
@@ -45841,7 +45841,7 @@
         <v>46.9599990844727</v>
       </c>
       <c r="G1568" t="n">
-        <v>45.1404151916504</v>
+        <v>45.1404190063477</v>
       </c>
       <c r="H1568" t="n">
         <v>228254</v>
@@ -45870,7 +45870,7 @@
         <v>47.5200004577637</v>
       </c>
       <c r="G1569" t="n">
-        <v>45.6787185668945</v>
+        <v>45.6787223815918</v>
       </c>
       <c r="H1569" t="n">
         <v>237974</v>
@@ -46131,7 +46131,7 @@
         <v>42.8800010681152</v>
       </c>
       <c r="G1578" t="n">
-        <v>41.218505859375</v>
+        <v>41.2185096740723</v>
       </c>
       <c r="H1578" t="n">
         <v>241144</v>
@@ -46160,7 +46160,7 @@
         <v>46.2599983215332</v>
       </c>
       <c r="G1579" t="n">
-        <v>44.4675369262695</v>
+        <v>44.4675407409668</v>
       </c>
       <c r="H1579" t="n">
         <v>356713</v>
@@ -46189,7 +46189,7 @@
         <v>46.3600006103516</v>
       </c>
       <c r="G1580" t="n">
-        <v>44.5636711120605</v>
+        <v>44.5636672973633</v>
       </c>
       <c r="H1580" t="n">
         <v>223235</v>
@@ -46218,7 +46218,7 @@
         <v>47.0999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>45.2749900817871</v>
+        <v>45.2749862670898</v>
       </c>
       <c r="H1581" t="n">
         <v>399215</v>
@@ -46421,7 +46421,7 @@
         <v>48.5200004577637</v>
       </c>
       <c r="G1588" t="n">
-        <v>46.6399688720703</v>
+        <v>46.6399726867676</v>
       </c>
       <c r="H1588" t="n">
         <v>357768</v>
@@ -46450,7 +46450,7 @@
         <v>46.6399993896484</v>
       </c>
       <c r="G1589" t="n">
-        <v>44.8328132629395</v>
+        <v>44.8328170776367</v>
       </c>
       <c r="H1589" t="n">
         <v>450533</v>
@@ -46479,7 +46479,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1590" t="n">
-        <v>43.9292373657227</v>
+        <v>43.9292411804199</v>
       </c>
       <c r="H1590" t="n">
         <v>222131</v>
@@ -46508,7 +46508,7 @@
         <v>44.8400001525879</v>
       </c>
       <c r="G1591" t="n">
-        <v>43.1025619506836</v>
+        <v>43.1025581359863</v>
       </c>
       <c r="H1591" t="n">
         <v>379874</v>
@@ -46566,7 +46566,7 @@
         <v>41.8400001525879</v>
       </c>
       <c r="G1593" t="n">
-        <v>40.2187995910645</v>
+        <v>40.2188034057617</v>
       </c>
       <c r="H1593" t="n">
         <v>497291</v>
@@ -46595,7 +46595,7 @@
         <v>39.4599990844727</v>
       </c>
       <c r="G1594" t="n">
-        <v>37.931022644043</v>
+        <v>37.9310188293457</v>
       </c>
       <c r="H1594" t="n">
         <v>493448</v>
@@ -46682,7 +46682,7 @@
         <v>39.3400001525879</v>
       </c>
       <c r="G1597" t="n">
-        <v>37.8156700134277</v>
+        <v>37.815673828125</v>
       </c>
       <c r="H1597" t="n">
         <v>215734</v>
@@ -46711,7 +46711,7 @@
         <v>39.6800003051758</v>
       </c>
       <c r="G1598" t="n">
-        <v>38.1424980163574</v>
+        <v>38.142505645752</v>
       </c>
       <c r="H1598" t="n">
         <v>367532</v>
@@ -46740,7 +46740,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1599" t="n">
-        <v>38.0655975341797</v>
+        <v>38.065601348877</v>
       </c>
       <c r="H1599" t="n">
         <v>206218</v>
@@ -46769,7 +46769,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>38.0655975341797</v>
+        <v>38.065601348877</v>
       </c>
       <c r="H1600" t="n">
         <v>225812</v>
@@ -46798,7 +46798,7 @@
         <v>40.0400009155273</v>
       </c>
       <c r="G1601" t="n">
-        <v>38.4885482788086</v>
+        <v>38.4885444641113</v>
       </c>
       <c r="H1601" t="n">
         <v>181803</v>
@@ -46885,7 +46885,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G1604" t="n">
-        <v>38.4308738708496</v>
+        <v>38.4308776855469</v>
       </c>
       <c r="H1604" t="n">
         <v>334661</v>
@@ -47001,7 +47001,7 @@
         <v>38.9000015258789</v>
       </c>
       <c r="G1608" t="n">
-        <v>37.3927192687988</v>
+        <v>37.3927230834961</v>
       </c>
       <c r="H1608" t="n">
         <v>185303</v>
@@ -47059,7 +47059,7 @@
         <v>37.560001373291</v>
       </c>
       <c r="G1610" t="n">
-        <v>36.1046485900879</v>
+        <v>36.1046447753906</v>
       </c>
       <c r="H1610" t="n">
         <v>335521</v>
@@ -47320,7 +47320,7 @@
         <v>38.6599998474121</v>
       </c>
       <c r="G1619" t="n">
-        <v>37.1620254516602</v>
+        <v>37.1620216369629</v>
       </c>
       <c r="H1619" t="n">
         <v>357618</v>
@@ -47349,7 +47349,7 @@
         <v>40.6199989318848</v>
       </c>
       <c r="G1620" t="n">
-        <v>39.0460777282715</v>
+        <v>39.0460739135742</v>
       </c>
       <c r="H1620" t="n">
         <v>899382</v>
@@ -47378,7 +47378,7 @@
         <v>41.0999984741211</v>
       </c>
       <c r="G1621" t="n">
-        <v>39.5074729919434</v>
+        <v>39.5074768066406</v>
       </c>
       <c r="H1621" t="n">
         <v>356177</v>
@@ -47436,7 +47436,7 @@
         <v>40.6800003051758</v>
       </c>
       <c r="G1623" t="n">
-        <v>39.1037483215332</v>
+        <v>39.1037521362305</v>
       </c>
       <c r="H1623" t="n">
         <v>268025</v>
@@ -47465,7 +47465,7 @@
         <v>41.0200004577637</v>
       </c>
       <c r="G1624" t="n">
-        <v>39.4305763244629</v>
+        <v>39.4305725097656</v>
       </c>
       <c r="H1624" t="n">
         <v>268830</v>
@@ -80067,6 +80067,35 @@
         <v>174277</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>35.7000007629395</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>36.0200004577637</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>35.439998626709</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>35.5800018310547</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>35.5800018310547</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>99180</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>
